--- a/TENDERS_1210.xlsx
+++ b/TENDERS_1210.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$P$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,16 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,15 +83,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -448,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -458,13 +473,15 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,35 +522,45 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Позиции: кол-во × цена за ед. в НМЦК, ₽</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Средняя цена за ед. в НМЦК, ₽</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Себестоимость, ₽</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Валовая маржа при НМЦК</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Ожид. снижение</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Прибыль при НМЦК, ₽</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Прибыль при ожид. снижении, ₽</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -557,7 +584,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Соль техническая 948 т (14 630 ₽/т)</t>
+          <t>Соль техническая 948 т</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -573,27 +600,35 @@
       <c r="G2" s="2" t="n">
         <v>13869240</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>948 т × 14 630 ₽/т</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>14630</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>2370000</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>0.8291182501708817</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>9262976.735973697</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>7859631.555813699</v>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Участвовать</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ на эквивалент</t>
         </is>
@@ -617,7 +652,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Соль техническая 400 т (16 810 ₽/т)</t>
+          <t>Соль техническая 400 т</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -633,27 +668,35 @@
       <c r="G3" s="2" t="n">
         <v>6724000</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>400 т × 16 810 ₽/т</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>16810</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>1000000</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <v>0.851279000594884</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="L3" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>4621641.290520548</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>3941280.074520547</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Участвовать</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>223-ФЗ; обеспечение исполнения 10%</t>
         </is>
@@ -677,7 +720,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Соль техническая 130 т (12 260 ₽/т)</t>
+          <t>Соль техническая 130 т</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -693,27 +736,35 @@
       <c r="G4" s="2" t="n">
         <v>1593800</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>130 т × 12 260 ₽/т</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>12260</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>325000</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="K4" s="4" t="n">
         <v>0.7960848287112561</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="L4" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>1018243.203419178</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>856976.144219178</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Участвовать</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ</t>
         </is>
@@ -722,22 +773,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0372100027326000601</t>
+          <t>0373200001326001396</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение «Администрация Волго-Балтийского бассейна внутренних водных путей»</t>
+          <t>ГБУЗ г. Москвы «ГКБ им. В.В. Вересаева ДЗМ»</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Поставка средств индивидуальной защиты, приобретаемых для нужд ФБУ «Администрация «Волго-Балт» (44-ФЗ)</t>
+          <t>Пробирки вакуумные с активатором</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -747,95 +798,111 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-13 10:00</t>
+          <t>15.10.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>18033874.9</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>13525406.175</v>
-      </c>
-      <c r="I5" s="3" t="n">
+        <v>2952000</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания,: 150 000 шт × 19.68</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1446500</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.5099932249322493</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>2571289.646392574</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>2571289.646392574</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+      <c r="M5" s="2" t="n">
+        <v>1178755.920547945</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>556474.3205479452</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>НМЦК 19,68 ₽ — вдвое выше рынка, поэтому ожидается сильное снижение (вероятно верхний квартиль скидки, 40–55%). Особенность крышки (полнозаходная резьба / двухступенчатое снятие) — нужно подтвердить, что UNIVAC/другая российская пробирка этому соответствует, иначе отклонение. СМП-only. Минимальный о</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0358200022926000030</t>
+          <t>32616447145</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ГКУ Ростовской обл. «Ростовская областная поисково-спасательная служба»</t>
+          <t>АО «Пассажирречтранс»</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Поставка обмундирования</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00</t>
+          <t>16.10.2026 05:00 МСК (09:00 местн.)</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6224420.7</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>4668315.525</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>887484.7246889586</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>887484.7246889586</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+        <v>450798.91</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Кабель судовой КНР и КНРЭ (ГОСТ 7866.1-76), с: 1 730 м × 260.58</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>260.5774046242774</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>281420</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.3757305225072527</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>136974.4710489863</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>68554.01568482628</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
         </is>
       </c>
     </row>
@@ -847,53 +914,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32616443256</t>
+          <t>0372100027326000601</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ГБУ Республики Саха (Якутия) «Государственная Противопожарная Служба Республики Саха(Якутия)»</t>
+          <t>Федеральное бюджетное учреждение «Администрация Волго-Балтийского бассейна внутренних водных путей»</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Поставка форменной одежды для нужд ГБУ РС(Я) "ГПС РС(Я)"</t>
+          <t>Поставка средств индивидуальной защиты, приобретаемых для нужд ФБУ «Администрация «Волго-Балт» (44-ФЗ)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00</t>
+          <t>2026-10-13 10:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4999001.85</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>3749251.3875</v>
-      </c>
-      <c r="I7" s="3" t="n">
+        <v>18033874.9</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Костюм для защиты от термических рисков элект: 1 КОМПЛ × 4 865.60; Строп одинарный регулируемый огнеупорный: 4 шт × 2 379.09; Каска защитная белая: 31 шт × 551.06; Гибкая анкерная линия (20 м): 2 шт × 2 765.56; Наколенники: 15 пар × 871.08; Белье нательное термостойкое: 192 КОМПЛ × 1 741.12; Одежда специальная повышенной видимости: 18 шт × 142.69; Обувь специальная кожаная для защиты от механ: 72 пар × 2 125.85; … ещё 126</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>13525406.175</v>
+      </c>
+      <c r="K7" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>712763.1621311915</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>712763.1621311915</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="2" t="n">
+        <v>2571289.646392574</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>2571289.646392574</v>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -907,53 +984,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32616438570</t>
+          <t>0358200022926000030</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ООО «Теплоэнергетическая Компания - 2»</t>
+          <t>ГКУ Ростовской обл. «Ростовская областная поисково-спасательная служба»</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Поставка зимней спецодежды</t>
+          <t>Поставка обмундирования</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00</t>
+          <t>2026-10-19 09:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4810413.58</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>3607810.185</v>
-      </c>
-      <c r="I8" s="3" t="n">
+        <v>6224420.7</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Костюм спасателя зимний (куртка, брюки утепле: 168 КОМПЛ × 7 698.83; Костюм спасателя летний (куртка, брюки, кепка: 241 КОМПЛ × 6 613.44; Комбинезон спасателя зимний, шт.: 208 шт × 7 565.57; Комбинезон спасателя летний, шт.: 239 шт × 6 542.14; Футболка форменная, шт.: 268 шт × 746.15</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>4668315.525</v>
+      </c>
+      <c r="K8" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="L8" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>685874.0399225147</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>685874.0399225147</v>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="2" t="n">
+        <v>887484.7246889586</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>887484.7246889586</v>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -967,53 +1054,61 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ГП622514</t>
+          <t>32616443256</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>АО «Арго»</t>
+          <t>ГБУ Республики Саха (Якутия) «Государственная Противопожарная Служба Республики Саха(Якутия)»</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Закупка спецодежды, обуви и средств индивидуальной защиты</t>
+          <t>Поставка форменной одежды для нужд ГБУ РС(Я) "ГПС РС(Я)"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Коммерческие</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00</t>
+          <t>2026-10-15 05:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="I9" s="3" t="n">
+        <v>4999001.85</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Костюм летний полевой: 405 Комплект × ?; Зимняя форменная одежда мужская: 150 Комплект × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>9007.21054054054</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>3749251.3875</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="L9" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>570324.3835616438</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>570324.3835616438</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="2" t="n">
+        <v>712763.1621311915</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>712763.1621311915</v>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1027,17 +1122,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32616402062</t>
+          <t>32616438570</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>МУП «Управление Городского Хозяйства» Муниципального Образования Города Пыть-Ях</t>
+          <t>ООО «Теплоэнергетическая Компания - 2»</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Поставка специальных обуви, одежды, головных уборов, рукавиц и краг</t>
+          <t>Поставка зимней спецодежды</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1047,33 +1142,41 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-13 06:00</t>
+          <t>2026-10-14 08:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3857857.45</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2893393.0875</v>
-      </c>
-      <c r="I10" s="3" t="n">
+        <v>4810413.58</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; Костюм сварщика со спилком утепленный: 20 Штука × ?; Костюм женский утепленный: 41 Штука × ?; Костюм зимний мужской для защиты от термическ: 28 Штука × ?; Куртка охранника зимняя: 46 Штука × ?; Брюки охранника зимние: 46 Штука × ?; Шеврон на липучке для спецодежды: 46 Штука × ?; Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; … ещё 6 (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>3891.920372168285</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>3607810.185</v>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="L10" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>550057.5430099862</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>550057.5430099862</v>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="2" t="n">
+        <v>685874.0399225147</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>685874.0399225147</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1087,53 +1190,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32616431081</t>
+          <t>ГП622514</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
+          <t>АО «Арго»</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Поставка спецодежды</t>
+          <t>Закупка спецодежды, обуви и средств индивидуальной защиты</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Коммерческие</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00</t>
+          <t>2026-10-15 17:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3637476.36</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>2728107.27</v>
-      </c>
-      <c r="I11" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="L11" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>518635.365684263</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>518635.365684263</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="2" t="n">
+        <v>570324.3835616438</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>570324.3835616438</v>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1147,17 +1256,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32616448893</t>
+          <t>32616402062</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Московской обл. «Мособллес»</t>
+          <t>МУП «Управление Городского Хозяйства» Муниципального Образования Города Пыть-Ях</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Поставка обуви специальной для защиты от механических воздействий</t>
+          <t>Поставка специальных обуви, одежды, головных уборов, рукавиц и краг</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1167,33 +1276,43 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00</t>
+          <t>2026-10-13 06:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2511958.68</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>1883969.01</v>
-      </c>
-      <c r="I12" s="3" t="n">
+        <v>3857857.45</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Ботинки кожаные утепленные: 46 Пара (2 шт.) × ?; Сапоги кожаные утепленные: 185 Пара (2 шт.) × ?; Сапоги утепленные "Надым" ТХ-011р/п с КП и АС: 21 Пара (2 шт.) × ?; Валенки с резиновым низом: 40 Пара (2 шт.) × ?; Костюм сварщика утепленный (4 класс защиты): 8 Штука × ?; Костюм от пониженных температур (4 класс защи: 115 Штука × ?; Костюм сигнальный с водоотталкивающей пропитк: 41 Штука × ?; Костюм зимний петролеум плюс куртка-П/К, Т.Си: 21 Штука × ?; … ещё 18</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>2893393.0875</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="L12" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>358157.8214258302</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>358157.8214258302</v>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="2" t="n">
+        <v>550057.5430099862</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>550057.5430099862</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1207,7 +1326,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32616427138</t>
+          <t>32616431081</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1217,7 +1336,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Поставка спецодежды для защиты от термических рисков электрической дуги</t>
+          <t>Поставка спецодежды</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1227,33 +1346,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00</t>
+          <t>2026-10-19 08:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1477969</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1108476.75</v>
-      </c>
-      <c r="I13" s="3" t="n">
+        <v>3637476.36</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Жилет сигнальный: 14 Штука × ?; Жилет утепленный: 64 Штука × ?; Костюм летний  мужской противоэнцэфалитный: 1 Комплект × ?; Костюм летний мужской для защиты от механичес: 23 Комплект × ?; Костюм летний женский для защиты от механичес: 1 Комплект × ?; Куртка зимняя мужской для защиты от механичес: 20 Штука × ?; Полукомбинезон зимний мужской для защиты от м: 20 Штука × ?; Костюм летний мужской сигнальный флуоресцентн: 4 Комплект × ?; … ещё 28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>2728107.27</v>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="L13" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K13" s="2" t="n">
-        <v>210730.4397120549</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>210730.4397120549</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="2" t="n">
+        <v>518635.365684263</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>518635.365684263</v>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1267,53 +1396,61 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10749746</t>
+          <t>32616448893</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Боханский Аграрный Техникум»</t>
+          <t>Государственное автономное учреждение Московской обл. «Мособллес»</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря, индивидуальная одежда и обувь для каждого студента. согласно спецификации и списка размеров.</t>
+          <t>Поставка обуви специальной для защиты от механических воздействий</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00</t>
+          <t>2026-10-16 10:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>498000</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>373500</v>
-      </c>
-      <c r="I14" s="3" t="n">
+        <v>2511958.68</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ?; Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>3171.665</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1883969.01</v>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="L14" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K14" s="2" t="n">
-        <v>71005.38575342466</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>71005.38575342466</v>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" s="2" t="n">
+        <v>358157.8214258302</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>358157.8214258302</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1327,53 +1464,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0173200001426002006</t>
+          <t>32616427138</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Московская Административная Дорожная Инспекция</t>
+          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Поставка форменной одежды</t>
+          <t>Поставка спецодежды для защиты от термических рисков электрической дуги</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-15 08:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>435666.4</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>326749.8</v>
-      </c>
-      <c r="I15" s="3" t="n">
+        <v>1477969</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Костюм летний для защиты от термических риско: 15 Комплект × ?; Костюм зимний для защиты от термических риско: 8 Комплект × ?; Куртка-рубашка для защиты от термических риск: 11 Штука × ?; Куртка-накидка для защиты от термических риск: 10 Штука × ?; Плащ термостойкий для защиты от термических р: 1 Штука × ?; Бельё нательное (фуфайка): 26 Штука × ?; Бельё нательное (кальсоны): 26 Штука × ?; Бельё нательное утепленное (фуфайка): 12 Штука × ?; … ещё 12</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1108476.75</v>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="L15" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K15" s="2" t="n">
-        <v>62117.79275463011</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>62117.79275463011</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" s="2" t="n">
+        <v>210730.4397120549</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>210730.4397120549</v>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1387,17 +1534,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10747873</t>
+          <t>10749746</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Боханский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
+          <t>Приобретение мягкого инвентаря, индивидуальная одежда и обувь для каждого студента. согласно спецификации и списка размеров.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1407,33 +1554,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-14 11:20</t>
+          <t>2026-10-14 10:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>402140</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>301605</v>
-      </c>
-      <c r="I16" s="3" t="n">
+        <v>498000</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n">
+        <v>373500</v>
+      </c>
+      <c r="K16" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="L16" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K16" s="2" t="n">
-        <v>57337.56190136987</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>57337.56190136987</v>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="2" t="n">
+        <v>71005.38575342466</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>71005.38575342466</v>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1447,53 +1600,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10747880</t>
+          <t>0173200001426002006</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
+          <t>Московская Административная Дорожная Инспекция</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
+          <t>Поставка форменной одежды</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-14 11:20</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>402140</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>301605</v>
-      </c>
-      <c r="I17" s="3" t="n">
+        <v>435666.4</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Термобелье спортивное, для взрослого: 2 шт × 6 100; Шорты: 2 шт × 4 266.67; Термобелье спортивное, для взрослого: 4 шт × 5 033.33; Футболка трикотажная: 2 шт × 1 033.33; Футболка трикотажная: 8 шт × 1 033.33; Шорты: 4 шт × 4 266.67; Шорты: 6 шт × 4 266.67; Шорты: 6 шт × 4 266.67; … ещё 29</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>2562.743529411765</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>326749.8</v>
+      </c>
+      <c r="K17" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="L17" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K17" s="2" t="n">
-        <v>57337.56190136987</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>57337.56190136987</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="2" t="n">
+        <v>62117.79275463011</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>62117.79275463011</v>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1507,53 +1668,59 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0358300160926000018</t>
+          <t>10747873</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>МКУ «Управление по Делам Гражданской Обороны, Предупреждения и Ликвидации Чрезвычайных Ситуаций Города Каменск-Шахтинский»</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Поставка специальной одежды</t>
+          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-14 11:20</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>320700.06</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>240525.045</v>
-      </c>
-      <c r="I18" s="3" t="n">
+        <v>402140</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n">
+        <v>301605</v>
+      </c>
+      <c r="K18" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="L18" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K18" s="2" t="n">
-        <v>45725.76600692053</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>45725.76600692053</v>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1567,53 +1734,59 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0301300019426000247</t>
+          <t>10747880</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ГБУЗ Республиканский Клинический Госпиталь Ветеранов Войн им. М.В. Каменева</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Поставка спецодежды</t>
+          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00</t>
+          <t>2026-10-14 11:20</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>270651</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>202988.25</v>
-      </c>
-      <c r="I19" s="3" t="n">
+        <v>402140</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n">
+        <v>301605</v>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="L19" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K19" s="2" t="n">
-        <v>38589.7161838356</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>38589.7161838356</v>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1627,17 +1800,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0302200020326000023</t>
+          <t>0358300160926000018</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Республиканская служба по охране, контролю и регулированию использования объектов животного мира, отнесенных к объектам охоты, контролю и надзору в сфере природопользования</t>
+          <t>МКУ «Управление по Делам Гражданской Обороны, Предупреждения и Ликвидации Чрезвычайных Ситуаций Города Каменск-Шахтинский»</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Поставка спецобуви</t>
+          <t>Поставка специальной одежды</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1647,33 +1820,43 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-14 04:00</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>230181</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>172635.75</v>
-      </c>
-      <c r="I20" s="3" t="n">
+        <v>320700.06</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Ботинки с высокими берцами зимние: 18 пар × 5 400; Футболка поло с длинным рукавом: 18 шт × 2 800; Головной убор зимний: 18 шт × 750; Костюм спасателя мужской зимний: 18 шт × 8 866.67</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>240525.045</v>
+      </c>
+      <c r="K20" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="L20" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>32819.45923315067</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>32819.45923315067</v>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="2" t="n">
+        <v>45725.76600692053</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>45725.76600692053</v>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1687,17 +1870,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0340100009726000070</t>
+          <t>0301300019426000247</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Федеральное государственное бюджетное Профессиональное Образовательное учреждение «Орловское Специальное Учебно-Воспитательное Учреждение Закрытого Типа»</t>
+          <t>ГБУЗ Республиканский Клинический Госпиталь Ветеранов Войн им. М.В. Каменева</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Поставка зимней одежды для воспитанников (термобелье)</t>
+          <t>Поставка спецодежды</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,33 +1890,41 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-15 08:30</t>
+          <t>2026-10-15 07:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>213567.9</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>160175.925</v>
-      </c>
-      <c r="I21" s="3" t="n">
+        <v>270651</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Костюм мужской рабочий  (96/170): 1 шт × 4 857; Костюм мужской рабочий  (104/165): 1 шт × 4 857; Костюм мужской рабочий  (104/176): 2 шт × 4 857; Костюм мужской рабочий  (108/170): 3 шт × 4 857; Костюм мужской рабочий  (108/176): 3 шт × 4 857; Костюм мужской рабочий  (112/170): 2 шт × 4 857; Костюм мужской рабочий  (112/176): 1 шт × 4 857; Костюм мужской рабочий  (96/158): 1 шт × 5 600; … ещё 29</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>5012.055555555556</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>202988.25</v>
+      </c>
+      <c r="K21" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="L21" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K21" s="2" t="n">
-        <v>30450.74522901369</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>30450.74522901369</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="2" t="n">
+        <v>38589.7161838356</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>38589.7161838356</v>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1747,53 +1938,61 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>32616452815</t>
+          <t>0302200020326000023</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Здравоохранения «Городская Больница № 2 г. Магнитогорск»</t>
+          <t>Республиканская служба по охране, контролю и регулированию использования объектов животного мира, отнесенных к объектам охоты, контролю и надзору в сфере природопользования</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Поставка комплектов зимней спецодежды и рукавиц</t>
+          <t>Поставка спецобуви</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00</t>
+          <t>2026-10-14 04:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>187355.52</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>140516.64</v>
-      </c>
-      <c r="I22" s="3" t="n">
+        <v>230181</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Ботинки специальные с высокими берцами зимние: 18 пар × 3 639; Ботинки специальные с высокими берцами: 17 пар × 8 299; Обувь демисезонная: 4 пар × 5 899</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>5902.076923076923</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>172635.75</v>
+      </c>
+      <c r="K22" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="L22" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K22" s="2" t="n">
-        <v>26713.3553627178</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>26713.3553627178</v>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="2" t="n">
+        <v>32819.45923315067</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>32819.45923315067</v>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1807,53 +2006,61 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>295997-26LO</t>
+          <t>0340100009726000070</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>МКУ «Городское Хозяйство» Муниципального Образования Волосовское Городское Поселение Волосовского Муниципального Района Ленинградской Области</t>
+          <t>Федеральное государственное бюджетное Профессиональное Образовательное учреждение «Орловское Специальное Учебно-Воспитательное Учреждение Закрытого Типа»</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Поставка товаров согласно Спецификации (Специальная одежда и обувь)</t>
+          <t>Поставка зимней одежды для воспитанников (термобелье)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-13 10:30</t>
+          <t>2026-10-15 08:30</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>152190</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>114142.5</v>
-      </c>
-      <c r="I23" s="3" t="n">
+        <v>213567.9</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 4 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 3 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; … ещё 29</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>2033.98</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>160175.925</v>
+      </c>
+      <c r="K23" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="L23" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K23" s="2" t="n">
-        <v>21699.41698356164</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>21699.41698356164</v>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="2" t="n">
+        <v>30450.74522901369</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>30450.74522901369</v>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1867,60 +2074,856 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>32616452815</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Государственное автономное учреждение Здравоохранения «Городская Больница № 2 г. Магнитогорск»</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Поставка комплектов зимней спецодежды и рукавиц</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:00</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>187355.52</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Костюм утепленный Ангара: 16 Комплект × ?; Рукавицы утепленные G14: 16 Пара (2 шт.) × ?</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>140516.64</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>26713.3553627178</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>26713.3553627178</v>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>295997-26LO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>МКУ «Городское Хозяйство» Муниципального Образования Волосовское Городское Поселение Волосовского Муниципального Района Ленинградской Области</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Поставка товаров согласно Спецификации (Специальная одежда и обувь)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:30</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>152190</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n">
+        <v>114142.5</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>21699.41698356164</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>21699.41698356164</v>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>1022079</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Краевое ГКУ Для Детей-Сирот и Детей, Оставшихся без Попечения Родителей «Шушенский Детский Дом»</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Закупка одежды</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Коммерческие</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>2026-10-15 20:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>114000</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n">
         <v>85500</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="K26" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="L26" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="M26" s="2" t="n">
         <v>16254.24493150685</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>16254.24493150685</v>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0348300075526000435</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ГБУЗ МО «Королёвская клиническая больница» (ЦКДЛ), лот 7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Контейнеры вакуумные для мочи</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Контейнер вакуумный для мочи 10 мл, 15–16х100: 21 667 шт × 20.64; Контейнер вакуумный для мочи 6,5–7 мл, 13х100: 21 667 шт × 10.66; Контейнер вакуумный для мочи 9–9,5 мл, 16х100: 21 667 шт × 22.70; Контейнер вакуумный для мочи 9,5 мл, 16х100, : 21 667 шт × 15.23</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>17.30742603959939</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1087916.66</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.2747222266666667</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>279266.7297835617</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>253970.7297835617</v>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0387200029826000340</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>БУ ХМАО-Югры «Нижневартовская окружная клиническая больница»</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные (8 видов)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>16.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>900000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная K2ЭДТА 2–? мл 13х75, кол-в: 8 154 шт × 12.86; Пробирка вакуумная цитрат 3,8% 3–? мл 13х75, : 8 154 шт × 12.87; Пробирка вакуумная тромбин 4,5 мл 13х75, кол-: 8 154 шт × 12.10; Пробирка вакуумная K-оксалат/NaF 4,5 мл 13х75: 8 154 шт × 14.72; Пробирка вакуумная активатор 5–? мл 13х(90–10: 8 154 шт × 14.67; Пробирка вакуумная цитрат 3,8% 4–? мл 13х75, : 8 154 шт × 12.88; Пробирка вакуумная K2ЭДТА 4–? мл 13х75, кол-в: 8 154 шт × 12.87; Пробирка вакуумная Li-гепарин 4–? мл 13х75, к: 8 154 шт × 17.40</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>13.79690949227373</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>617434.5</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.3139616666666666</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>190924.8400684932</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1204.840068493151</v>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Количество не определено — qty условные (НМЦК/Σцен ед. поровну). Доставка в Нижневартовск (дорогая логистика). Контракт до 31.03.2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Кабель (ЭОМ)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>32616445794</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Саратовский филиал</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Кабель (27.32)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>15.10.2026 12:00 МСК</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>2176178.2</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>поз.1 ОКПД2 27.32.13.144 Кабели высоковольтны: 100 Метр × ?; поз.2 ОКПД2 27.32.13.111 Кабели силовые с мед: 300 Метр × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 0.07 Километр; тысяча метров × ?; поз.4 ОКПД2 27.32.13.111 Кабели силовые с мед: 120 Метр × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 50 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.22 Километр; тысяча метров × ?; поз.7 ОКПД2 27.32.13.124 Кабели силовые гибки: 1.30 Километр; тысяча метров × ?; поз.8 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; … ещё 10</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>НМЦ 2 176 178,20 в ЕИС — БЕЗ НДС (rostender показывает 2 654 937 с НДС 22%). Клиент на УСН: уточнить в ДоЗ правило сравнения цен (у РусГидро обычно без НДС). Флаги нацрежима по всем 18 позициям = false (ЕИС), но ПП №1875 для 27.32 может быть указан в ДоЗ — проверить. Цены поставщиков не подобраны: н</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Кабель (ЭОМ)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>32616445272</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Воткинский филиал</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Кабель (27.32)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>15.10.2026 12:00 МСК</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1201357.95</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>поз.1 ОКПД2 27.32.13.159 Кабели, провода и шн: 135 Метр × ?; поз.2 ОКПД2 27.32.13.131 Провода силовые для : 0.10 Километр; тысяча метров × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 100 Метр × ?; поз.4 ОКПД2 27.32.14.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 60 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 115 Метр × ?; поз.7 ОКПД2 27.32.13.111 Кабели силовые с мед: 100 Метр × ?; поз.8 ОКПД2 27.32.13.143 Кабели контрольные (: 0.20 Километр; тысяча метров × ?; … ещё 7</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>НМЦ 1 201 357,95 без НДС (rostender: 1 465 656 с НДС). Флаги нацрежима false. Цены не подобраны — нет марок/сечений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Кабель (ЭОМ)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>32616445510</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>АО «НИОПИК»</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Кабель (27.32)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>14.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>529280.65</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Кабель сигнальный КИМЭлВ-ЗГнг(А) (ОКПД2 27.32: 1 усл. ед. × 529 280.65</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>529280.65</v>
+      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Цена за метр не определена: неизвестны длина и конструкция. Ориентир по аналогам 1х2х0,75 (КПСнг(А)-FRHF, МКЭШВнг(А)-LS) 30–60 ₽/м с НДС — для КИМ неприменимо без спецификации. ЭТП РТС-тендер.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0855200000526003358</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Каменская ЦРБ им. Г.М. Савельевой»; организатор ГКУ ПО «Управление по осуществлению закупок Пензенской обл.»</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные (цитрат/K3/активатор)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>15.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1432800</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с цитратом натрия 3,8%, 4–: 15 600 шт × 10.80; Пробирка вакуумная K3ЭДТА 3–? мл 13х75 (КТРУ : 50 400 шт × 10.80; Пробирка вакуумная с активатором свертывания : 60 000 шт × 12</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>11.37142857142857</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1171120</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.1826353992183138</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>103594.3298630137</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>-233458.7178082192</v>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0809500000326003912</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ГБУЗ РМ «Республиканская клиническая больница им. С.В. Каткова»; организатор ГКУ РМ «Региональный центр организации закупок»</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>16.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>950000</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная K3ЭДТА 2–? мл 13х75, пласт: 95 000 шт × 10</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>852400</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>0.1027368421052632</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>-3413.698630136991</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>-239013.698630137</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0164200001926003491</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, Тамбовская КЦРБ, онкодиспансер, Петровская, Мичуринская ЦРБ, ТОДКБ и др.)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1691688</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с K3ЭДТА, пластик, 2–2,7 м: 35 000 шт × 9.24; То же, поз.2: 54 500 шт × 9.58; То же, поз.3: 25 000 шт × 9.93; То же, поз.4: 10 000 шт × 10.32; То же, поз.5: 2 400 шт × 10.72; То же, поз.6: 50 000 шт × 9.38</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>9.56296212549463</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1587948</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.06132336459205243</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>10112.2218739726</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>-407641.8923835617</v>
+      </c>
+      <c r="O34" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0164200001926003492</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, ТОДКБ, Тамбовская КЦРБ, онкодиспансер, Петровская, Уметская, Бондарская ЦРБ и др.); организатор — уполномоченный орган Тамбовской обл.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные с активатором свёртывания</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>2815055</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания,: 60 000 шт × 9.89; То же, поз.2: 115 900 шт × 10.15; То же, поз.3: 20 000 шт × 10.31; То же, поз.4: 36 000 шт × 10.92; То же, поз.5: 45 000 шт × 9.91</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>10.16632358252077</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>2484948</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.1172648491770143</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>157285.0023013699</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-513092.4608219178</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0335200014926003799</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Совместная закупка 26 ГБУЗ Калининградской обл.; организатор ГКУ КО «Центр обеспечения организации и проведения торгов»</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные (совместная закупка, гель/NaF)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>26.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>5909000</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания/: 94 122 шт × 12.29; Пробирка вакуумная с K-оксалатом и NaF 4 мл 1: 94 122 шт × 9.90; Пробирка вакуумная с активатором/гелем 5 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 6 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 5,5 мл: 94 122 шт × 13.53</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>12.55604428295191</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>5187766.56</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.1220567676425792</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>89623.21567123328</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>-1359992.922739726</v>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК поделена поровну по позициям (НМЦК/Σцен ед.). 26 отдельных контрактов, ~26 точек доставки в эксклаве (транзит через ЛТ/паром), срок до 31.07.2027. NaF-пробирка: дистрибьюторская цена 10,93 &gt; НМЦК 9,90 — убыточна без завод</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N24"/>
+  <autoFilter ref="A1:P36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1931,7 +2934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1939,22 +2942,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Лотов</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>«Участвовать»</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Прибыль по «Участвовать», ₽</t>
         </is>
@@ -1979,16 +2982,48 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>556474.3205479452</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Кабель (ЭОМ)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>68554.01568482628</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Одежда</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>7525368.13277052</v>
       </c>
     </row>

--- a/TENDERS_1210.xlsx
+++ b/TENDERS_1210.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$P$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2585,272 +2585,232 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>СС</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0855200000526003358</t>
+          <t>32616449701</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ГБУЗ «Каменская ЦРБ им. Г.М. Савельевой»; организатор ГКУ ПО «Управление по осуществлению закупок Пензенской обл.»</t>
+          <t>НАО «Центр «Омега» (Краснодарский край)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные (цитрат/K3/активатор)</t>
+          <t>Видеонаблюдение (СС, поставка)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15.10.2026 08:00 МСК</t>
+          <t>16.10.2026 10:00 МСК</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1432800</v>
+        <v>3229618.2</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с цитратом натрия 3,8%, 4–: 15 600 шт × 10.80; Пробирка вакуумная K3ЭДТА 3–? мл 13х75 (КТРУ : 50 400 шт × 10.80; Пробирка вакуумная с активатором свертывания : 60 000 шт × 12</t>
+          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Видеокамера тип 1 (26.40.33.111): 20 шт × ?; Видеокамера тип 2: 30 шт × ?; Видеокамера тип 3: 30 шт × ?; Видеокамера тип 4: 20 шт × ?; Аппаратура коммуникационная передающая (26.30: 1 шт × ?; Панели/комплекты электр. аппаратуры (27.12.31: 2 шт × ?; Приборы для телекоммуникаций (26.51.44, тесте: 1 шт × ?; … ещё 2 (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11.37142857142857</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>1171120</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>0.1826353992183138</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>103594.3298630137</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>-233458.7178082192</v>
-      </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>23923.09777777778</v>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
+          <t>Поставка (АЭФ только СМП), РТС-тендер Id=4056547. Монтаж в предмете не указан, но проверить проект договора. unit_nmck неизвестны → covered_nmck приравнен nmck условно, маржа по гипотезам ненадёжна. Нужна ручная выгрузка Обоснования НМЦД.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>СС</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0809500000326003912</t>
+          <t>32616433554</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ГБУЗ РМ «Республиканская клиническая больница им. С.В. Каткова»; организатор ГКУ РМ «Региональный центр организации закупок»</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА</t>
+          <t>Видеонаблюдение (СС, поставка)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>16.10.2026 09:00 МСК</t>
+          <t>14.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>950000</v>
+        <v>1675767</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная K3ЭДТА 2–? мл 13х75, пласт: 95 000 шт × 10</t>
+          <t>Видеокамера (26.40.33.111): 41 шт × ?; Части/принадлежности видеооборудования (кронш: 41 шт × ?; Части/принадлежности видеооборудования (короб: 41 шт × ?; Видеорегистратор: 2 шт × ?; Базовые системы хранения данных (HDD?): 16 шт × ? (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>852400</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>0.1027368421052632</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>-3413.698630136991</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>-239013.698630137</v>
-      </c>
-      <c r="O33" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>11884.87234042553</v>
+      </c>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
+          <t>АЭФ только СМП, РТС-тендер Id=4052238. Поставка, монтаж не указан. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>СС</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0164200001926003491</t>
+          <t>32616419880</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, Тамбовская КЦРБ, онкодиспансер, Петровская, Мичуринская ЦРБ, ТОДКБ и др.)</t>
+          <t>ФГБУ «ФЦТОЭ» Минздрава России (г. Чебоксары)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА</t>
+          <t>Видеонаблюдение (СС, поставка)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>19.10.2026 07:00 МСК</t>
+          <t>15.10.2026 14:00 МСК</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1691688</v>
+        <v>878563.71</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с K3ЭДТА, пластик, 2–2,7 м: 35 000 шт × 9.24; То же, поз.2: 54 500 шт × 9.58; То же, поз.3: 25 000 шт × 9.93; То же, поз.4: 10 000 шт × 10.32; То же, поз.5: 2 400 шт × 10.72; То же, поз.6: 50 000 шт × 9.38</t>
+          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Камера видеонаблюдения (26.70.13.000): 16 шт × ?; Коммутатор (26.30.11.110): 3 шт × ? (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9.56296212549463</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>1587948</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>0.06132336459205243</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>10112.2218739726</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>-407641.8923835617</v>
-      </c>
-      <c r="O34" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>43928.1855</v>
+      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
+          <t>Документация (.docx) недоступна. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>СС</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0164200001926003492</t>
+          <t>32616439096</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, ТОДКБ, Тамбовская КЦРБ, онкодиспансер, Петровская, Уметская, Бондарская ЦРБ и др.); организатор — уполномоченный орган Тамбовской обл.</t>
+          <t>СПб ГБУК «Михайловский театр»</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные с активатором свёртывания</t>
+          <t>Телеком-оборудование и расходники (СКС, низкий приоритет)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19.10.2026 07:00 МСК</t>
+          <t>13.10.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2815055</v>
+        <v>987824.58</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с активатором свертывания,: 60 000 шт × 9.89; То же, поз.2: 115 900 шт × 10.15; То же, поз.3: 20 000 шт × 10.31; То же, поз.4: 36 000 шт × 10.92; То же, поз.5: 45 000 шт × 9.91</t>
+          <t>ITK оптический пигтейл: 240 шт/м × ?; Кабель оптический: 900 шт/м × ?; Кросс оптический: 10 шт/м × ?; Шкаф телеком. тип 1: 1 шт/м × ?; Шкаф телеком. тип 2: 2 шт/м × ?; Патч-корды типы 1–5: 160 шт/м × ?; Лоток глухой ЛМГ: 10 шт/м × ?; Кабель-канал типы 1–2: 44 шт/м × ?; … ещё 13 (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10.16632358252077</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>2484948</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>0.1172648491770143</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>157285.0023013699</v>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>-513092.4608219178</v>
-      </c>
-      <c r="O35" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>528.2484385026738</v>
+      </c>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
+          <t>Пропущено: низкий приоритет, срок истекает, не профиль видеонаблюдения. Себестоимость не оценивалась.</t>
         </is>
       </c>
     </row>
@@ -2862,17 +2822,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0335200014926003799</t>
+          <t>0855200000526003358</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Совместная закупка 26 ГБУЗ Калининградской обл.; организатор ГКУ КО «Центр обеспечения организации и проведения торгов»</t>
+          <t>ГБУЗ «Каменская ЦРБ им. Г.М. Савельевой»; организатор ГКУ ПО «Управление по осуществлению закупок Пензенской обл.»</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные (совместная закупка, гель/NaF)</t>
+          <t>Пробирки вакуумные (цитрат/K3/активатор)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2882,48 +2842,390 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00 МСК</t>
+          <t>15.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5909000</v>
+        <v>1432800</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с активатором свертывания/: 94 122 шт × 12.29; Пробирка вакуумная с K-оксалатом и NaF 4 мл 1: 94 122 шт × 9.90; Пробирка вакуумная с активатором/гелем 5 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 6 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 5,5 мл: 94 122 шт × 13.53</t>
+          <t>Пробирка вакуумная с цитратом натрия 3,8%, 4–: 15 600 шт × 10.80; Пробирка вакуумная K3ЭДТА 3–? мл 13х75 (КТРУ : 50 400 шт × 10.80; Пробирка вакуумная с активатором свертывания : 60 000 шт × 12</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12.55604428295191</v>
+        <v>11.37142857142857</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5187766.56</v>
+        <v>1171120</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.1220567676425792</v>
+        <v>0.1826353992183138</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>0.25</v>
       </c>
       <c r="M36" s="2" t="n">
+        <v>103594.3298630137</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>-233458.7178082192</v>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0809500000326003912</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ГБУЗ РМ «Республиканская клиническая больница им. С.В. Каткова»; организатор ГКУ РМ «Региональный центр организации закупок»</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>16.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>950000</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная K3ЭДТА 2–? мл 13х75, пласт: 95 000 шт × 10</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>852400</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0.1027368421052632</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-3413.698630136991</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>-239013.698630137</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0171100002826000003</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Управление Минюста России по Ярославской области</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение (СС, поставка)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>15.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>588408.7</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Камера видеонаблюдения КТРУ 26.70.13.000-0000: 21 шт × 6 059.67; Коммутатор: 2 шт × 10 851; Трансивер: 1 шт × 2 185.67; Трансивер: 1 шт × 2 184; Источник бесперебойного питания (1): 1 шт × 15 589; Источник бесперебойного питания (2): 1 шт × 21 507; Блок розеток: 2 шт × 1 356.67; Шкаф телекоммуникационный: 2 шт × 15 799.67; … ещё 9</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>745107.8</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>-0.2663099644855695</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-193660.3510794521</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>-336667.2015274521</v>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0164200001926003491</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, Тамбовская КЦРБ, онкодиспансер, Петровская, Мичуринская ЦРБ, ТОДКБ и др.)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1691688</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с K3ЭДТА, пластик, 2–2,7 м: 35 000 шт × 9.24; То же, поз.2: 54 500 шт × 9.58; То же, поз.3: 25 000 шт × 9.93; То же, поз.4: 10 000 шт × 10.32; То же, поз.5: 2 400 шт × 10.72; То же, поз.6: 50 000 шт × 9.38</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>9.56296212549463</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1587948</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0.06132336459205243</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>10112.2218739726</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>-407641.8923835617</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0164200001926003492</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, ТОДКБ, Тамбовская КЦРБ, онкодиспансер, Петровская, Уметская, Бондарская ЦРБ и др.); организатор — уполномоченный орган Тамбовской обл.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные с активатором свёртывания</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>2815055</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания,: 60 000 шт × 9.89; То же, поз.2: 115 900 шт × 10.15; То же, поз.3: 20 000 шт × 10.31; То же, поз.4: 36 000 шт × 10.92; То же, поз.5: 45 000 шт × 9.91</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>10.16632358252077</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>2484948</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0.1172648491770143</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>157285.0023013699</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>-513092.4608219178</v>
+      </c>
+      <c r="O40" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0335200014926003799</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Совместная закупка 26 ГБУЗ Калининградской обл.; организатор ГКУ КО «Центр обеспечения организации и проведения торгов»</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные (совместная закупка, гель/NaF)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>26.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>5909000</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания/: 94 122 шт × 12.29; Пробирка вакуумная с K-оксалатом и NaF 4 мл 1: 94 122 шт × 9.90; Пробирка вакуумная с активатором/гелем 5 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 6 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 5,5 мл: 94 122 шт × 13.53</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>12.55604428295191</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>5187766.56</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0.1220567676425792</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>89623.21567123328</v>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="N41" s="2" t="n">
         <v>-1359992.922739726</v>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O41" s="8" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК поделена поровну по позициям (НМЦК/Σцен ед.). 26 отдельных контрактов, ~26 точек доставки в эксклаве (транзит через ЛТ/паром), срок до 31.07.2027. NaF-пробирка: дистрибьюторская цена 10,93 &gt; НМЦК 9,90 — убыточна без завод</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P36"/>
+  <autoFilter ref="A1:P41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2934,7 +3236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3027,6 +3329,22 @@
         <v>7525368.13277052</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TENDERS_1210.xlsx
+++ b/TENDERS_1210.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тендеры 12.10" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Коммерческие без НМЦК" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$P$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$P$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Коммерческие без НМЦК'!$A$1:$H$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -841,22 +843,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Сантехника и ЖКХ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32616447145</t>
+          <t>32616442935</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>АО «Пассажирречтранс»</t>
+          <t>ПАО «Т Плюс», филиал «Нижегородский»</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Запорная арматура стальная (ТЭЦ)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -866,34 +868,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.10.2026 05:00 МСК (09:00 местн.)</t>
+          <t>16.10.2026 14:00 МСК</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>450798.91</v>
+        <v>1883587.49</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Кабель судовой КНР и КНРЭ (ГОСТ 7866.1-76), с: 1 730 м × 260.58</t>
+          <t>Вентиль ВТ-5 Ду10 Ру250: 10 шт × ?; Вентиль ВИГ-250Д-Н1Б1Г Ду5 Ру250: 10 шт × ?; Вентиль ВИГ-6С-Н1Б1Б Ду5 Ру6: 5 шт × ?; Клапан запорный 15с27нж Ду25: 5 шт × ?; Клапан обратный 19лс53нж Ду100 Ру16: 1 шт × ?; Клапан обратный 19ч16бр Ду100 Ру16: 6 шт × ?; Клапан 15с22нж Ду50 с КОФ: 8 шт × ?; Вентиль 14с17п30-1 Ду50 Ру10: 4 шт × ?; … ещё 11 (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>260.5774046242774</v>
+        <v>14831.39755905512</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>281420</v>
+        <v>1273942</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3757305225072527</v>
+        <v>0.3236618915960203</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>136974.4710489863</v>
+        <v>478689.8433488219</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>68554.01568482628</v>
+        <v>256336.1073293019</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -902,147 +904,143 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
+          <t xml:space="preserve">Цены по позициям в извещении не указаны: НМЦ лота задана одной суммой, документация (zip) на zakupki.gov.ru, доступа к ней нет, поэтому unit_nmck не указаны. У Т Плюс НМЦ часто указана без НДС — проверить; для УСН это важно. Около половины позиций (энергетические вентили ВТ-5, ВИГ, 15с27нж, 14с17п, </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Сантехника и ЖКХ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0372100027326000601</t>
+          <t>32616450774</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение «Администрация Волго-Балтийского бассейна внутренних водных путей»</t>
+          <t>МУП «Уфимские инженерные сети» ГО г. Уфа</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Поставка средств индивидуальной защиты, приобретаемых для нужд ФБУ «Администрация «Волго-Балт» (44-ФЗ)</t>
+          <t>Изделия в ППУ изоляции</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-13 10:00</t>
+          <t>20.10.2026 12:00 МСК</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>18033874.9</v>
+        <v>639848.52</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Костюм для защиты от термических рисков элект: 1 КОМПЛ × 4 865.60; Строп одинарный регулируемый огнеупорный: 4 шт × 2 379.09; Каска защитная белая: 31 шт × 551.06; Гибкая анкерная линия (20 м): 2 шт × 2 765.56; Наколенники: 15 пар × 871.08; Белье нательное термостойкое: 192 КОМПЛ × 1 741.12; Одежда специальная повышенной видимости: 18 шт × 142.69; Обувь специальная кожаная для защиты от механ: 72 пар × 2 125.85; … ещё 126</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
+          <t>Отвод Ст 108х4,5-90-1-ППУ-ПЭ: 3 шт × ?; Отвод Ст 377х8-90-1-ППУ-ПЭ: 2 шт × ?; Отвод Ст 426х8-90-1-ППУ-ПЭ: 3 шт × ?; Отвод Ст 530х9,0-90-1-ППУ-ПЭ: 1 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>71094.28</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13525406.175</v>
+        <v>373458.9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4163323219064412</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2571289.646392574</v>
+        <v>216862.0142146849</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2571289.646392574</v>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>189886.000611485</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Цены по позициям не указаны в извещении; длины плеч, диаметр оболочки и наличие проводников ОДК — в документах (недоступны). Тяжёлый груз (426/530 — по 200–300 кг), доставка в Уфу — оценка 45 тыс. Уфимские производители ППУ (например, местные заводы) имеют логистическое преимущество. Не СМП-закупка.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0358200022926000030</t>
+          <t>32616447145</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ГКУ Ростовской обл. «Ростовская областная поисково-спасательная служба»</t>
+          <t>АО «Пассажирречтранс»</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Поставка обмундирования</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00</t>
+          <t>16.10.2026 05:00 МСК (09:00 местн.)</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6224420.7</v>
+        <v>450798.91</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Костюм спасателя зимний (куртка, брюки утепле: 168 КОМПЛ × 7 698.83; Костюм спасателя летний (куртка, брюки, кепка: 241 КОМПЛ × 6 613.44; Комбинезон спасателя зимний, шт.: 208 шт × 7 565.57; Комбинезон спасателя летний, шт.: 239 шт × 6 542.14; Футболка форменная, шт.: 268 шт × 746.15</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
+          <t>Кабель судовой КНР и КНРЭ (ГОСТ 7866.1-76), с: 1 730 м × 260.58</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>260.5774046242774</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4668315.525</v>
+        <v>281420</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.25</v>
+        <v>0.3757305225072527</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>887484.7246889586</v>
+        <v>136974.4710489863</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>887484.7246889586</v>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>68554.01568482628</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
         </is>
       </c>
     </row>
@@ -1054,42 +1052,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32616443256</t>
+          <t>0372100027326000601</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ГБУ Республики Саха (Якутия) «Государственная Противопожарная Служба Республики Саха(Якутия)»</t>
+          <t>Федеральное бюджетное учреждение «Администрация Волго-Балтийского бассейна внутренних водных путей»</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Поставка форменной одежды для нужд ГБУ РС(Я) "ГПС РС(Я)"</t>
+          <t>Поставка средств индивидуальной защиты, приобретаемых для нужд ФБУ «Администрация «Волго-Балт» (44-ФЗ)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00</t>
+          <t>2026-10-13 10:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4999001.85</v>
+        <v>18033874.9</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Костюм летний полевой: 405 Комплект × ?; Зимняя форменная одежда мужская: 150 Комплект × ? (цена за ед. = НМЦК / кол-во)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>9007.21054054054</v>
+          <t>Костюм для защиты от термических рисков элект: 1 КОМПЛ × 4 865.60; Строп одинарный регулируемый огнеупорный: 4 шт × 2 379.09; Каска защитная белая: 31 шт × 551.06; Гибкая анкерная линия (20 м): 2 шт × 2 765.56; Наколенники: 15 пар × 871.08; Белье нательное термостойкое: 192 КОМПЛ × 1 741.12; Одежда специальная повышенной видимости: 18 шт × 142.69; Обувь специальная кожаная для защиты от механ: 72 пар × 2 125.85; … ещё 126</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3749251.3875</v>
+        <v>13525406.175</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.25</v>
@@ -1098,10 +1098,10 @@
         <v>0.05</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>712763.1621311915</v>
+        <v>2571289.646392574</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>712763.1621311915</v>
+        <v>2571289.646392574</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -1122,42 +1122,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32616438570</t>
+          <t>0358200022926000030</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ООО «Теплоэнергетическая Компания - 2»</t>
+          <t>ГКУ Ростовской обл. «Ростовская областная поисково-спасательная служба»</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Поставка зимней спецодежды</t>
+          <t>Поставка обмундирования</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00</t>
+          <t>2026-10-19 09:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4810413.58</v>
+        <v>6224420.7</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; Костюм сварщика со спилком утепленный: 20 Штука × ?; Костюм женский утепленный: 41 Штука × ?; Костюм зимний мужской для защиты от термическ: 28 Штука × ?; Куртка охранника зимняя: 46 Штука × ?; Брюки охранника зимние: 46 Штука × ?; Шеврон на липучке для спецодежды: 46 Штука × ?; Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; … ещё 6 (цена за ед. = НМЦК / кол-во)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>3891.920372168285</v>
+          <t>Костюм спасателя зимний (куртка, брюки утепле: 168 КОМПЛ × 7 698.83; Костюм спасателя летний (куртка, брюки, кепка: 241 КОМПЛ × 6 613.44; Комбинезон спасателя зимний, шт.: 208 шт × 7 565.57; Комбинезон спасателя летний, шт.: 239 шт × 6 542.14; Футболка форменная, шт.: 268 шт × 746.15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3607810.185</v>
+        <v>4668315.525</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.25</v>
@@ -1166,10 +1168,10 @@
         <v>0.05</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>685874.0399225147</v>
+        <v>887484.7246889586</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>685874.0399225147</v>
+        <v>887484.7246889586</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -1190,40 +1192,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ГП622514</t>
+          <t>32616443256</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>АО «Арго»</t>
+          <t>ГБУ Республики Саха (Якутия) «Государственная Противопожарная Служба Республики Саха(Якутия)»</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Закупка спецодежды, обуви и средств индивидуальной защиты</t>
+          <t>Поставка форменной одежды для нужд ГБУ РС(Я) "ГПС РС(Я)"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Коммерческие</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00</t>
+          <t>2026-10-15 05:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4000000</v>
+        <v>4999001.85</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t>Костюм летний полевой: 405 Комплект × ?; Зимняя форменная одежда мужская: 150 Комплект × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>9007.21054054054</v>
+      </c>
       <c r="J11" s="2" t="n">
-        <v>3000000</v>
+        <v>3749251.3875</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0.25</v>
@@ -1232,10 +1236,10 @@
         <v>0.05</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>570324.3835616438</v>
+        <v>712763.1621311915</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>570324.3835616438</v>
+        <v>712763.1621311915</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -1256,17 +1260,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32616402062</t>
+          <t>32616438570</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>МУП «Управление Городского Хозяйства» Муниципального Образования Города Пыть-Ях</t>
+          <t>ООО «Теплоэнергетическая Компания - 2»</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Поставка специальных обуви, одежды, головных уборов, рукавиц и краг</t>
+          <t>Поставка зимней спецодежды</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1276,24 +1280,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-13 06:00</t>
+          <t>2026-10-14 08:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3857857.45</v>
+        <v>4810413.58</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Ботинки кожаные утепленные: 46 Пара (2 шт.) × ?; Сапоги кожаные утепленные: 185 Пара (2 шт.) × ?; Сапоги утепленные "Надым" ТХ-011р/п с КП и АС: 21 Пара (2 шт.) × ?; Валенки с резиновым низом: 40 Пара (2 шт.) × ?; Костюм сварщика утепленный (4 класс защиты): 8 Штука × ?; Костюм от пониженных температур (4 класс защи: 115 Штука × ?; Костюм сигнальный с водоотталкивающей пропитк: 41 Штука × ?; Костюм зимний петролеум плюс куртка-П/К, Т.Си: 21 Штука × ?; … ещё 18</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
+          <t>Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; Костюм сварщика со спилком утепленный: 20 Штука × ?; Костюм женский утепленный: 41 Штука × ?; Костюм зимний мужской для защиты от термическ: 28 Штука × ?; Куртка охранника зимняя: 46 Штука × ?; Брюки охранника зимние: 46 Штука × ?; Шеврон на липучке для спецодежды: 46 Штука × ?; Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; … ещё 6 (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3891.920372168285</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2893393.0875</v>
+        <v>3607810.185</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.25</v>
@@ -1302,10 +1304,10 @@
         <v>0.05</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>550057.5430099862</v>
+        <v>685874.0399225147</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>550057.5430099862</v>
+        <v>685874.0399225147</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -1326,44 +1328,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32616431081</t>
+          <t>ГП622514</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
+          <t>АО «Арго»</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Поставка спецодежды</t>
+          <t>Закупка спецодежды, обуви и средств индивидуальной защиты</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Коммерческие</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00</t>
+          <t>2026-10-15 17:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3637476.36</v>
+        <v>4000000</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Жилет сигнальный: 14 Штука × ?; Жилет утепленный: 64 Штука × ?; Костюм летний  мужской противоэнцэфалитный: 1 Комплект × ?; Костюм летний мужской для защиты от механичес: 23 Комплект × ?; Костюм летний женский для защиты от механичес: 1 Комплект × ?; Куртка зимняя мужской для защиты от механичес: 20 Штука × ?; Полукомбинезон зимний мужской для защиты от м: 20 Штука × ?; Костюм летний мужской сигнальный флуоресцентн: 4 Комплект × ?; … ещё 28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
-      </c>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n">
-        <v>2728107.27</v>
+        <v>3000000</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.25</v>
@@ -1372,10 +1370,10 @@
         <v>0.05</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>518635.365684263</v>
+        <v>570324.3835616438</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>518635.365684263</v>
+        <v>570324.3835616438</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -1396,17 +1394,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32616448893</t>
+          <t>32616402062</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Московской обл. «Мособллес»</t>
+          <t>МУП «Управление Городского Хозяйства» Муниципального Образования Города Пыть-Ях</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Поставка обуви специальной для защиты от механических воздействий</t>
+          <t>Поставка специальных обуви, одежды, головных уборов, рукавиц и краг</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1416,22 +1414,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00</t>
+          <t>2026-10-13 06:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2511958.68</v>
+        <v>3857857.45</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ?; Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ? (цена за ед. = НМЦК / кол-во)</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>3171.665</v>
+          <t>Ботинки кожаные утепленные: 46 Пара (2 шт.) × ?; Сапоги кожаные утепленные: 185 Пара (2 шт.) × ?; Сапоги утепленные "Надым" ТХ-011р/п с КП и АС: 21 Пара (2 шт.) × ?; Валенки с резиновым низом: 40 Пара (2 шт.) × ?; Костюм сварщика утепленный (4 класс защиты): 8 Штука × ?; Костюм от пониженных температур (4 класс защи: 115 Штука × ?; Костюм сигнальный с водоотталкивающей пропитк: 41 Штука × ?; Костюм зимний петролеум плюс куртка-П/К, Т.Си: 21 Штука × ?; … ещё 18</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1883969.01</v>
+        <v>2893393.0875</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.25</v>
@@ -1440,10 +1440,10 @@
         <v>0.05</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>358157.8214258302</v>
+        <v>550057.5430099862</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>358157.8214258302</v>
+        <v>550057.5430099862</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32616427138</t>
+          <t>32616431081</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Поставка спецодежды для защиты от термических рисков электрической дуги</t>
+          <t>Поставка спецодежды</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1484,15 +1484,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00</t>
+          <t>2026-10-19 08:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1477969</v>
+        <v>3637476.36</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Костюм летний для защиты от термических риско: 15 Комплект × ?; Костюм зимний для защиты от термических риско: 8 Комплект × ?; Куртка-рубашка для защиты от термических риск: 11 Штука × ?; Куртка-накидка для защиты от термических риск: 10 Штука × ?; Плащ термостойкий для защиты от термических р: 1 Штука × ?; Бельё нательное (фуфайка): 26 Штука × ?; Бельё нательное (кальсоны): 26 Штука × ?; Бельё нательное утепленное (фуфайка): 12 Штука × ?; … ещё 12</t>
+          <t>Жилет сигнальный: 14 Штука × ?; Жилет утепленный: 64 Штука × ?; Костюм летний  мужской противоэнцэфалитный: 1 Комплект × ?; Костюм летний мужской для защиты от механичес: 23 Комплект × ?; Костюм летний женский для защиты от механичес: 1 Комплект × ?; Куртка зимняя мужской для защиты от механичес: 20 Штука × ?; Полукомбинезон зимний мужской для защиты от м: 20 Штука × ?; Костюм летний мужской сигнальный флуоресцентн: 4 Комплект × ?; … ещё 28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1108476.75</v>
+        <v>2728107.27</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>0.25</v>
@@ -1510,10 +1510,10 @@
         <v>0.05</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>210730.4397120549</v>
+        <v>518635.365684263</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>210730.4397120549</v>
+        <v>518635.365684263</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
@@ -1534,40 +1534,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10749746</t>
+          <t>32616448893</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Боханский Аграрный Техникум»</t>
+          <t>Государственное автономное учреждение Московской обл. «Мособллес»</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря, индивидуальная одежда и обувь для каждого студента. согласно спецификации и списка размеров.</t>
+          <t>Поставка обуви специальной для защиты от механических воздействий</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00</t>
+          <t>2026-10-16 10:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>498000</v>
+        <v>2511958.68</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
+          <t>Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ?; Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>3171.665</v>
+      </c>
       <c r="J16" s="2" t="n">
-        <v>373500</v>
+        <v>1883969.01</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0.25</v>
@@ -1576,10 +1578,10 @@
         <v>0.05</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>71005.38575342466</v>
+        <v>358157.8214258302</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>71005.38575342466</v>
+        <v>358157.8214258302</v>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
@@ -1600,42 +1602,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0173200001426002006</t>
+          <t>32616427138</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Московская Административная Дорожная Инспекция</t>
+          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Поставка форменной одежды</t>
+          <t>Поставка спецодежды для защиты от термических рисков электрической дуги</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-15 08:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>435666.4</v>
+        <v>1477969</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Термобелье спортивное, для взрослого: 2 шт × 6 100; Шорты: 2 шт × 4 266.67; Термобелье спортивное, для взрослого: 4 шт × 5 033.33; Футболка трикотажная: 2 шт × 1 033.33; Футболка трикотажная: 8 шт × 1 033.33; Шорты: 4 шт × 4 266.67; Шорты: 6 шт × 4 266.67; Шорты: 6 шт × 4 266.67; … ещё 29</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>2562.743529411765</v>
+          <t>Костюм летний для защиты от термических риско: 15 Комплект × ?; Костюм зимний для защиты от термических риско: 8 Комплект × ?; Куртка-рубашка для защиты от термических риск: 11 Штука × ?; Куртка-накидка для защиты от термических риск: 10 Штука × ?; Плащ термостойкий для защиты от термических р: 1 Штука × ?; Бельё нательное (фуфайка): 26 Штука × ?; Бельё нательное (кальсоны): 26 Штука × ?; Бельё нательное утепленное (фуфайка): 12 Штука × ?; … ещё 12</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>326749.8</v>
+        <v>1108476.75</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>0.25</v>
@@ -1644,10 +1648,10 @@
         <v>0.05</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>62117.79275463011</v>
+        <v>210730.4397120549</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>62117.79275463011</v>
+        <v>210730.4397120549</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
@@ -1668,17 +1672,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10747873</t>
+          <t>10749746</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Боханский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
+          <t>Приобретение мягкого инвентаря, индивидуальная одежда и обувь для каждого студента. согласно спецификации и списка размеров.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1688,11 +1692,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-14 11:20</t>
+          <t>2026-10-14 10:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>402140</v>
+        <v>498000</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1701,7 +1705,7 @@
       </c>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n">
-        <v>301605</v>
+        <v>373500</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.25</v>
@@ -1710,10 +1714,10 @@
         <v>0.05</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>57337.56190136987</v>
+        <v>71005.38575342466</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>57337.56190136987</v>
+        <v>71005.38575342466</v>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
@@ -1734,40 +1738,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10747880</t>
+          <t>0173200001426002006</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
+          <t>Московская Административная Дорожная Инспекция</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
+          <t>Поставка форменной одежды</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-14 11:20</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>402140</v>
+        <v>435666.4</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
+          <t>Термобелье спортивное, для взрослого: 2 шт × 6 100; Шорты: 2 шт × 4 266.67; Термобелье спортивное, для взрослого: 4 шт × 5 033.33; Футболка трикотажная: 2 шт × 1 033.33; Футболка трикотажная: 8 шт × 1 033.33; Шорты: 4 шт × 4 266.67; Шорты: 6 шт × 4 266.67; Шорты: 6 шт × 4 266.67; … ещё 29</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>2562.743529411765</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>301605</v>
+        <v>326749.8</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.25</v>
@@ -1776,10 +1782,10 @@
         <v>0.05</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>57337.56190136987</v>
+        <v>62117.79275463011</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>57337.56190136987</v>
+        <v>62117.79275463011</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
@@ -1800,44 +1806,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0358300160926000018</t>
+          <t>10747873</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>МКУ «Управление по Делам Гражданской Обороны, Предупреждения и Ликвидации Чрезвычайных Ситуаций Города Каменск-Шахтинский»</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Поставка специальной одежды</t>
+          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-14 11:20</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>320700.06</v>
+        <v>402140</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Ботинки с высокими берцами зимние: 18 пар × 5 400; Футболка поло с длинным рукавом: 18 шт × 2 800; Головной убор зимний: 18 шт × 750; Костюм спасателя мужской зимний: 18 шт × 8 866.67</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
-      </c>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n">
-        <v>240525.045</v>
+        <v>301605</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0.25</v>
@@ -1846,10 +1848,10 @@
         <v>0.05</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>45725.76600692053</v>
+        <v>57337.56190136987</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>45725.76600692053</v>
+        <v>57337.56190136987</v>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
@@ -1870,42 +1872,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0301300019426000247</t>
+          <t>10747880</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ГБУЗ Республиканский Клинический Госпиталь Ветеранов Войн им. М.В. Каменева</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Поставка спецодежды</t>
+          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00</t>
+          <t>2026-10-14 11:20</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>270651</v>
+        <v>402140</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Костюм мужской рабочий  (96/170): 1 шт × 4 857; Костюм мужской рабочий  (104/165): 1 шт × 4 857; Костюм мужской рабочий  (104/176): 2 шт × 4 857; Костюм мужской рабочий  (108/170): 3 шт × 4 857; Костюм мужской рабочий  (108/176): 3 шт × 4 857; Костюм мужской рабочий  (112/170): 2 шт × 4 857; Костюм мужской рабочий  (112/176): 1 шт × 4 857; Костюм мужской рабочий  (96/158): 1 шт × 5 600; … ещё 29</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>5012.055555555556</v>
-      </c>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n">
-        <v>202988.25</v>
+        <v>301605</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>0.25</v>
@@ -1914,10 +1914,10 @@
         <v>0.05</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>38589.7161838356</v>
+        <v>57337.56190136987</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>38589.7161838356</v>
+        <v>57337.56190136987</v>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0302200020326000023</t>
+          <t>0358300160926000018</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Республиканская служба по охране, контролю и регулированию использования объектов животного мира, отнесенных к объектам охоты, контролю и надзору в сфере природопользования</t>
+          <t>МКУ «Управление по Делам Гражданской Обороны, Предупреждения и Ликвидации Чрезвычайных Ситуаций Города Каменск-Шахтинский»</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Поставка спецобуви</t>
+          <t>Поставка специальной одежды</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1958,22 +1958,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-14 04:00</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>230181</v>
+        <v>320700.06</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Ботинки специальные с высокими берцами зимние: 18 пар × 3 639; Ботинки специальные с высокими берцами: 17 пар × 8 299; Обувь демисезонная: 4 пар × 5 899</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>5902.076923076923</v>
+          <t>Ботинки с высокими берцами зимние: 18 пар × 5 400; Футболка поло с длинным рукавом: 18 шт × 2 800; Головной убор зимний: 18 шт × 750; Костюм спасателя мужской зимний: 18 шт × 8 866.67</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>172635.75</v>
+        <v>240525.045</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.25</v>
@@ -1982,10 +1984,10 @@
         <v>0.05</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>32819.45923315067</v>
+        <v>45725.76600692053</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>32819.45923315067</v>
+        <v>45725.76600692053</v>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
@@ -2006,17 +2008,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0340100009726000070</t>
+          <t>0301300019426000247</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Федеральное государственное бюджетное Профессиональное Образовательное учреждение «Орловское Специальное Учебно-Воспитательное Учреждение Закрытого Типа»</t>
+          <t>ГБУЗ Республиканский Клинический Госпиталь Ветеранов Войн им. М.В. Каменева</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Поставка зимней одежды для воспитанников (термобелье)</t>
+          <t>Поставка спецодежды</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2026,22 +2028,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15 08:30</t>
+          <t>2026-10-15 07:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>213567.9</v>
+        <v>270651</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 4 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 3 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; … ещё 29</t>
+          <t>Костюм мужской рабочий  (96/170): 1 шт × 4 857; Костюм мужской рабочий  (104/165): 1 шт × 4 857; Костюм мужской рабочий  (104/176): 2 шт × 4 857; Костюм мужской рабочий  (108/170): 3 шт × 4 857; Костюм мужской рабочий  (108/176): 3 шт × 4 857; Костюм мужской рабочий  (112/170): 2 шт × 4 857; Костюм мужской рабочий  (112/176): 1 шт × 4 857; Костюм мужской рабочий  (96/158): 1 шт × 5 600; … ещё 29</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2033.98</v>
+        <v>5012.055555555556</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>160175.925</v>
+        <v>202988.25</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>0.25</v>
@@ -2050,10 +2052,10 @@
         <v>0.05</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>30450.74522901369</v>
+        <v>38589.7161838356</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>30450.74522901369</v>
+        <v>38589.7161838356</v>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
@@ -2074,44 +2076,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32616452815</t>
+          <t>0302200020326000023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Здравоохранения «Городская Больница № 2 г. Магнитогорск»</t>
+          <t>Республиканская служба по охране, контролю и регулированию использования объектов животного мира, отнесенных к объектам охоты, контролю и надзору в сфере природопользования</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Поставка комплектов зимней спецодежды и рукавиц</t>
+          <t>Поставка спецобуви</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00</t>
+          <t>2026-10-14 04:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>187355.52</v>
+        <v>230181</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Костюм утепленный Ангара: 16 Комплект × ?; Рукавицы утепленные G14: 16 Пара (2 шт.) × ?</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
+          <t>Ботинки специальные с высокими берцами зимние: 18 пар × 3 639; Ботинки специальные с высокими берцами: 17 пар × 8 299; Обувь демисезонная: 4 пар × 5 899</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>5902.076923076923</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>140516.64</v>
+        <v>172635.75</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.25</v>
@@ -2120,10 +2120,10 @@
         <v>0.05</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>26713.3553627178</v>
+        <v>32819.45923315067</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>26713.3553627178</v>
+        <v>32819.45923315067</v>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
@@ -2144,40 +2144,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>295997-26LO</t>
+          <t>0340100009726000070</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>МКУ «Городское Хозяйство» Муниципального Образования Волосовское Городское Поселение Волосовского Муниципального Района Ленинградской Области</t>
+          <t>Федеральное государственное бюджетное Профессиональное Образовательное учреждение «Орловское Специальное Учебно-Воспитательное Учреждение Закрытого Типа»</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Поставка товаров согласно Спецификации (Специальная одежда и обувь)</t>
+          <t>Поставка зимней одежды для воспитанников (термобелье)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-13 10:30</t>
+          <t>2026-10-15 08:30</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>152190</v>
+        <v>213567.9</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n"/>
+          <t>Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 4 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 3 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; … ещё 29</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>2033.98</v>
+      </c>
       <c r="J25" s="2" t="n">
-        <v>114142.5</v>
+        <v>160175.925</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>0.25</v>
@@ -2186,10 +2188,10 @@
         <v>0.05</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>21699.41698356164</v>
+        <v>30450.74522901369</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>21699.41698356164</v>
+        <v>30450.74522901369</v>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
@@ -2210,40 +2212,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1022079</t>
+          <t>32616452815</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Краевое ГКУ Для Детей-Сирот и Детей, Оставшихся без Попечения Родителей «Шушенский Детский Дом»</t>
+          <t>Государственное автономное учреждение Здравоохранения «Городская Больница № 2 г. Магнитогорск»</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Закупка одежды</t>
+          <t>Поставка комплектов зимней спецодежды и рукавиц</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Коммерческие</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00</t>
+          <t>2026-10-15 07:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>114000</v>
+        <v>187355.52</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t>Костюм утепленный Ангара: 16 Комплект × ?; Рукавицы утепленные G14: 16 Пара (2 шт.) × ?</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="n">
-        <v>85500</v>
+        <v>140516.64</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0.25</v>
@@ -2252,10 +2258,10 @@
         <v>0.05</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>16254.24493150685</v>
+        <v>26713.3553627178</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>16254.24493150685</v>
+        <v>26713.3553627178</v>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
@@ -2271,218 +2277,222 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0348300075526000435</t>
+          <t>295997-26LO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ГБУЗ МО «Королёвская клиническая больница» (ЦКДЛ), лот 7</t>
+          <t>МКУ «Городское Хозяйство» Муниципального Образования Волосовское Городское Поселение Волосовского Муниципального Района Ленинградской Области</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Контейнеры вакуумные для мочи</t>
+          <t>Поставка товаров согласно Спецификации (Специальная одежда и обувь)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>19.10.2026 10:00 МСК</t>
+          <t>2026-10-13 10:30</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1500000</v>
+        <v>152190</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Контейнер вакуумный для мочи 10 мл, 15–16х100: 21 667 шт × 20.64; Контейнер вакуумный для мочи 6,5–7 мл, 13х100: 21 667 шт × 10.66; Контейнер вакуумный для мочи 9–9,5 мл, 16х100: 21 667 шт × 22.70; Контейнер вакуумный для мочи 9,5 мл, 16х100, : 21 667 шт × 15.23</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>17.30742603959939</v>
-      </c>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n">
-        <v>1087916.66</v>
+        <v>114142.5</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2747222266666667</v>
+        <v>0.25</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>279266.7297835617</v>
+        <v>21699.41698356164</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>253970.7297835617</v>
+        <v>21699.41698356164</v>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0387200029826000340</t>
+          <t>1022079</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>БУ ХМАО-Югры «Нижневартовская окружная клиническая больница»</t>
+          <t>Краевое ГКУ Для Детей-Сирот и Детей, Оставшихся без Попечения Родителей «Шушенский Детский Дом»</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные (8 видов)</t>
+          <t>Закупка одежды</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>Коммерческие</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16.10.2026 07:00 МСК</t>
+          <t>2026-10-15 20:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>900000</v>
+        <v>114000</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная K2ЭДТА 2–? мл 13х75, кол-в: 8 154 шт × 12.86; Пробирка вакуумная цитрат 3,8% 3–? мл 13х75, : 8 154 шт × 12.87; Пробирка вакуумная тромбин 4,5 мл 13х75, кол-: 8 154 шт × 12.10; Пробирка вакуумная K-оксалат/NaF 4,5 мл 13х75: 8 154 шт × 14.72; Пробирка вакуумная активатор 5–? мл 13х(90–10: 8 154 шт × 14.67; Пробирка вакуумная цитрат 3,8% 4–? мл 13х75, : 8 154 шт × 12.88; Пробирка вакуумная K2ЭДТА 4–? мл 13х75, кол-в: 8 154 шт × 12.87; Пробирка вакуумная Li-гепарин 4–? мл 13х75, к: 8 154 шт × 17.40</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>13.79690949227373</v>
-      </c>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n">
-        <v>617434.5</v>
+        <v>85500</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3139616666666666</v>
+        <v>0.25</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>190924.8400684932</v>
+        <v>16254.24493150685</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1204.840068493151</v>
+        <v>16254.24493150685</v>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Количество не определено — qty условные (НМЦК/Σцен ед. поровну). Доставка в Нижневартовск (дорогая логистика). Контракт до 31.03.2027.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32616445794</t>
+          <t>0348300075526000435</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Саратовский филиал</t>
+          <t>ГБУЗ МО «Королёвская клиническая больница» (ЦКДЛ), лот 7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Контейнеры вакуумные для мочи</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15.10.2026 12:00 МСК</t>
+          <t>19.10.2026 10:00 МСК</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2176178.2</v>
+        <v>1500000</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>поз.1 ОКПД2 27.32.13.144 Кабели высоковольтны: 100 Метр × ?; поз.2 ОКПД2 27.32.13.111 Кабели силовые с мед: 300 Метр × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 0.07 Километр; тысяча метров × ?; поз.4 ОКПД2 27.32.13.111 Кабели силовые с мед: 120 Метр × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 50 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.22 Километр; тысяча метров × ?; поз.7 ОКПД2 27.32.13.124 Кабели силовые гибки: 1.30 Километр; тысяча метров × ?; поз.8 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; … ещё 10</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+          <t>Контейнер вакуумный для мочи 10 мл, 15–16х100: 21 667 шт × 20.64; Контейнер вакуумный для мочи 6,5–7 мл, 13х100: 21 667 шт × 10.66; Контейнер вакуумный для мочи 9–9,5 мл, 16х100: 21 667 шт × 22.70; Контейнер вакуумный для мочи 9,5 мл, 16х100, : 21 667 шт × 15.23</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>17.30742603959939</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1087916.66</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0.2747222266666667</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>279266.7297835617</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>253970.7297835617</v>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>НМЦ 2 176 178,20 в ЕИС — БЕЗ НДС (rostender показывает 2 654 937 с НДС 22%). Клиент на УСН: уточнить в ДоЗ правило сравнения цен (у РусГидро обычно без НДС). Флаги нацрежима по всем 18 позициям = false (ЕИС), но ПП №1875 для 27.32 может быть указан в ДоЗ — проверить. Цены поставщиков не подобраны: н</t>
+          <t>Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Сантехника и ЖКХ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32616445272</t>
+          <t>32616451568</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Воткинский филиал</t>
+          <t>ПАО «Россети Центр и Приволжье» — филиал «Удмуртэнерго»</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Запорная арматура</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2492,115 +2502,133 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15.10.2026 12:00 МСК</t>
+          <t>19.10.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1201357.95</v>
+        <v>113094</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>поз.1 ОКПД2 27.32.13.159 Кабели, провода и шн: 135 Метр × ?; поз.2 ОКПД2 27.32.13.131 Провода силовые для : 0.10 Километр; тысяча метров × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 100 Метр × ?; поз.4 ОКПД2 27.32.14.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 60 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 115 Метр × ?; поз.7 ОКПД2 27.32.13.111 Кабели силовые с мед: 100 Метр × ?; поз.8 ОКПД2 27.32.13.143 Кабели контрольные (: 0.20 Километр; тысяча метров × ?; … ещё 7</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+          <t>Задвижки (28.14.13.120), характеристики в док: 6 шт × ?; Затворы дисковые (28.14.13.132): 10 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>7068.375</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>84950</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.2488549348329708</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>21966.38819726027</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>7662.259077260269</v>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>НМЦ 1 201 357,95 без НДС (rostender: 1 465 656 с НДС). Флаги нацрежима false. Цены не подобраны — нет марок/сечений.</t>
+          <t>Диаметры и типы неизвестны: ТЗ в rar на zakupki.gov.ru, доступа нет. Запрос котировок для МСП на ЭТП РАД (lot-online). Флаг нацрежима стоит → нужен российский производитель. Малый лот, логистика съедает маржу.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32616445510</t>
+          <t>0387200029826000340</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>АО «НИОПИК»</t>
+          <t>БУ ХМАО-Югры «Нижневартовская окружная клиническая больница»</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Пробирки вакуумные (8 видов)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14.10.2026 10:00 МСК</t>
+          <t>16.10.2026 07:00 МСК</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>529280.65</v>
+        <v>900000</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Кабель сигнальный КИМЭлВ-ЗГнг(А) (ОКПД2 27.32: 1 усл. ед. × 529 280.65</t>
+          <t>Пробирка вакуумная K2ЭДТА 2–? мл 13х75, кол-в: 8 154 шт × 12.86; Пробирка вакуумная цитрат 3,8% 3–? мл 13х75, : 8 154 шт × 12.87; Пробирка вакуумная тромбин 4,5 мл 13х75, кол-: 8 154 шт × 12.10; Пробирка вакуумная K-оксалат/NaF 4,5 мл 13х75: 8 154 шт × 14.72; Пробирка вакуумная активатор 5–? мл 13х(90–10: 8 154 шт × 14.67; Пробирка вакуумная цитрат 3,8% 4–? мл 13х75, : 8 154 шт × 12.88; Пробирка вакуумная K2ЭДТА 4–? мл 13х75, кол-в: 8 154 шт × 12.87; Пробирка вакуумная Li-гепарин 4–? мл 13х75, к: 8 154 шт × 17.40</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>529280.65</v>
-      </c>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+        <v>13.79690949227373</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>617434.5</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0.3139616666666666</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>190924.8400684932</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>1204.840068493151</v>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Цена за метр не определена: неизвестны длина и конструкция. Ориентир по аналогам 1х2х0,75 (КПСнг(А)-FRHF, МКЭШВнг(А)-LS) 30–60 ₽/м с НДС — для КИМ неприменимо без спецификации. ЭТП РТС-тендер.</t>
+          <t>Количество не определено — qty условные (НМЦК/Σцен ед. поровну). Доставка в Нижневартовск (дорогая логистика). Контракт до 31.03.2027.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>32616449701</t>
+          <t>32616445794</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>НАО «Центр «Омега» (Краснодарский край)</t>
+          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Саратовский филиал</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2610,19 +2638,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16.10.2026 10:00 МСК</t>
+          <t>15.10.2026 12:00 МСК</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>3229618.2</v>
+        <v>2176178.2</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Видеокамера тип 1 (26.40.33.111): 20 шт × ?; Видеокамера тип 2: 30 шт × ?; Видеокамера тип 3: 30 шт × ?; Видеокамера тип 4: 20 шт × ?; Аппаратура коммуникационная передающая (26.30: 1 шт × ?; Панели/комплекты электр. аппаратуры (27.12.31: 2 шт × ?; Приборы для телекоммуникаций (26.51.44, тесте: 1 шт × ?; … ещё 2 (цена за ед. = НМЦК / кол-во)</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>23923.09777777778</v>
+          <t>поз.1 ОКПД2 27.32.13.144 Кабели высоковольтны: 100 Метр × ?; поз.2 ОКПД2 27.32.13.111 Кабели силовые с мед: 300 Метр × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 0.07 Километр; тысяча метров × ?; поз.4 ОКПД2 27.32.13.111 Кабели силовые с мед: 120 Метр × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 50 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.22 Километр; тысяча метров × ?; поз.7 ОКПД2 27.32.13.124 Кабели силовые гибки: 1.30 Километр; тысяча метров × ?; поз.8 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; … ещё 10</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
       </c>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="4" t="n"/>
@@ -2636,29 +2666,29 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Поставка (АЭФ только СМП), РТС-тендер Id=4056547. Монтаж в предмете не указан, но проверить проект договора. unit_nmck неизвестны → covered_nmck приравнен nmck условно, маржа по гипотезам ненадёжна. Нужна ручная выгрузка Обоснования НМЦД.</t>
+          <t>НМЦ 2 176 178,20 в ЕИС — БЕЗ НДС (rostender показывает 2 654 937 с НДС 22%). Клиент на УСН: уточнить в ДоЗ правило сравнения цен (у РусГидро обычно без НДС). Флаги нацрежима по всем 18 позициям = false (ЕИС), но ПП №1875 для 27.32 может быть указан в ДоЗ — проверить. Цены поставщиков не подобраны: н</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>32616433554</t>
+          <t>32616445272</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Воткинский филиал</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2668,19 +2698,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14.10.2026 08:00 МСК</t>
+          <t>15.10.2026 12:00 МСК</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1675767</v>
+        <v>1201357.95</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Видеокамера (26.40.33.111): 41 шт × ?; Части/принадлежности видеооборудования (кронш: 41 шт × ?; Части/принадлежности видеооборудования (короб: 41 шт × ?; Видеорегистратор: 2 шт × ?; Базовые системы хранения данных (HDD?): 16 шт × ? (цена за ед. = НМЦК / кол-во)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>11884.87234042553</v>
+          <t>поз.1 ОКПД2 27.32.13.159 Кабели, провода и шн: 135 Метр × ?; поз.2 ОКПД2 27.32.13.131 Провода силовые для : 0.10 Километр; тысяча метров × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 100 Метр × ?; поз.4 ОКПД2 27.32.14.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 60 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 115 Метр × ?; поз.7 ОКПД2 27.32.13.111 Кабели силовые с мед: 100 Метр × ?; поз.8 ОКПД2 27.32.13.143 Кабели контрольные (: 0.20 Километр; тысяча метров × ?; … ещё 7</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
       </c>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="4" t="n"/>
@@ -2694,29 +2726,29 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>АЭФ только СМП, РТС-тендер Id=4052238. Поставка, монтаж не указан. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
+          <t>НМЦ 1 201 357,95 без НДС (rostender: 1 465 656 с НДС). Флаги нацрежима false. Цены не подобраны — нет марок/сечений.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32616419880</t>
+          <t>32616445510</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ФГБУ «ФЦТОЭ» Минздрава России (г. Чебоксары)</t>
+          <t>АО «НИОПИК»</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2726,19 +2758,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15.10.2026 14:00 МСК</t>
+          <t>14.10.2026 10:00 МСК</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>878563.71</v>
+        <v>529280.65</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Камера видеонаблюдения (26.70.13.000): 16 шт × ?; Коммутатор (26.30.11.110): 3 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+          <t>Кабель сигнальный КИМЭлВ-ЗГнг(А) (ОКПД2 27.32: 1 усл. ед. × 529 280.65</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>43928.1855</v>
+        <v>529280.65</v>
       </c>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="4" t="n"/>
@@ -2752,7 +2784,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Документация (.docx) недоступна. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
+          <t>Цена за метр не определена: неизвестны длина и конструкция. Ориентир по аналогам 1х2х0,75 (КПСнг(А)-FRHF, МКЭШВнг(А)-LS) 30–60 ₽/м с НДС — для КИМ неприменимо без спецификации. ЭТП РТС-тендер.</t>
         </is>
       </c>
     </row>
@@ -2764,17 +2796,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>32616439096</t>
+          <t>32616449701</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>СПб ГБУК «Михайловский театр»</t>
+          <t>НАО «Центр «Омега» (Краснодарский край)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Телеком-оборудование и расходники (СКС, низкий приоритет)</t>
+          <t>Видеонаблюдение (СС, поставка)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2784,19 +2816,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13.10.2026 09:00 МСК</t>
+          <t>16.10.2026 10:00 МСК</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>987824.58</v>
+        <v>3229618.2</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>ITK оптический пигтейл: 240 шт/м × ?; Кабель оптический: 900 шт/м × ?; Кросс оптический: 10 шт/м × ?; Шкаф телеком. тип 1: 1 шт/м × ?; Шкаф телеком. тип 2: 2 шт/м × ?; Патч-корды типы 1–5: 160 шт/м × ?; Лоток глухой ЛМГ: 10 шт/м × ?; Кабель-канал типы 1–2: 44 шт/м × ?; … ещё 13 (цена за ед. = НМЦК / кол-во)</t>
+          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Видеокамера тип 1 (26.40.33.111): 20 шт × ?; Видеокамера тип 2: 30 шт × ?; Видеокамера тип 3: 30 шт × ?; Видеокамера тип 4: 20 шт × ?; Аппаратура коммуникационная передающая (26.30: 1 шт × ?; Панели/комплекты электр. аппаратуры (27.12.31: 2 шт × ?; Приборы для телекоммуникаций (26.51.44, тесте: 1 шт × ?; … ещё 2 (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>528.2484385026738</v>
+        <v>23923.09777777778</v>
       </c>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="4" t="n"/>
@@ -2810,143 +2842,123 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Пропущено: низкий приоритет, срок истекает, не профиль видеонаблюдения. Себестоимость не оценивалась.</t>
+          <t>Поставка (АЭФ только СМП), РТС-тендер Id=4056547. Монтаж в предмете не указан, но проверить проект договора. unit_nmck неизвестны → covered_nmck приравнен nmck условно, маржа по гипотезам ненадёжна. Нужна ручная выгрузка Обоснования НМЦД.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>СС</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0855200000526003358</t>
+          <t>32616433554</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ГБУЗ «Каменская ЦРБ им. Г.М. Савельевой»; организатор ГКУ ПО «Управление по осуществлению закупок Пензенской обл.»</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные (цитрат/K3/активатор)</t>
+          <t>Видеонаблюдение (СС, поставка)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15.10.2026 08:00 МСК</t>
+          <t>14.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>1432800</v>
+        <v>1675767</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с цитратом натрия 3,8%, 4–: 15 600 шт × 10.80; Пробирка вакуумная K3ЭДТА 3–? мл 13х75 (КТРУ : 50 400 шт × 10.80; Пробирка вакуумная с активатором свертывания : 60 000 шт × 12</t>
+          <t>Видеокамера (26.40.33.111): 41 шт × ?; Части/принадлежности видеооборудования (кронш: 41 шт × ?; Части/принадлежности видеооборудования (короб: 41 шт × ?; Видеорегистратор: 2 шт × ?; Базовые системы хранения данных (HDD?): 16 шт × ? (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.37142857142857</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1171120</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>0.1826353992183138</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>103594.3298630137</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>-233458.7178082192</v>
-      </c>
-      <c r="O36" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>11884.87234042553</v>
+      </c>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
+          <t>АЭФ только СМП, РТС-тендер Id=4052238. Поставка, монтаж не указан. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>СС</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0809500000326003912</t>
+          <t>32616419880</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ГБУЗ РМ «Республиканская клиническая больница им. С.В. Каткова»; организатор ГКУ РМ «Региональный центр организации закупок»</t>
+          <t>ФГБУ «ФЦТОЭ» Минздрава России (г. Чебоксары)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА</t>
+          <t>Видеонаблюдение (СС, поставка)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16.10.2026 09:00 МСК</t>
+          <t>15.10.2026 14:00 МСК</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>950000</v>
+        <v>878563.71</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная K3ЭДТА 2–? мл 13х75, пласт: 95 000 шт × 10</t>
+          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Камера видеонаблюдения (26.70.13.000): 16 шт × ?; Коммутатор (26.30.11.110): 3 шт × ? (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>852400</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0.1027368421052632</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>-3413.698630136991</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>-239013.698630137</v>
-      </c>
-      <c r="O37" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>43928.1855</v>
+      </c>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
+          <t>Документация (.docx) недоступна. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
         </is>
       </c>
     </row>
@@ -2958,87 +2970,75 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0171100002826000003</t>
+          <t>32616439096</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Управление Минюста России по Ярославской области</t>
+          <t>СПб ГБУК «Михайловский театр»</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Телеком-оборудование и расходники (СКС, низкий приоритет)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>15.10.2026 09:00 МСК</t>
+          <t>13.10.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>588408.7</v>
+        <v>987824.58</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Камера видеонаблюдения КТРУ 26.70.13.000-0000: 21 шт × 6 059.67; Коммутатор: 2 шт × 10 851; Трансивер: 1 шт × 2 185.67; Трансивер: 1 шт × 2 184; Источник бесперебойного питания (1): 1 шт × 15 589; Источник бесперебойного питания (2): 1 шт × 21 507; Блок розеток: 2 шт × 1 356.67; Шкаф телекоммуникационный: 2 шт × 15 799.67; … ещё 9</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>745107.8</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>-0.2663099644855695</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>-193660.3510794521</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>-336667.2015274521</v>
-      </c>
-      <c r="O38" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>ITK оптический пигтейл: 240 шт/м × ?; Кабель оптический: 900 шт/м × ?; Кросс оптический: 10 шт/м × ?; Шкаф телеком. тип 1: 1 шт/м × ?; Шкаф телеком. тип 2: 2 шт/м × ?; Патч-корды типы 1–5: 160 шт/м × ?; Лоток глухой ЛМГ: 10 шт/м × ?; Кабель-канал типы 1–2: 44 шт/м × ?; … ещё 13 (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>528.2484385026738</v>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
+          <t>Пропущено: низкий приоритет, срок истекает, не профиль видеонаблюдения. Себестоимость не оценивалась.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Амуниция</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0164200001926003491</t>
+          <t>0356500001426008776</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, Тамбовская КЦРБ, онкодиспансер, Петровская, Мичуринская ЦРБ, ТОДКБ и др.)</t>
+          <t>МКУ «Управление по делам ГО и ЧС» Лысьвенского МО</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА</t>
+          <t>Палатки</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3048,34 +3048,34 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>19.10.2026 07:00 МСК</t>
+          <t>13.10.2026 05:00 МСК</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1691688</v>
+        <v>190000</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с K3ЭДТА, пластик, 2–2,7 м: 35 000 шт × 9.24; То же, поз.2: 54 500 шт × 9.58; То же, поз.3: 25 000 шт × 9.93; То же, поз.4: 10 000 шт × 10.32; То же, поз.5: 2 400 шт × 10.72; То же, поз.6: 50 000 шт × 9.38</t>
+          <t>Палатка каркасная с утеплителем для спасатель: 1 шт × 190 000</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>9.56296212549463</v>
+        <v>190000</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1587948</v>
+        <v>160000</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.06132336459205243</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10112.2218739726</v>
+        <v>21972.38356164384</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-407641.8923835617</v>
+        <v>-11846.13698630137</v>
       </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
@@ -3084,29 +3084,29 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
+          <t>Приём заявок заканчивается завтра (13.10.2026 05:00 МСК) — успеть практически нереально. Запрет ПП 1875: нужна реестровая запись российского производителя. Цена — гипотеза.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Сантехника и ЖКХ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0164200001926003492</t>
+          <t>0372100004526000032</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, ТОДКБ, Тамбовская КЦРБ, онкодиспансер, Петровская, Уметская, Бондарская ЦРБ и др.); организатор — уполномоченный орган Тамбовской обл.</t>
+          <t>ФКУ ИК-7 ГУФСИН России по г. Санкт-Петербургу и Ленинградской обл.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные с активатором свёртывания</t>
+          <t>Запорная арматура (котельная)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3116,34 +3116,34 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19.10.2026 07:00 МСК</t>
+          <t>20.10.2026 11:45 МСК</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2815055</v>
+        <v>525965.97</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с активатором свертывания,: 60 000 шт × 9.89; То же, поз.2: 115 900 шт × 10.15; То же, поз.3: 20 000 шт × 10.31; То же, поз.4: 36 000 шт × 10.92; То же, поз.5: 45 000 шт × 9.91</t>
+          <t>Задвижка чугунная клиновая фланцевая PN16 DN8: 5 шт × 5 652.36; Затвор межфланцевый, корпус сталь, DN80 PN1,6: 5 шт × 5 203.79; Задвижка чугунная клиновая фланцевая PN16 DN1: 10 шт × 7 949.06; Затвор межфланцевый, корпус сталь, DN100: 5 шт × 6 546.88; Затвор межфланцевый, корпус сталь, DN50: 5 шт × 4 080.65; Задвижка чугунная клиновая фланцевая PN16 DN5: 3 шт × 3 414.66; Задвижка чугунная клиновая фланцевая PN16 DN5: 3 шт × 7 376; Обратный клапан межфланцевый чугун DN100: 3 шт × 7 861.20; … ещё 11</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10.16632358252077</v>
+        <v>4696.124732142857</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2484948</v>
+        <v>445321</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.1172648491770143</v>
+        <v>0.1533273530985284</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>157285.0023013699</v>
+        <v>57712.31357523285</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-513092.4608219178</v>
+        <v>-36454.80894772601</v>
       </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
@@ -3152,80 +3152,560 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
+          <t>Ограничение ПП 1875 (кроме фланцев — преимущество): нужна арматура российского производства с номером реестровой записи РПП (Челарм, СибЗТА — проверить реестр). ТЗ: задвижки чугунные PN16 металл-по-металлу — 30ч6бр это Ру10; под PN16 нужна 30ч515бр/30ч15бр (цена по запросу, вероятно дороже). Затворы</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Амуниция</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>32616456220</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ГАУ Амурской области «Амурская авиабаза»</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Палатки</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>20.10.2026 16:00 МСК</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>630600</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Палатка универсальная УП-5 «Берег» или эквива: 6 шт × 66 481.86; Тамбур-баня ПБ-1 «Берег» или эквивалент: 6 шт × 27 863.72; Тамбур-соединитель для палаток УП: 6 шт × 10 754.42</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>35033.33333333334</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>670000</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>-0.0624801776086267</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-55458.49863013699</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-118014.018630137</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>НМЦК за комплект 105 100 ₽ против розницы производителя 107 500 ₽ (УП-5 68 000 + ПБ-1 28 500 + соединитель 11 000) — маржа будет только при дилерской скидке Берега (обычно 15–25% для перепродавцов; нужно запросить). Цены по позициям в извещении не указаны, разбивка unit_nmck — оценка пропорционально</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Амуниция</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>32616447980</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>МАУ Сургутского района «Районный молодёжный центр»</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Спальные принадлежности</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>15.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Комплекты постельного белья (13.92.12.114): 280 компл × ?; Матрасы (31.03.12.120): 150 шт × ?; Одеяла (13.92.11.110): 150 шт × ?; Подушки (13.92.24.149): 150 шт × ?; Изделия текстильные прочие (13.92.29.190 — на: 150 шт × ?</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1091850</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.2201071428571429</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>237151.5136986302</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-137638.2191780823</v>
+      </c>
+      <c r="O42" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Срок подачи 15.10 09:00 МСК — осталось меньше 3 дней. ТЗ и обоснование НМЦД (xls) лежат на zakupki.gov.ru, доступа к ним нет: характеристики (ткань, плотность, наполнитель, размеры) и цены по позициям неизвестны, поэтому вся себестоимость — гипотеза. Вероятна высокая конкуренция ивановских производи</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Медрасходники</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0855200000526003358</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Каменская ЦРБ им. Г.М. Савельевой»; организатор ГКУ ПО «Управление по осуществлению закупок Пензенской обл.»</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные (цитрат/K3/активатор)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>15.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1432800</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с цитратом натрия 3,8%, 4–: 15 600 шт × 10.80; Пробирка вакуумная K3ЭДТА 3–? мл 13х75 (КТРУ : 50 400 шт × 10.80; Пробирка вакуумная с активатором свертывания : 60 000 шт × 12</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>11.37142857142857</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1171120</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0.1826353992183138</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>103594.3298630137</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-233458.7178082192</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0809500000326003912</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ГБУЗ РМ «Республиканская клиническая больница им. С.В. Каткова»; организатор ГКУ РМ «Региональный центр организации закупок»</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>16.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>950000</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная K3ЭДТА 2–? мл 13х75, пласт: 95 000 шт × 10</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>852400</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.1027368421052632</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-3413.698630136991</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-239013.698630137</v>
+      </c>
+      <c r="O44" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0171100002826000003</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Управление Минюста России по Ярославской области</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение (СС, поставка)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>15.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>588408.7</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Камера видеонаблюдения КТРУ 26.70.13.000-0000: 21 шт × 6 059.67; Коммутатор: 2 шт × 10 851; Трансивер: 1 шт × 2 185.67; Трансивер: 1 шт × 2 184; Источник бесперебойного питания (1): 1 шт × 15 589; Источник бесперебойного питания (2): 1 шт × 21 507; Блок розеток: 2 шт × 1 356.67; Шкаф телекоммуникационный: 2 шт × 15 799.67; … ещё 9</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>745107.8</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>-0.2663099644855695</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-193660.3510794521</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>-336667.2015274521</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0164200001926003491</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, Тамбовская КЦРБ, онкодиспансер, Петровская, Мичуринская ЦРБ, ТОДКБ и др.)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1691688</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с K3ЭДТА, пластик, 2–2,7 м: 35 000 шт × 9.24; То же, поз.2: 54 500 шт × 9.58; То же, поз.3: 25 000 шт × 9.93; То же, поз.4: 10 000 шт × 10.32; То же, поз.5: 2 400 шт × 10.72; То же, поз.6: 50 000 шт × 9.38</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>9.56296212549463</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1587948</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.06132336459205243</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>10112.2218739726</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>-407641.8923835617</v>
+      </c>
+      <c r="O46" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0164200001926003492</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, ТОДКБ, Тамбовская КЦРБ, онкодиспансер, Петровская, Уметская, Бондарская ЦРБ и др.); организатор — уполномоченный орган Тамбовской обл.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные с активатором свёртывания</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>2815055</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания,: 60 000 шт × 9.89; То же, поз.2: 115 900 шт × 10.15; То же, поз.3: 20 000 шт × 10.31; То же, поз.4: 36 000 шт × 10.92; То же, поз.5: 45 000 шт × 9.91</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>10.16632358252077</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>2484948</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>0.1172648491770143</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>157285.0023013699</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>-513092.4608219178</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>0335200014926003799</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Совместная закупка 26 ГБУЗ Калининградской обл.; организатор ГКУ КО «Центр обеспечения организации и проведения торгов»</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Пробирки вакуумные (совместная закупка, гель/NaF)</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>44-ФЗ</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>26.10.2026 10:00 МСК</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5909000</v>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Пробирка вакуумная с активатором свертывания/: 94 122 шт × 12.29; Пробирка вакуумная с K-оксалатом и NaF 4 мл 1: 94 122 шт × 9.90; Пробирка вакуумная с активатором/гелем 5 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 6 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 5,5 мл: 94 122 шт × 13.53</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>12.55604428295191</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>5187766.56</v>
       </c>
-      <c r="K41" s="4" t="n">
+      <c r="K48" s="4" t="n">
         <v>0.1220567676425792</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L48" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>89623.21567123328</v>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="N48" s="2" t="n">
         <v>-1359992.922739726</v>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O48" s="8" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК поделена поровну по позициям (НМЦК/Σцен ед.). 26 отдельных контрактов, ~26 точек доставки в эксклаве (транзит через ЛТ/паром), срок до 31.07.2027. NaF-пробирка: дистрибьюторская цена 10,93 &gt; НМЦК 9,90 — убыточна без завод</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P41"/>
+  <autoFilter ref="A1:P48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3236,7 +3716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3300,52 +3780,5285 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Сантехника и ЖКХ</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>68554.01568482628</v>
+        <v>446222.1079407868</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7525368.13277052</v>
+        <v>68554.01568482628</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7525368.13277052</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>СС</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Амуниция</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Предмет</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Регион</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Подача</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>ЭТП</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Что делать</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Амуниция и снаряжение</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2143317/1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Палатка армейская Берег 10М2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ПАО «Нижнекамскнефтехим»</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>16 Республика Татарстан</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Сибур</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Амуниция и снаряжение</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COM29092600103</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Поставка палаток для ООО "ЛУКОЙЛ-ПНОС" в 2027 году.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ООО «Лукойл-Пермнефтеоргсинтез»</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>59 Пермский край</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Амуниция и снаряжение</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0036026006DP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Поставка товара (палатка)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Центр услуг в сфере закупок</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Амуниция и снаряжение</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5572307</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Поставка плащ-палаток в целях реализации мероприятия "Региональный слет «Хранители истории». Волгоградская область" (ИД 26/63065)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Общероссийское Общественно-государственное Движение Детей и Молодежи «Движение Первых»</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Амуниция и снаряжение</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COM05102600023</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Поставка Шатров туристических с москитной сеткой Btrace Camp для ООО "ЛУКОЙЛ-Пермнефтеоргсинтез" в 2026г. -</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ООО «Лукойл-Пермнефтеоргсинтез»</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>59 Пермский край</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Амуниция и снаряжение</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>COM01102600102</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Поставка палаток для ООО "ЛУКОЙЛ-Пермь" в 2027 году.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ООО «Лукойл-Пермь»</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>59 Пермский край</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Вентиляция</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0801200000426000157</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Поставка фильтров для очистки воздуха</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ГКУ Республики Башкортостан Транспортное Управление</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>02 Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:45</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0372200048026000444</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>СПБ ГБУЗ «Детский Городской Многопрофильный Клинический Специализированный Центр Высоких Медицинских Технологий»</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>78 Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:50</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0358100011226000578</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Инструменты и оборудование медицинские (Расходные материалы для ЦКДЛ)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Федеральное ГБУЗ «Новороссийский Клинический Центр Федерального Медико-Биологического Агентства»</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0335200007326000234</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий (Пробирка вакуумная для взятия образцов крови ИВД)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Инфекционная Больница Калининградской Области»</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>39 Калининградская область</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0380200006426000026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Поставка изделий медицинского назначения и дезинфицирующих средств на 1-ое полугодие 2027 года.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ГБУЗ Республики Хакасия «Республиканская Клиническая Психиатрическая Больница»</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>19 Республика Хакасия</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0368400000226000827</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий (Филиал №1)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Федеральное ГБУ «Федеральный Научно-Клинический Центр Медицинской Радиологии и Онкологии» Федерального Медико-Биологического Агентства</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>73 Ульяновская область</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4636388</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ветеринарные расходные и зоотехния, дезинфектанты, инсектициды и родентициды для КРС для нужд ГК Агропромкомплектация (ООО "АПК-Курск" и АО "Агрофирма Дмитрова Гора") на ноябрь 2026г.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ООО «Агропромкомплектация»</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0387200027826000473</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов (контейнер для сбора мочи для анализа на наркотики ИВД)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономного Округа - Югры «Мегионская Городская Больница»</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0319100000226000765</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>На поставку общелабораторных расходных материалов на 2027 год</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Федеральное ГБУ «Федеральный Центр Сердечно-Сосудистой Хирургии» Министерства Здравоохранения РФ (г. Красноярск)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>24 Красноярский край</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0318200023226000051</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий (Пробирка вакуумная для взятия образцов крови ИВД, с K3ЭДТА, пробирка вакуумная для взятия образцов крови ИВД, с натрия цитратом, пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Краевой Клинический Госпиталь Для Ветеранов Войн Им. Проф. В.К. Красовитова» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0334300106826000204</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий (пробирок вакуумных) (лот1)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Областное ГБУЗ «Тайшетская Районная Больница»</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0355200004926000462</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов (контейнер для сбора мочи, кала, чашка Петри, петли бактериологические) для бактериологического отдела клинико-диагностической лаборатории на 2027 год для нужд ГБУЗ «Областной онкологический клинический диспансер»</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Областной Онкологический Клинический Диспансер»</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>58 Пензенская область</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0316300093226000066</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов (Лабораторные расходники, тесты, пробирки) на 2027 год</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ГБУ Республики Саха (Якутия) «Вилюйская Центральная Районная Больница Имени П.А. Петрова»</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>14 Республика Саха (Якутия)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0321200022026000841</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Поставка изделий медицинского назначения</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ГБУЗ Ставропольского Края «Ставропольская Краевая Клиническая Больница»</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>26 Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0387200003226000356</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для микробиологической лаборатории</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономного Округа - Югры «Сургутская Клиническая Травматологическая Больница»</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0335300052226000348</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>На поставку изделий медицинского назначения контейнер (для сбора проб мочи ИВД)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ГБУЗ Калининградской обл. «Городская Больница № 2»</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>39 Калининградская область</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-31 18:00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4625189</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Закупка спецобуви»</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>АО «Саянскхимпласт»</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5516838</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Костюмы, куртки 2027</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:45</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ЭТП ПАО ММК</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0373100134526000891</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Поставка специальной обуви для нужд филиала ФГБУ «Рослесинфорг» «Дальлеспроект»</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Федеральное ГБУ «Рослесинфорг»</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>50 Московская область</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>382-758</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Закупка зимней спецодежды в г.Тюмень</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:52</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0348100009626000412</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Вещевое имущество (Ботинки с высокими берцами)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ФГКУ «Ногинский Ордена Жукова Спасательный Центр Министерства РФ по Делам Гражданской Обороны, Чрезвычайным Ситуациям и Ликвидации Последствий Стихийных Бедствий»</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>50 Московская область</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4628361</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>СИЗ (Медикаменты, бронежилеты,защита)_АЗОТ_ДГ октябрь_2026г.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Азот АО Охк Уралхим в г. Березники, Филиал</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>587955</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Спецодежда для АО «ЧЕЛНЫ ХЛЕБ»</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>АО «Челны-Хлеб»</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16 Республика Татарстан</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Электронная торговая площадка ONLINECONTRACT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>381-629</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Закупка зимней спецодежды для ООО "Заречное". 2026г.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>АО «Агрохолдинг «Просторы»</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4630854</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Приобретение спецодежды и СИЗ для ООО СГРК</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>АО «Высочайший»</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ГП622856</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Поставка СИЗ 2027</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ООО «Омский Завод Полипропилена»</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>55 Омская область</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>383-467</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Закупка специальной одежды и СИЗ на склад Томилино</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>АО «Кюхенлэнд Хоум Рус»</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3502975</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Поставка спецодежды, спецобуви для ООО "АЛАБУГА-ВОЛОКНО".</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ООО «Алабуга-Волокно»</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16 Республика Татарстан</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-16 23:59</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0573400000126006237</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Поставка специальной одежды, специальной обуви и других средств индивидуальной защиты для нужд Владивостокского центра ОВД филиала «Аэронавигация Дальнего Востока»</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ФГУП «Государственная Корпорация по Организации Воздушного Движения в РФ»</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-21 07:07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4634447</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Открытый запрос предложений по выбору ПУЛа поставщиков спецодежды для ГК Биннофарм Групп на 2026-2027 гг.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ООО «Биннофарм Групп»</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>СИЗ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>374-491</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Поставка СИЗ и спецодежды для нужд АО "Нижфарм"/ООО "Хемофарм"</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>АО «Нижегородский Химико-Фармацевтический Завод»</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>52 Нижегородская область</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>СИЗ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>COM12102600016</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Закуп запчастей для ТК и СВТ(АРМ), сервиса печати ОКТЯБРЬ 2026 АО ДИАЙПИ г. Полевской</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>АО «Диайпи»</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>74 Челябинская область</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ЭТП Группы ТМК</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>СИЗ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>311-335</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Закупка_ Консолидированная закупка СИЗ 2027 г._ просьба подать ваше предложение+ подготовить невозвратные образцы</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>АО «Прогресс»</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>48 Липецкая область</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>СИЗ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>372-446</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Приобретение специальной одежды, специальной обуви, СИЗ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ООО «Благо-Армавир»</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>СИЗ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3503134</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты головы, органов зрения, слуха, дыхания</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>АО «Машиностроительный Завод»</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>50 Московская область</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:59</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4632023</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>КД-И-0645 Поставка МТР (трубная продукция)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Филиал Общества с ограниченной ответственностью «Аргос-Строй»-Прометей</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4626595</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Проведение конкурентной процедуры по закупке запорной арматуры для нужд филиала ЗМУ и ЖТК ТОО "Казфосфат", г. Тараз.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ТОО «Казфосфат» филиал Жтк</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:44</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7795</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Поставка ЗИП к ЗРА (Sisto20)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7797</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Поставка ЗРА общепром (НЖ)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7799</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Поставка ЗРА химическая</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7798</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Поставка ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5514020</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>410.215 Черные металлы. Трубы черные бесшовные</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ПАО «Магнитогорский Металлургический Комбинат»</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>74 Челябинская область</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:45</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ЭТП ПАО ММК</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>B0910261413495</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Поставка соединителей и клапана</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>АО «Таганрогский Завод «Прибой»</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>61 Ростовская область</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7823</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7821</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (НЖ)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7824</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (чугун, бронза, латунь)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4628452</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Трубопроводная арматура</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>АО «Уральская Сталь»</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>56 Оренбургская область</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4610157</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Проведение конкурентной закупочной процедуры Запорной арматуры для нужд ТОО "Казфосфат" Филиал: ЗМУ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ТОО «Казфосфат» филиал Зму</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>РН61002402</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Запорная арматура</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ООО «РН-Юганскнефтегаз»</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>4056154</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Закупка отводов в ППУ-изоляции</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>АО «Урало-Сибирская Теплоэнергетическая Компания-Челябинск»</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>74 Челябинская область</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7855</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ЗРА (затворы)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7854</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ЗИП к ЗРА по ASTM</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7826</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ЗРА химическая</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7856</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (нж)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7827</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ЗРА прочее</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7825</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ЗРА регулирующая, отсечная</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7858</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (чугун, бронза, латунь)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>140434-ТТ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ЗАТВОР 1200 + задвижка 1200 ЧЦ00-Ц02948</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>АО «Челябинский Цинковый Завод»</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>74 Челябинская область</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ЭТП Металл-ИТ</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7860</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ЗРА (энергетика)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:04</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7796</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Поставка ЗРА по ASTM</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>4634875</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Поставка кранов 2-го класса для нужд объекта АЭС "Руппур"</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>АО Оэс</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>32616426481</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Поставка задвижек и клапанов для филиала «ТЭЦ-9» ООО «БЭК» в 2027 году.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ООО «Эн+ ТД»</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-10-15 18:00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>3502351</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Задвижки стальные</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>АО «Сибирский Химический Комбинат»</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>70 Томская область</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-10-15 23:59</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7870</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (чугун, бронза, латунь)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7872</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (нж)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (нж)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7851</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ЗРА (прочее)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7869</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ЗРА по ASTM</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7864</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Энергетическая ЗРА</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ЗРА (химическая)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>7849</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ЗРА (спец. исполнение)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>141078-ТТ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Поставка запорной арматуры и комплектующих на 4 квартал 2026 и 1 квартал 2027 г. для АО ЧЦЗ</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>АО «Челябинский Цинковый Завод»</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>74 Челябинская область</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ЭТП Металл-ИТ</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7865</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (чугун, бронза, латунь)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:02</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>7866</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:04</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>7875</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (нж)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7873</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4628404</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Поставка ЗРА для нужд ООО "ЛУКОЙЛ-КНТ"</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ООО «Лукойл-Транс»</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7886</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7878</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (сталь)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7887</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (НЖ)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7884</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (чугун, бронза, латунь)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>7879</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ЗРА общепром (нж)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ООО «Рх-Снабжение»</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ЭТП Торги РФ</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1251633</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Отбор на поставку импортной запорной арматуры на 2027 год для филиалов ИСО в г. Красноярске, Новокузнецке, Шелехове, Братске, Тайшете, Саяногорске.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ООО «Инжиниринг Строительство Обслуживание»</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-10-19 20:00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Тендер.Про</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1253241</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Закупка зматериалов (трубы, муфты, втулки, отводы, кольца ОНК, фланцы, люки) для внутриплощадочных сетей, сооружений водоснабжения и канализации НВК-10 в рамках реализации проекта "Братский алюминиевый завод. Экологическая реконструкция"</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ООО «Объединенная Компания Русал Промышленное Технологическое Развитие»</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Тендер.Про</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>РН61002730</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15лс68нж 25х250 ХЛ1 A с ответными фланцами</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ООО «Башнефть-Полюс»</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>83 Ненецкий АО</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1251608</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Отбор поставщиков отечественной запорной арматуры для филиалов ООО "ИСО" на 2027 год</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ООО «Инжиниринг Строительство Обслуживание»</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-10-20 23:00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Тендер.Про</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1253374</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>закупка сантехники для филиала ООО ИСО в г. Шелехов</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Филиал ООО «Исо» (г Шелехов)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Тендер.Про</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4628678</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Поставка электротоваров для нужд Невьянского филиала АО "ЦЕМРОС"</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>АО «Цемрос»</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>4633153</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Изоляционные материалы для трубопроводов</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ООО «Аргос-Строй»</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ЗП610443</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Кабельная арматура для нужд Филиала Яйвинская ГРЭС ПАО Юнипро</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ПАО «Юнипро»</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ЗП610451</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Провода неизолированные</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ПАО «Юнипро»</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:31</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>4581487</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Хозяйственно питьевой водопровод кран гильза муфта (служебка)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ООО «Артстройтехнология»</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>4581432</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Авиамоторная Водопровод отвод (служебка)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ООО «Артстройтехнология»</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>4581008</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Авиамоторная Хозяйственно питьевой водопровод горячий (служебка)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ООО «Артстройтехнология»</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>4579771</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Авиамотрная Противопожарный водопровод (Служебка)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ООО «Артстройтехнология»</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>4578344</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Авиамоторная Водопровод Groovex (Служебка)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ООО «Артстройтехнология»</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4578008</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Авиамоторная Хозяйственно-питьевой водопровод (Служебка)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ООО «Артстройтехнология»</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4572755</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Авиамоторная Светильник Люстра (Служебка )</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ООО «Артстройтехнология»</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>4634356</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Опоры для трубопроводов. По ОСТ 36-146-88 и др. УКК. DDP, Пермский край, г.Березники</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ООО «Еврохим - Укк»</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>59 Пермский край</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4635948</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Кабеленесущие системы (ПР0000592)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Филиал Общества с ограниченной ответственностью «Аргос-Строй»-Кедр</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>4634099</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Куллера и проводки</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ООО «Промсорт»</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>4632337</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Поставка электролампой продукции и электроустановочных изделий для филиала «Невинномысская ГРЭС» ПАО «ЭЛ5-Энерго» в 2027 году</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ПАО «Эл5-Энерго»</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>66 Свердловская область</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ЗП610233</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Сетевой кабель для филиала "Яйвинская ГРЭС" ПАО "ЮНИПРО"</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ПАО «Юнипро»</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ДН00-00001742</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Закупка деталей трубопровода</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>18 Удмуртская республика</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:59</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4632494</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>АО «ПромСорт-Урал». Закупка автоматики</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ООО «Промсорт»</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:00</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>4632400</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Кабель КВБШвнг-ХЛ 5х1,5</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>АО «Холдинг Эрсо»</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SBR028-2610090033</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1363 - поставка инструментов для диагностики и очистки оптических кабелей для нужд ООО «Облачные технологии»</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ООО «Облачные Технологии»</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>4632340</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Закупка светильников,прожекторов,газоанализаторов,громкоговорителя.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ООО «Аргос-Строй»</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ЗП610785</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Поставка Кабеля ТППэпт для нужд филиала "Смоленская ГРЭС" ПАО "ЮНИПРО"</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ПАО «Юнипро»</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>4629870</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Поставка греющего кабеля и комплектующих для структурного подразделения ООО "ЛУКОЙЛ-Транс" (ООО "РПК-Высоцк "ЛУКОЙЛ-II")»</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ООО «Лукойл-Транс»</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4634359</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Закупка кабельной продукции ( FLOP- Устранение технологических ограничений м/р им. В. Филановского)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ООО «Аргос-Строй»</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:00</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>4551799</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Поставка автоматического электроустановочного оборудования и комплектующих ООО "Варандейский терминал"</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ООО «Лукойл-Транс»</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-10-16 14:51</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>4635736</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Трубопроводы стеклопластик с резин. футер. для маточного раствора, фильтрата, флокулянта</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ООО «Еврохим - Укк»</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>59 Пермский край</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-10-16 23:00</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ЭОМ (кабель)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4634957</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Трубопровод стеклопластиковый с внутренней футеровкой</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ООО «Еврохим - Укк»</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>59 Пермский край</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-10-16 23:00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Цена не опубликована: запросить ТЗ на площадке и подать КП</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H124"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/TENDERS_1210.xlsx
+++ b/TENDERS_1210.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цены по позициям в извещении не указаны: НМЦ лота задана одной суммой, документация (zip) на zakupki.gov.ru, доступа к ней нет, поэтому unit_nmck не указаны. У Т Плюс НМЦ часто указана без НДС — проверить; для УСН это важно. Около половины позиций (энергетические вентили ВТ-5, ВИГ, 15с27нж, 14с17п, </t>
+          <t xml:space="preserve">[ГИПОТЕЗА по себестоимости] Цены по позициям в извещении не указаны: НМЦ лота задана одной суммой, документация (zip) на zakupki.gov.ru, доступа к ней нет, поэтому unit_nmck не указаны. У Т Плюс НМЦ часто указана без НДС — проверить; для УСН это важно. Около половины позиций (энергетические вентили ВТ-5, ВИГ, 15с27нж, 14с17п, </t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Цены по позициям не указаны в извещении; длины плеч, диаметр оболочки и наличие проводников ОДК — в документах (недоступны). Тяжёлый груз (426/530 — по 200–300 кг), доставка в Уфу — оценка 45 тыс. Уфимские производители ППУ (например, местные заводы) имеют логистическое преимущество. Не СМП-закупка.</t>
+          <t>[ГИПОТЕЗА по себестоимости] Цены по позициям не указаны в извещении; длины плеч, диаметр оболочки и наличие проводников ОДК — в документах (недоступны). Тяжёлый груз (426/530 — по 200–300 кг), доставка в Уфу — оценка 45 тыс. Уфимские производители ППУ (например, местные заводы) имеют логистическое преимущество. Не СМП-закупка.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
+          <t>[ГИПОТЕЗА по себестоимости] Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
+          <t>[ГИПОТЕЗА по себестоимости] Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Диаметры и типы неизвестны: ТЗ в rar на zakupki.gov.ru, доступа нет. Запрос котировок для МСП на ЭТП РАД (lot-online). Флаг нацрежима стоит → нужен российский производитель. Малый лот, логистика съедает маржу.</t>
+          <t>[ГИПОТЕЗА по себестоимости] Диаметры и типы неизвестны: ТЗ в rar на zakupki.gov.ru, доступа нет. Запрос котировок для МСП на ЭТП РАД (lot-online). Флаг нацрежима стоит → нужен российский производитель. Малый лот, логистика съедает маржу.</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Приём заявок заканчивается завтра (13.10.2026 05:00 МСК) — успеть практически нереально. Запрет ПП 1875: нужна реестровая запись российского производителя. Цена — гипотеза.</t>
+          <t>[ГИПОТЕЗА по себестоимости] Приём заявок заканчивается завтра (13.10.2026 05:00 МСК) — успеть практически нереально. Запрет ПП 1875: нужна реестровая запись российского производителя. Цена — гипотеза.</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ограничение ПП 1875 (кроме фланцев — преимущество): нужна арматура российского производства с номером реестровой записи РПП (Челарм, СибЗТА — проверить реестр). ТЗ: задвижки чугунные PN16 металл-по-металлу — 30ч6бр это Ру10; под PN16 нужна 30ч515бр/30ч15бр (цена по запросу, вероятно дороже). Затворы</t>
+          <t>[ГИПОТЕЗА по себестоимости] Ограничение ПП 1875 (кроме фланцев — преимущество): нужна арматура российского производства с номером реестровой записи РПП (Челарм, СибЗТА — проверить реестр). ТЗ: задвижки чугунные PN16 металл-по-металлу — 30ч6бр это Ру10; под PN16 нужна 30ч515бр/30ч15бр (цена по запросу, вероятно дороже). Затворы</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Срок подачи 15.10 09:00 МСК — осталось меньше 3 дней. ТЗ и обоснование НМЦД (xls) лежат на zakupki.gov.ru, доступа к ним нет: характеристики (ткань, плотность, наполнитель, размеры) и цены по позициям неизвестны, поэтому вся себестоимость — гипотеза. Вероятна высокая конкуренция ивановских производи</t>
+          <t>[ГИПОТЕЗА по себестоимости] Срок подачи 15.10 09:00 МСК — осталось меньше 3 дней. ТЗ и обоснование НМЦД (xls) лежат на zakupki.gov.ru, доступа к ним нет: характеристики (ткань, плотность, наполнитель, размеры) и цены по позициям неизвестны, поэтому вся себестоимость — гипотеза. Вероятна высокая конкуренция ивановских производи</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
+          <t>[ГИПОТЕЗА по себестоимости] Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
         </is>
       </c>
     </row>

--- a/TENDERS_1210.xlsx
+++ b/TENDERS_1210.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Коммерческие без НМЦК" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$P$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$U$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Коммерческие без НМЦК'!$A$1:$H$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,12 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -564,6 +569,31 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Аванс</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Обеспечение заявки</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Обеспечение исполнения контракта</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Только СМП</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Площадка (ЭТП)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Комментарий</t>
         </is>
       </c>
@@ -632,6 +662,31 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ на эквивалент</t>
         </is>
       </c>
@@ -700,6 +755,27 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>67 240 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>672 400 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>223-ФЗ; обеспечение исполнения 10%</t>
         </is>
       </c>
@@ -768,6 +844,31 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ</t>
         </is>
       </c>
@@ -836,6 +937,31 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>14 760 ₽ (0.5%)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>5.00 % (≈147 600 ₽)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>НМЦК 19,68 ₽ — вдвое выше рынка, поэтому ожидается сильное снижение (вероятно верхний квартиль скидки, 40–55%). Особенность крышки (полнозаходная резьба / двухступенчатое снятие) — нужно подтвердить, что UNIVAC/другая российская пробирка этому соответствует, иначе отклонение. СМП-only. Минимальный о</t>
         </is>
       </c>
@@ -904,6 +1030,27 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ПАО «Т‑Плюс»</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t xml:space="preserve">[ГИПОТЕЗА по себестоимости] Цены по позициям в извещении не указаны: НМЦ лота задана одной суммой, документация (zip) на zakupki.gov.ru, доступа к ней нет, поэтому unit_nmck не указаны. У Т Плюс НМЦ часто указана без НДС — проверить; для УСН это важно. Около половины позиций (энергетические вентили ВТ-5, ВИГ, 15с27нж, 14с17п, </t>
         </is>
       </c>
@@ -972,6 +1119,27 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Российская электронная система торгов</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Цены по позициям не указаны в извещении; длины плеч, диаметр оболочки и наличие проводников ОДК — в документах (недоступны). Тяжёлый груз (426/530 — по 200–300 кг), доставка в Уфу — оценка 45 тыс. Уфимские производители ППУ (например, местные заводы) имеют логистическое преимущество. Не СМП-закупка.</t>
         </is>
       </c>
@@ -1040,6 +1208,31 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>есть, размер в документации</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
         </is>
       </c>
@@ -1110,6 +1303,31 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>180 339 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10.00 % (≈1 803 387 ₽)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1180,6 +1398,31 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>62 244 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>10.00 % (≈622 442 ₽)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1248,6 +1491,31 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Центр Закупок Республики Саха (Якутия)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1315,6 +1583,31 @@
         </is>
       </c>
       <c r="P12" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1382,6 +1675,27 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1452,6 +1766,31 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1522,6 +1861,27 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1590,6 +1950,31 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>125 598 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1659,6 +2044,27 @@
         </is>
       </c>
       <c r="P17" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1726,6 +2132,31 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1793,6 +2224,31 @@
         </is>
       </c>
       <c r="P19" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4 357 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>5.00 % (≈21 783 ₽)</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -1860,6 +2316,27 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1926,6 +2403,27 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -1996,6 +2494,31 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>5.00 % (≈16 035 ₽)</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -2064,6 +2587,27 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1 353 ₽ (0.5%)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>27 065 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -2132,6 +2676,31 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1.00 % (≈2 302 ₽)</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -2200,6 +2769,31 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2 136 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>10.00 % (≈21 357 ₽)</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -2269,6 +2863,31 @@
         </is>
       </c>
       <c r="P26" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Информационная система "Управление закупками отдельными видами юридических лиц"</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
@@ -2336,6 +2955,27 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Электронный Магазин Ленинградской области</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -2402,6 +3042,27 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
@@ -2470,6 +3131,27 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>15 000 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>150 000 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
         </is>
       </c>
@@ -2538,6 +3220,31 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>РАД (Lot-Online)</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Диаметры и типы неизвестны: ТЗ в rar на zakupki.gov.ru, доступа нет. Запрос котировок для МСП на ЭТП РАД (lot-online). Флаг нацрежима стоит → нужен российский производитель. Малый лот, логистика съедает маржу.</t>
         </is>
       </c>
@@ -2605,6 +3312,27 @@
         </is>
       </c>
       <c r="P31" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>90 000 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>Количество не определено — qty условные (НМЦК/Σцен ед. поровну). Доставка в Нижневартовск (дорогая логистика). Контракт до 31.03.2027.</t>
         </is>
@@ -2666,6 +3394,27 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
+          <t>есть, размер в документации</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>РАД (Lot-Online)</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>НМЦ 2 176 178,20 в ЕИС — БЕЗ НДС (rostender показывает 2 654 937 с НДС 22%). Клиент на УСН: уточнить в ДоЗ правило сравнения цен (у РусГидро обычно без НДС). Флаги нацрежима по всем 18 позициям = false (ЕИС), но ПП №1875 для 27.32 может быть указан в ДоЗ — проверить. Цены поставщиков не подобраны: н</t>
         </is>
       </c>
@@ -2726,6 +3475,27 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
+          <t>есть, размер в документации</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>РАД (Lot-Online)</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>НМЦ 1 201 357,95 без НДС (rostender: 1 465 656 с НДС). Флаги нацрежима false. Цены не подобраны — нет марок/сечений.</t>
         </is>
       </c>
@@ -2784,6 +3554,31 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
+          <t>есть, размер в документации</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
           <t>Цена за метр не определена: неизвестны длина и конструкция. Ориентир по аналогам 1х2х0,75 (КПСнг(А)-FRHF, МКЭШВнг(А)-LS) 30–60 ₽/м с НДС — для КИМ неприменимо без спецификации. ЭТП РТС-тендер.</t>
         </is>
       </c>
@@ -2842,6 +3637,31 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>161 481 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>Поставка (АЭФ только СМП), РТС-тендер Id=4056547. Монтаж в предмете не указан, но проверить проект договора. unit_nmck неизвестны → covered_nmck приравнен nmck условно, маржа по гипотезам ненадёжна. Нужна ручная выгрузка Обоснования НМЦД.</t>
         </is>
       </c>
@@ -2900,6 +3720,31 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>83 788 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
           <t>АЭФ только СМП, РТС-тендер Id=4052238. Поставка, монтаж не указан. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
         </is>
       </c>
@@ -2958,6 +3803,27 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>87 856 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>Документация (.docx) недоступна. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
         </is>
       </c>
@@ -3016,6 +3882,31 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>49 391 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>Пропущено: низкий приоритет, срок истекает, не профиль видеонаблюдения. Себестоимость не оценивалась.</t>
         </is>
       </c>
@@ -3084,6 +3975,31 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.00 % (≈1 900 ₽)</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Приём заявок заканчивается завтра (13.10.2026 05:00 МСК) — успеть практически нереально. Запрет ПП 1875: нужна реестровая запись российского производителя. Цена — гипотеза.</t>
         </is>
       </c>
@@ -3152,6 +4068,31 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5.00 % (≈26 298 ₽)</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Ограничение ПП 1875 (кроме фланцев — преимущество): нужна арматура российского производства с номером реестровой записи РПП (Челарм, СибЗТА — проверить реестр). ТЗ: задвижки чугунные PN16 металл-по-металлу — 30ч6бр это Ру10; под PN16 нужна 30ч515бр/30ч15бр (цена по запросу, вероятно дороже). Затворы</t>
         </is>
       </c>
@@ -3220,6 +4161,31 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
           <t>НМЦК за комплект 105 100 ₽ против розницы производителя 107 500 ₽ (УП-5 68 000 + ПБ-1 28 500 + соединитель 11 000) — маржа будет только при дилерской скидке Берега (обычно 15–25% для перепродавцов; нужно запросить). Цены по позициям в извещении не указаны, разбивка unit_nmck — оценка пропорционально</t>
         </is>
       </c>
@@ -3290,6 +4256,31 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Срок подачи 15.10 09:00 МСК — осталось меньше 3 дней. ТЗ и обоснование НМЦД (xls) лежат на zakupki.gov.ru, доступа к ним нет: характеристики (ткань, плотность, наполнитель, размеры) и цены по позициям неизвестны, поэтому вся себестоимость — гипотеза. Вероятна высокая конкуренция ивановских производи</t>
         </is>
       </c>
@@ -3358,6 +4349,31 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>14 328 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5.00 % (≈71 640 ₽)</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
           <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
         </is>
       </c>
@@ -3426,6 +4442,31 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5.00 % (≈47 500 ₽)</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>РАД (Lot-Online)</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
           <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
         </is>
       </c>
@@ -3496,6 +4537,31 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>5 884 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>30.00 % (≈176 523 ₽)</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>[ГИПОТЕЗА по себестоимости] Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
         </is>
       </c>
@@ -3564,6 +4630,27 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>16 917 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>84 584 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
         </is>
       </c>
@@ -3632,6 +4719,27 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>28 151 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>140 753 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
         </is>
       </c>
@@ -3700,12 +4808,33 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>7 500 ₽ (0.1%)</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>295 450 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК поделена поровну по позициям (НМЦК/Σцен ед.). 26 отдельных контрактов, ~26 точек доставки в эксклаве (транзит через ЛТ/паром), срок до 31.07.2027. NaF-пробирка: дистрибьюторская цена 10,93 &gt; НМЦК 9,90 — убыточна без завод</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P48"/>
+  <autoFilter ref="A1:U48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TENDERS_1210.xlsx
+++ b/TENDERS_1210.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Коммерческие без НМЦК" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$U$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тендеры 12.10'!$A$1:$U$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Коммерческие без НМЦК'!$A$1:$H$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U48"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -783,59 +783,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32616447519</t>
+          <t>0373200024426001489</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>АО «Волоколамское ПТП РЖКХ», МО</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ГОРОДА МОСКВЫ "ГОРОДСКАЯ КЛИНИЧЕСКАЯ БОЛЬНИЦА № 15 ИМЕНИ О.М. ФИЛАТОВА ДЕПАРТАМЕНТА ЗДРАВООХРАНЕНИЯ ГОРОДА МОСКВЫ"</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Соль техническая 130 т</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.10.2026 10:00</t>
+          <t>14.10.2026 11:00 МСК</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1593800</v>
+        <v>9999955.800000001</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>130 т × 12 260 ₽/т</t>
+          <t>Пробирка вакуумная с активатором свертывания : 95 730 шт × 21.43; Пробирка вакуумная с активатором свертывания : 95 730 шт × 28.39; Пробирка вакуумная для определения скорости о: 95 730 шт × 32.08; Пробирка для сбора образцов крови не вакуумна: 95 730 шт × 22.56</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12260</v>
+        <v>26.115</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>325000</v>
+        <v>2859158</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.7960848287112561</v>
+        <v>0.6353248293079067</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1018243.203419178</v>
+        <v>4080771.001139726</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>856976.144219178</v>
+        <v>2428038.501539726</v>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>50 000 ₽ (0.5%)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>5.00 % (≈499 998 ₽)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -864,71 +864,71 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ</t>
+          <t>[ГИПОТЕЗА по себестоимости] Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК/Σцен ед. поровну по позициям. Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до ?. Позиции вне профиля (себестоимость не дана): Пробирка для с</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Соль</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0373200001326001396</t>
+          <t>32616447519</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ГБУЗ г. Москвы «ГКБ им. В.В. Вересаева ДЗМ»</t>
+          <t>АО «Волоколамское ПТП РЖКХ», МО</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные с активатором</t>
+          <t>Соль техническая 130 т</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15.10.2026 09:00 МСК</t>
+          <t>16.10.2026 10:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2952000</v>
+        <v>1593800</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с активатором свертывания,: 150 000 шт × 19.68</t>
+          <t>130 т × 12 260 ₽/т</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>19.68</v>
+        <v>12260</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1446500</v>
+        <v>325000</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.5099932249322493</v>
+        <v>0.7960848287112561</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1178755.920547945</v>
+        <v>1018243.203419178</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>556474.3205479452</v>
+        <v>856976.144219178</v>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
@@ -942,12 +942,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>14 760 ₽ (0.5%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>5.00 % (≈147 600 ₽)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -957,71 +957,71 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>НМЦК 19,68 ₽ — вдвое выше рынка, поэтому ожидается сильное снижение (вероятно верхний квартиль скидки, 40–55%). Особенность крышки (полнозаходная резьба / двухступенчатое снятие) — нужно подтвердить, что UNIVAC/другая российская пробирка этому соответствует, иначе отклонение. СМП-only. Минимальный о</t>
+          <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Сантехника и ЖКХ</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32616442935</t>
+          <t>0373200001326001396</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ПАО «Т Плюс», филиал «Нижегородский»</t>
+          <t>ГБУЗ г. Москвы «ГКБ им. В.В. Вересаева ДЗМ»</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Запорная арматура стальная (ТЭЦ)</t>
+          <t>Пробирки вакуумные с активатором</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.10.2026 14:00 МСК</t>
+          <t>15.10.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1883587.49</v>
+        <v>2952000</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Вентиль ВТ-5 Ду10 Ру250: 10 шт × ?; Вентиль ВИГ-250Д-Н1Б1Г Ду5 Ру250: 10 шт × ?; Вентиль ВИГ-6С-Н1Б1Б Ду5 Ру6: 5 шт × ?; Клапан запорный 15с27нж Ду25: 5 шт × ?; Клапан обратный 19лс53нж Ду100 Ру16: 1 шт × ?; Клапан обратный 19ч16бр Ду100 Ру16: 6 шт × ?; Клапан 15с22нж Ду50 с КОФ: 8 шт × ?; Вентиль 14с17п30-1 Ду50 Ру10: 4 шт × ?; … ещё 11 (цена за ед. = НМЦК / кол-во)</t>
+          <t>Пробирка вакуумная с активатором свертывания,: 150 000 шт × 19.68</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14831.39755905512</v>
+        <v>19.68</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1273942</v>
+        <v>1446500</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3236618915960203</v>
+        <v>0.5099932249322493</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>478689.8433488219</v>
+        <v>1178755.920547945</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>256336.1073293019</v>
+        <v>556474.3205479452</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -1035,23 +1035,27 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>14 760 ₽ (0.5%)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+          <t>5.00 % (≈147 600 ₽)</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ПАО «Т‑Плюс»</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[ГИПОТЕЗА по себестоимости] Цены по позициям в извещении не указаны: НМЦ лота задана одной суммой, документация (zip) на zakupki.gov.ru, доступа к ней нет, поэтому unit_nmck не указаны. У Т Плюс НМЦ часто указана без НДС — проверить; для УСН это важно. Около половины позиций (энергетические вентили ВТ-5, ВИГ, 15с27нж, 14с17п, </t>
+          <t>НМЦК 19,68 ₽ — вдвое выше рынка, поэтому ожидается сильное снижение (вероятно верхний квартиль скидки, 40–55%). Особенность крышки (полнозаходная резьба / двухступенчатое снятие) — нужно подтвердить, что UNIVAC/другая российская пробирка этому соответствует, иначе отклонение. СМП-only. Минимальный о</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1067,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32616450774</t>
+          <t>32616442935</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>МУП «Уфимские инженерные сети» ГО г. Уфа</t>
+          <t>ПАО «Т Плюс», филиал «Нижегородский»</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Изделия в ППУ изоляции</t>
+          <t>Запорная арматура стальная (ТЭЦ)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1083,34 +1087,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.10.2026 12:00 МСК</t>
+          <t>16.10.2026 14:00 МСК</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>639848.52</v>
+        <v>1883587.49</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Отвод Ст 108х4,5-90-1-ППУ-ПЭ: 3 шт × ?; Отвод Ст 377х8-90-1-ППУ-ПЭ: 2 шт × ?; Отвод Ст 426х8-90-1-ППУ-ПЭ: 3 шт × ?; Отвод Ст 530х9,0-90-1-ППУ-ПЭ: 1 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+          <t>Вентиль ВТ-5 Ду10 Ру250: 10 шт × ?; Вентиль ВИГ-250Д-Н1Б1Г Ду5 Ру250: 10 шт × ?; Вентиль ВИГ-6С-Н1Б1Б Ду5 Ру6: 5 шт × ?; Клапан запорный 15с27нж Ду25: 5 шт × ?; Клапан обратный 19лс53нж Ду100 Ру16: 1 шт × ?; Клапан обратный 19ч16бр Ду100 Ру16: 6 шт × ?; Клапан 15с22нж Ду50 с КОФ: 8 шт × ?; Вентиль 14с17п30-1 Ду50 Ру10: 4 шт × ?; … ещё 11 (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>71094.28</v>
+        <v>14831.39755905512</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>373458.9</v>
+        <v>1273942</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.4163323219064412</v>
+        <v>0.3236618915960203</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>216862.0142146849</v>
+        <v>478689.8433488219</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>189886.000611485</v>
+        <v>256336.1073293019</v>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
@@ -1135,34 +1139,34 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Российская электронная система торгов</t>
+          <t>ПАО «Т‑Плюс»</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Цены по позициям не указаны в извещении; длины плеч, диаметр оболочки и наличие проводников ОДК — в документах (недоступны). Тяжёлый груз (426/530 — по 200–300 кг), доставка в Уфу — оценка 45 тыс. Уфимские производители ППУ (например, местные заводы) имеют логистическое преимущество. Не СМП-закупка.</t>
+          <t xml:space="preserve">[ГИПОТЕЗА по себестоимости] Цены по позициям в извещении не указаны: НМЦ лота задана одной суммой, документация (zip) на zakupki.gov.ru, доступа к ней нет, поэтому unit_nmck не указаны. У Т Плюс НМЦ часто указана без НДС — проверить; для УСН это важно. Около половины позиций (энергетические вентили ВТ-5, ВИГ, 15с27нж, 14с17п, </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Сантехника и ЖКХ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32616447145</t>
+          <t>32616450774</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>АО «Пассажирречтранс»</t>
+          <t>МУП «Уфимские инженерные сети» ГО г. Уфа</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Изделия в ППУ изоляции</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1172,34 +1176,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.10.2026 05:00 МСК (09:00 местн.)</t>
+          <t>20.10.2026 12:00 МСК</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>450798.91</v>
+        <v>639848.52</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Кабель судовой КНР и КНРЭ (ГОСТ 7866.1-76), с: 1 730 м × 260.58</t>
+          <t>Отвод Ст 108х4,5-90-1-ППУ-ПЭ: 3 шт × ?; Отвод Ст 377х8-90-1-ППУ-ПЭ: 2 шт × ?; Отвод Ст 426х8-90-1-ППУ-ПЭ: 3 шт × ?; Отвод Ст 530х9,0-90-1-ППУ-ПЭ: 1 шт × ? (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>260.5774046242774</v>
+        <v>71094.28</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>281420</v>
+        <v>373458.9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3757305225072527</v>
+        <v>0.4163323219064412</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>136974.4710489863</v>
+        <v>216862.0142146849</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>68554.01568482628</v>
+        <v>189886.000611485</v>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
@@ -1208,7 +1212,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>есть, размер в документации</t>
+          <t>нет / не указан</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1221,41 +1225,37 @@
           <t>не установлено / не указано</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>Российская электронная система торгов</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
+          <t>[ГИПОТЕЗА по себестоимости] Цены по позициям не указаны в извещении; длины плеч, диаметр оболочки и наличие проводников ОДК — в документах (недоступны). Тяжёлый груз (426/530 — по 200–300 кг), доставка в Уфу — оценка 45 тыс. Уфимские производители ППУ (например, местные заводы) имеют логистическое преимущество. Не СМП-закупка.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0372100027326000601</t>
+          <t>0318300100526000186</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение «Администрация Волго-Балтийского бассейна внутренних водных путей»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "ТИХОРЕЦКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА" МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ КРАСНОДАРСКОГО КРАЯ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Поставка средств индивидуальной защиты, приобретаемых для нужд ФБУ «Администрация «Волго-Балт» (44-ФЗ)</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1265,40 +1265,38 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-13 10:00</t>
+          <t>20.10.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>18033874.9</v>
+        <v>597406</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Костюм для защиты от термических рисков элект: 1 КОМПЛ × 4 865.60; Строп одинарный регулируемый огнеупорный: 4 шт × 2 379.09; Каска защитная белая: 31 шт × 551.06; Гибкая анкерная линия (20 м): 2 шт × 2 765.56; Наколенники: 15 пар × 871.08; Белье нательное термостойкое: 192 КОМПЛ × 1 741.12; Одежда специальная повышенной видимости: 18 шт × 142.69; Обувь специальная кожаная для защиты от механ: 72 пар × 2 125.85; … ещё 126</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
+          <t>Пробирка вакуумная для взятия образцов крови : 4 600 шт × 21.10; Пробирка вакуумная для взятия образцов крови : 19 800 шт × 25.27</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>24.48385245901639</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13525406.175</v>
+        <v>268387</v>
       </c>
       <c r="K9" s="4" t="n">
+        <v>0.5507460587941869</v>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L9" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M9" s="2" t="n">
-        <v>2571289.646392574</v>
+        <v>256478.458049315</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2571289.646392574</v>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>130545.2732493151</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1308,12 +1306,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>180 339 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>10.00 % (≈1 803 387 ₽)</t>
+          <t>5.00 % (≈29 870 ₽)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1323,34 +1321,34 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-06-16.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0358200022926000030</t>
+          <t>0318300137626000327</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ГКУ Ростовской обл. «Ростовская областная поисково-спасательная служба»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КУРГАНИНСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА" МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ КРАСНОДАРСКОГО КРАЯ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Поставка обмундирования</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1360,40 +1358,38 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00</t>
+          <t>14.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6224420.7</v>
+        <v>596407.5</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Костюм спасателя зимний (куртка, брюки утепле: 168 КОМПЛ × 7 698.83; Костюм спасателя летний (куртка, брюки, кепка: 241 КОМПЛ × 6 613.44; Комбинезон спасателя зимний, шт.: 208 шт × 7 565.57; Комбинезон спасателя летний, шт.: 239 шт × 6 542.14; Футболка форменная, шт.: 268 шт × 746.15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
+          <t>Пробирка вакуумная для взятия образцов крови : 20 000 шт × 21.40; Пробирка вакуумная для взятия образцов крови : 7 750 шт × 21.73</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>21.49216216216216</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4668315.525</v>
+        <v>261668.5</v>
       </c>
       <c r="K10" s="4" t="n">
+        <v>0.5612588708223823</v>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L10" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M10" s="2" t="n">
-        <v>887484.7246889586</v>
+        <v>256097.979</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>887484.7246889586</v>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>130375.278</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1403,12 +1399,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>62 244 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10.00 % (≈622 442 ₽)</t>
+          <t>5.00 % (≈29 820 ₽)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1418,75 +1414,75 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-30.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32616443256</t>
+          <t>0318300137626000325</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ГБУ Республики Саха (Якутия) «Государственная Противопожарная Служба Республики Саха(Якутия)»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КУРГАНИНСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА" МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ КРАСНОДАРСКОГО КРАЯ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Поставка форменной одежды для нужд ГБУ РС(Я) "ГПС РС(Я)"</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00</t>
+          <t>14.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4999001.85</v>
+        <v>595655</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Костюм летний полевой: 405 Комплект × ?; Зимняя форменная одежда мужская: 150 Комплект × ? (цена за ед. = НМЦК / кол-во)</t>
+          <t>Пробирка вакуумная для взятия образцов крови : 6 500 шт × 21.40; Пробирка вакуумная для взятия образцов крови : 7 500 шт × 21.73; Пробирка вакуумная для взятия образцов крови : 14 000 шт × 20.97</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>9007.21054054054</v>
+        <v>21.27339285714286</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3749251.3875</v>
+        <v>263719</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>0.5572621735736291</v>
+      </c>
+      <c r="L11" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L11" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M11" s="2" t="n">
-        <v>712763.1621311915</v>
+        <v>253529.5405205479</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>712763.1621311915</v>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>127965.466520548</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1501,7 +1497,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>5.00 % (≈29 783 ₽)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1511,75 +1507,75 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Центр Закупок Республики Саха (Якутия)</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-30.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32616438570</t>
+          <t>0318300502726000085</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ООО «Теплоэнергетическая Компания - 2»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "ГОРОДСКАЯ ПОЛИКЛИНИКА № 5 ГОРОДА КРАСНОДАРА" МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ КРАСНОДАРСКОГО КРАЯ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Поставка зимней спецодежды</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00</t>
+          <t>13.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4810413.58</v>
+        <v>600000</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; Костюм сварщика со спилком утепленный: 20 Штука × ?; Костюм женский утепленный: 41 Штука × ?; Костюм зимний мужской для защиты от термическ: 28 Штука × ?; Куртка охранника зимняя: 46 Штука × ?; Брюки охранника зимние: 46 Штука × ?; Шеврон на липучке для спецодежды: 46 Штука × ?; Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; … ещё 6 (цена за ед. = НМЦК / кол-во)</t>
+          <t>Пробирка вакуумная для взятия образцов крови : 10 241 шт × 19.69; Пробирка вакуумная для взятия образцов крови : 10 241 шт × 19.53; Пробирка вакуумная для взятия образцов крови : 10 241 шт × 19.37</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3891.920372168285</v>
+        <v>19.52934283761351</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3607810.185</v>
+        <v>289910.63</v>
       </c>
       <c r="K12" s="4" t="n">
+        <v>0.5168318752740636</v>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M12" s="2" t="n">
-        <v>685874.0399225147</v>
+        <v>250061.1078943013</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>685874.0399225147</v>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>123576.8518423013</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1594,7 +1590,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>5.00 % (≈30 000 ₽)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1604,73 +1600,75 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК/Σцен ед. поровну по позициям. Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-31.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ГП622514</t>
+          <t>0318300137626000328</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>АО «Арго»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КУРГАНИНСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА" МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ КРАСНОДАРСКОГО КРАЯ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Закупка спецодежды, обуви и средств индивидуальной защиты</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Коммерческие</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00</t>
+          <t>14.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4000000</v>
+        <v>583162.5</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n"/>
+          <t>Пробирка вакуумная для взятия образцов крови : 10 750 шт × 21.40; Пробирка вакуумная для взятия образцов крови : 16 250 шт × 21.73</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>21.59861111111111</v>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>3000000</v>
+        <v>260474.5</v>
       </c>
       <c r="K13" s="4" t="n">
+        <v>0.5533414785758687</v>
+      </c>
+      <c r="L13" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M13" s="2" t="n">
-        <v>570324.3835616438</v>
+        <v>246055.9169178082</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>570324.3835616438</v>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>123125.2619178082</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1685,83 +1683,85 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+          <t>5.00 % (≈29 158 ₽)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-30.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32616402062</t>
+          <t>0352200022726000839</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>МУП «Управление Городского Хозяйства» Муниципального Образования Города Пыть-Ях</t>
+          <t>БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ОМСКОЙ ОБЛАСТИ "КЛИНИЧЕСКИЙ ОНКОЛОГИЧЕСКИЙ ДИСПАНСЕР"</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Поставка специальных обуви, одежды, головных уборов, рукавиц и краг</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-13 06:00</t>
+          <t>15.10.2026 05:00 МСК</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3857857.45</v>
+        <v>500000</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Ботинки кожаные утепленные: 46 Пара (2 шт.) × ?; Сапоги кожаные утепленные: 185 Пара (2 шт.) × ?; Сапоги утепленные "Надым" ТХ-011р/п с КП и АС: 21 Пара (2 шт.) × ?; Валенки с резиновым низом: 40 Пара (2 шт.) × ?; Костюм сварщика утепленный (4 класс защиты): 8 Штука × ?; Костюм от пониженных температур (4 класс защи: 115 Штука × ?; Костюм сигнальный с водоотталкивающей пропитк: 41 Штука × ?; Костюм зимний петролеум плюс куртка-П/К, Т.Си: 21 Штука × ?; … ещё 18</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
+          <t>Пробирка вакуумная для взятия образцов крови : 3 502 шт × 23.97; Пробирка вакуумная для взятия образцов крови : 3 502 шт × 21.55; Пробирка вакуумная для взятия образцов крови : 3 502 шт × 24.33; Пробирка вакуумная для взятия образцов крови : 3 502 шт × 21.88; Пробирка вакуумная для взятия образцов крови : 3 502 шт × 27.77; Пробирка вакуумная для взятия образцов крови : 3 502 шт × 23.28</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>23.79592613744527</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2893393.0875</v>
+        <v>209355.28</v>
       </c>
       <c r="K14" s="4" t="n">
+        <v>0.5813024698671377</v>
+      </c>
+      <c r="L14" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M14" s="2" t="n">
-        <v>550057.5430099862</v>
+        <v>224159.5444659726</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>550057.5430099862</v>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>118756.2644179726</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>10.00 % (≈50 000 ₽)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1791,72 +1791,70 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК/Σцен ед. поровну по позициям. Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-31. Нужна винтовая или двухступенчатая (поворотная) кр</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32616431081</t>
+          <t>0318300137626000329</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КУРГАНИНСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА" МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ КРАСНОДАРСКОГО КРАЯ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Поставка спецодежды</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00</t>
+          <t>14.10.2026 08:00 МСК</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3637476.36</v>
+        <v>564980</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Жилет сигнальный: 14 Штука × ?; Жилет утепленный: 64 Штука × ?; Костюм летний  мужской противоэнцэфалитный: 1 Комплект × ?; Костюм летний мужской для защиты от механичес: 23 Комплект × ?; Костюм летний женский для защиты от механичес: 1 Комплект × ?; Куртка зимняя мужской для защиты от механичес: 20 Штука × ?; Полукомбинезон зимний мужской для защиты от м: 20 Штука × ?; Костюм летний мужской сигнальный флуоресцентн: 4 Комплект × ?; … ещё 28</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
+          <t>Пробирка вакуумная для взятия образцов крови : 26 000 шт × 21.73</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>21.73</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2728107.27</v>
+        <v>257814</v>
       </c>
       <c r="K15" s="4" t="n">
+        <v>0.5436758823321179</v>
+      </c>
+      <c r="L15" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L15" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M15" s="2" t="n">
-        <v>518635.365684263</v>
+        <v>233233.6853150685</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>518635.365684263</v>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>114135.9013150685</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1871,81 +1869,85 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
+          <t>5.00 % (≈28 249 ₽)</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-30.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32616448893</t>
+          <t>0318300299426000956</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Московской обл. «Мособллес»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "ЕЙСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА" МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ КРАСНОДАРСКОГО КРАЯ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Поставка обуви специальной для защиты от механических воздействий</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00</t>
+          <t>13.10.2026 10:00 МСК</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2511958.68</v>
+        <v>599999</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ?; Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ? (цена за ед. = НМЦК / кол-во)</t>
+          <t>Пробирка вакуумная для взятия образцов крови : 8 396 шт × 17.42; Пробирка вакуумная для взятия образцов крови : 8 396 шт × 19.40; Пробирка вакуумная для взятия образцов крови : 8 396 шт × 17.49; Пробирка вакуумная для взятия образцов крови : 8 396 шт × 17.15</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3171.665</v>
+        <v>17.86562053358742</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1883969.01</v>
+        <v>326283.84</v>
       </c>
       <c r="K16" s="4" t="n">
+        <v>0.4561738047264921</v>
+      </c>
+      <c r="L16" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M16" s="2" t="n">
-        <v>358157.8214258302</v>
+        <v>218074.5412155617</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>358157.8214258302</v>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>91599.14508756166</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1960,7 +1962,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>125 598 ₽ (5.0%)</t>
+          <t>10.00 % (≈60 000 ₽)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1970,34 +1972,34 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК/Σцен ед. поровну по позициям. Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-30.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32616427138</t>
+          <t>32616447145</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
+          <t>АО «Пассажирречтранс»</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Поставка спецодежды для защиты от термических рисков электрической дуги</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2007,45 +2009,43 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00</t>
+          <t>16.10.2026 05:00 МСК (09:00 местн.)</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1477969</v>
+        <v>450798.91</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Костюм летний для защиты от термических риско: 15 Комплект × ?; Костюм зимний для защиты от термических риско: 8 Комплект × ?; Куртка-рубашка для защиты от термических риск: 11 Штука × ?; Куртка-накидка для защиты от термических риск: 10 Штука × ?; Плащ термостойкий для защиты от термических р: 1 Штука × ?; Бельё нательное (фуфайка): 26 Штука × ?; Бельё нательное (кальсоны): 26 Штука × ?; Бельё нательное утепленное (фуфайка): 12 Штука × ?; … ещё 12</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
+          <t>Кабель судовой КНР и КНРЭ (ГОСТ 7866.1-76), с: 1 730 м × 260.58</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>260.5774046242774</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1108476.75</v>
+        <v>281420</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.25</v>
+        <v>0.3757305225072527</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>210730.4397120549</v>
+        <v>136974.4710489863</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>210730.4397120549</v>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>68554.01568482628</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>нет / не указан</t>
+          <t>есть, размер в документации</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2058,76 +2058,82 @@
           <t>не установлено / не указано</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>[ГИПОТЕЗА по себестоимости] Сечения и доля КНРЭ неизвестны — себестоимость гипотетична. Розничные цены агрегаторов (Рукабель, kabel-s) 170–440 ₽/м выше средней НМЦК 260,6 ₽/м → если в лоте 3х2,5 и крупнее, маржи может не быть; реально только при цене завода (Кольчугино/Рыбинсккабель/Камкабель) ~126–154 ₽/м за 3х2,5 и малых сеч</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10749746</t>
+          <t>0860200000826008096</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Боханский Аграрный Техникум»</t>
+          <t>ГОСУДАРСТВЕННОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ САРАТОВСКОЙ ОБЛАСТИ "ПУГАЧЕВСКАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря, индивидуальная одежда и обувь для каждого студента. согласно спецификации и списка размеров.</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00</t>
+          <t>15.10.2026 07:00 МСК</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>498000</v>
+        <v>599072</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
+          <t>Пробирка вакуумная для взятия образцов крови : 13 468 шт × 15.90; Пробирка вакуумная для взятия образцов крови : 13 468 шт × 14.38; Пробирка вакуумная для взятия образцов крови : 13 468 шт × 14.20</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>14.82704682704683</v>
+      </c>
       <c r="J18" s="2" t="n">
-        <v>373500</v>
+        <v>378413.24</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>0.3683180942623389</v>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L18" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M18" s="2" t="n">
-        <v>71005.38575342466</v>
+        <v>171312.2437378631</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>71005.38575342466</v>
-      </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>45031.104025863</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2142,7 +2148,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>5.00 % (≈29 954 ₽)</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2152,34 +2158,34 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК/Σцен ед. поровну по позициям. Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-29. Крышка: двухступенчатое снятие или винтовая — уточ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0173200001426002006</t>
+          <t>0816500000626015179</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Московская Административная Дорожная Инспекция</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ РЕСПУБЛИКИ САХА (ЯКУТИЯ) "СУНТАРСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Поставка форменной одежды</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2189,38 +2195,38 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>13.10.2026 03:30 МСК</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>435666.4</v>
+        <v>288450</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Термобелье спортивное, для взрослого: 2 шт × 6 100; Шорты: 2 шт × 4 266.67; Термобелье спортивное, для взрослого: 4 шт × 5 033.33; Футболка трикотажная: 2 шт × 1 033.33; Футболка трикотажная: 8 шт × 1 033.33; Шорты: 4 шт × 4 266.67; Шорты: 6 шт × 4 266.67; Шорты: 6 шт × 4 266.67; … ещё 29</t>
+          <t>Пробирка вакуумная для взятия образцов крови : 15 000 шт × 19.23</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2562.743529411765</v>
+        <v>19.23</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>326749.8</v>
+        <v>174103</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0.3964187900849367</v>
+      </c>
+      <c r="L19" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L19" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M19" s="2" t="n">
-        <v>62117.79275463011</v>
+        <v>88340.91917808219</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>62117.79275463011</v>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>27535.65917808219</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2230,88 +2236,86 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4 357 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>5.00 % (≈21 783 ₽)</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-01-31. Доставка в Якутию.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10747873</t>
+          <t>0829500001126006592</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "СРЕДНЕАХТУБИНСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
+          <t>Контейнеры для биоматериала</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-14 11:20</t>
+          <t>13.10.2026 06:00 МСК</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>402140</v>
+        <v>195930</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
+          <t>Контейнер для сбора проб мочи ИВД (22.22.14.0: 6 000 шт × 19.42; Контейнер для сбора кала ИВД, без добавок (22: 3 000 шт × 17.47; Пробирка центрифужная ИВД (32.50.50.000-00001: 2 000 шт × 13.50</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>17.81181818181818</v>
+      </c>
       <c r="J20" s="2" t="n">
-        <v>301605</v>
+        <v>98400</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4175102113301367</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>57337.56190136987</v>
+        <v>55593.6664109589</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>57337.56190136987</v>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>25680.89345095892</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2326,79 +2330,85 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+          <t>30.00 % (≈58 779 ₽)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Только СМП. Срок контракта до 2026-12-31. Позиции вне профиля (себестоимость не дана): Пробирка центрифужная ИВД Позиция «Пробирка центрифужная ИВД» (2000 шт × 13,50) — не наш товар, себестоимость не дана. Контейнер для мочи 100–150 мл, высота 66–89 мм, диаметр 49–66 мм — проверить, что Перинт 120 м</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10747880</t>
+          <t>0119200000126017137</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
+          <t>КРАЕВОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КРАСНОЯРСКИЙ КРАЕВОЙ ВРАЧЕБНО-ФИЗКУЛЬТУРНЫЙ ДИСПАНСЕР"</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-14 11:20</t>
+          <t>16.10.2026 04:00 МСК</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>402140</v>
+        <v>123000</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
+          <t>Пробирка вакуумная для взятия образцов крови : 6 000 шт × 20.50</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>20.5</v>
+      </c>
       <c r="J21" s="2" t="n">
-        <v>301605</v>
+        <v>61230</v>
       </c>
       <c r="K21" s="4" t="n">
+        <v>0.5021951219512195</v>
+      </c>
+      <c r="L21" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L21" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M21" s="2" t="n">
-        <v>57337.56190136987</v>
+        <v>49529.24383561643</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>57337.56190136987</v>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>23600.84383561644</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2413,10 +2423,14 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>5.00 % (≈6 150 ₽)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
@@ -2424,29 +2438,29 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до ?. Объём 9 мл — обычно это формат 16×100; у UNIVAC 9 мл может не быть, цена 13×100 условная.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Медрасходники</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0358300160926000018</t>
+          <t>0367100026526000082</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>МКУ «Управление по Делам Гражданской Обороны, Предупреждения и Ликвидации Чрезвычайных Ситуаций Города Каменск-Шахтинский»</t>
+          <t>ФЕДЕРАЛЬНОЕ КАЗЕННОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "МЕДИКО-САНИТАРНАЯ ЧАСТЬ № 72 ФЕДЕРАЛЬНОЙ СЛУЖБЫ ИСПОЛНЕНИЯ НАКАЗАНИЙ"</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Поставка специальной одежды</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2456,40 +2470,38 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>15.10.2026 10:00 МСК</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>320700.06</v>
+        <v>207167</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Ботинки с высокими берцами зимние: 18 пар × 5 400; Футболка поло с длинным рукавом: 18 шт × 2 800; Головной убор зимний: 18 шт × 750; Костюм спасателя мужской зимний: 18 шт × 8 866.67</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
+          <t>Пробирка вакуумная для взятия образцов крови : 8 100 шт × 15.93; Пробирка вакуумная для взятия образцов крови : 5 500 шт × 13.94; Пробирка вакуумная для взятия образцов крови : 100 шт × 14.64</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>15.12167883211679</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>240525.045</v>
+        <v>134490</v>
       </c>
       <c r="K22" s="4" t="n">
+        <v>0.3508135948292923</v>
+      </c>
+      <c r="L22" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L22" s="4" t="n">
-        <v>0.05</v>
-      </c>
       <c r="M22" s="2" t="n">
-        <v>45725.76600692053</v>
+        <v>55981.97193424658</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>45725.76600692053</v>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>Участвовать, если ≤2 заявок</t>
+        <v>12311.16833424657</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2504,14 +2516,10 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>5.00 % (≈16 035 ₽)</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+          <t>10 358 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
@@ -2519,7 +2527,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2026-12-31.</t>
         </is>
       </c>
     </row>
@@ -2531,17 +2539,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0301300019426000247</t>
+          <t>0372100027326000601</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ГБУЗ Республиканский Клинический Госпиталь Ветеранов Войн им. М.В. Каменева</t>
+          <t>Федеральное бюджетное учреждение «Администрация Волго-Балтийского бассейна внутренних водных путей»</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Поставка спецодежды</t>
+          <t>Поставка средств индивидуальной защиты, приобретаемых для нужд ФБУ «Администрация «Волго-Балт» (44-ФЗ)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2551,22 +2559,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00</t>
+          <t>2026-10-13 10:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>270651</v>
+        <v>18033874.9</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Костюм мужской рабочий  (96/170): 1 шт × 4 857; Костюм мужской рабочий  (104/165): 1 шт × 4 857; Костюм мужской рабочий  (104/176): 2 шт × 4 857; Костюм мужской рабочий  (108/170): 3 шт × 4 857; Костюм мужской рабочий  (108/176): 3 шт × 4 857; Костюм мужской рабочий  (112/170): 2 шт × 4 857; Костюм мужской рабочий  (112/176): 1 шт × 4 857; Костюм мужской рабочий  (96/158): 1 шт × 5 600; … ещё 29</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>5012.055555555556</v>
+          <t>Костюм для защиты от термических рисков элект: 1 КОМПЛ × 4 865.60; Строп одинарный регулируемый огнеупорный: 4 шт × 2 379.09; Каска защитная белая: 31 шт × 551.06; Гибкая анкерная линия (20 м): 2 шт × 2 765.56; Наколенники: 15 пар × 871.08; Белье нательное термостойкое: 192 КОМПЛ × 1 741.12; Одежда специальная повышенной видимости: 18 шт × 142.69; Обувь специальная кожаная для защиты от механ: 72 пар × 2 125.85; … ещё 126</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>202988.25</v>
+        <v>13525406.175</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>0.25</v>
@@ -2575,10 +2585,10 @@
         <v>0.05</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>38589.7161838356</v>
+        <v>2571289.646392574</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>38589.7161838356</v>
+        <v>2571289.646392574</v>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
@@ -2592,18 +2602,22 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1 353 ₽ (0.5%)</t>
+          <t>180 339 ₽ (1.0%)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>27 065 ₽ (10.0%)</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+          <t>10.00 % (≈1 803 387 ₽)</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2620,17 +2634,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0302200020326000023</t>
+          <t>0358200022926000030</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Республиканская служба по охране, контролю и регулированию использования объектов животного мира, отнесенных к объектам охоты, контролю и надзору в сфере природопользования</t>
+          <t>ГКУ Ростовской обл. «Ростовская областная поисково-спасательная служба»</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Поставка спецобуви</t>
+          <t>Поставка обмундирования</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2640,22 +2654,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-14 04:00</t>
+          <t>2026-10-19 09:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>230181</v>
+        <v>6224420.7</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Ботинки специальные с высокими берцами зимние: 18 пар × 3 639; Ботинки специальные с высокими берцами: 17 пар × 8 299; Обувь демисезонная: 4 пар × 5 899</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>5902.076923076923</v>
+          <t>Костюм спасателя зимний (куртка, брюки утепле: 168 КОМПЛ × 7 698.83; Костюм спасателя летний (куртка, брюки, кепка: 241 КОМПЛ × 6 613.44; Комбинезон спасателя зимний, шт.: 208 шт × 7 565.57; Комбинезон спасателя летний, шт.: 239 шт × 6 542.14; Футболка форменная, шт.: 268 шт × 746.15</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>172635.75</v>
+        <v>4668315.525</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.25</v>
@@ -2664,10 +2680,10 @@
         <v>0.05</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>32819.45923315067</v>
+        <v>887484.7246889586</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>32819.45923315067</v>
+        <v>887484.7246889586</v>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
@@ -2681,12 +2697,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>62 244 ₽ (1.0%)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.00 % (≈2 302 ₽)</t>
+          <t>10.00 % (≈622 442 ₽)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2696,7 +2712,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2713,42 +2729,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0340100009726000070</t>
+          <t>32616443256</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Федеральное государственное бюджетное Профессиональное Образовательное учреждение «Орловское Специальное Учебно-Воспитательное Учреждение Закрытого Типа»</t>
+          <t>ГБУ Республики Саха (Якутия) «Государственная Противопожарная Служба Республики Саха(Якутия)»</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Поставка зимней одежды для воспитанников (термобелье)</t>
+          <t>Поставка форменной одежды для нужд ГБУ РС(Я) "ГПС РС(Я)"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-15 08:30</t>
+          <t>2026-10-15 05:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>213567.9</v>
+        <v>4999001.85</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 4 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 3 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; … ещё 29</t>
+          <t>Костюм летний полевой: 405 Комплект × ?; Зимняя форменная одежда мужская: 150 Комплект × ? (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2033.98</v>
+        <v>9007.21054054054</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>160175.925</v>
+        <v>3749251.3875</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>0.25</v>
@@ -2757,10 +2773,10 @@
         <v>0.05</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>30450.74522901369</v>
+        <v>712763.1621311915</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>30450.74522901369</v>
+        <v>712763.1621311915</v>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
@@ -2774,12 +2790,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2 136 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10.00 % (≈21 357 ₽)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2789,7 +2805,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>Центр Закупок Республики Саха (Якутия)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2806,17 +2822,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32616452815</t>
+          <t>32616438570</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Здравоохранения «Городская Больница № 2 г. Магнитогорск»</t>
+          <t>ООО «Теплоэнергетическая Компания - 2»</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Поставка комплектов зимней спецодежды и рукавиц</t>
+          <t>Поставка зимней спецодежды</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2826,24 +2842,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00</t>
+          <t>2026-10-14 08:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>187355.52</v>
+        <v>4810413.58</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Костюм утепленный Ангара: 16 Комплект × ?; Рукавицы утепленные G14: 16 Пара (2 шт.) × ?</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
+          <t>Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; Костюм сварщика со спилком утепленный: 20 Штука × ?; Костюм женский утепленный: 41 Штука × ?; Костюм зимний мужской для защиты от термическ: 28 Штука × ?; Куртка охранника зимняя: 46 Штука × ?; Брюки охранника зимние: 46 Штука × ?; Шеврон на липучке для спецодежды: 46 Штука × ?; Костюм мужской для защиты от пониженных темпе: 391 Штука × ?; … ещё 6 (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>3891.920372168285</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>140516.64</v>
+        <v>3607810.185</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0.25</v>
@@ -2852,10 +2866,10 @@
         <v>0.05</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>26713.3553627178</v>
+        <v>685874.0399225147</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>26713.3553627178</v>
+        <v>685874.0399225147</v>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
@@ -2884,7 +2898,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Информационная система "Управление закупками отдельными видами юридических лиц"</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2901,31 +2915,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>295997-26LO</t>
+          <t>ГП622514</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>МКУ «Городское Хозяйство» Муниципального Образования Волосовское Городское Поселение Волосовского Муниципального Района Ленинградской Области</t>
+          <t>АО «Арго»</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Поставка товаров согласно Спецификации (Специальная одежда и обувь)</t>
+          <t>Закупка спецодежды, обуви и средств индивидуальной защиты</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Малые закупки</t>
+          <t>Коммерческие</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-13 10:30</t>
+          <t>2026-10-15 17:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>152190</v>
+        <v>4000000</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2948,7 @@
       </c>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n">
-        <v>114142.5</v>
+        <v>3000000</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>0.25</v>
@@ -2943,10 +2957,10 @@
         <v>0.05</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21699.41698356164</v>
+        <v>570324.3835616438</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>21699.41698356164</v>
+        <v>570324.3835616438</v>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
@@ -2971,7 +2985,7 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Электронный Магазин Ленинградской области</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2988,40 +3002,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1022079</t>
+          <t>32616402062</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Краевое ГКУ Для Детей-Сирот и Детей, Оставшихся без Попечения Родителей «Шушенский Детский Дом»</t>
+          <t>МУП «Управление Городского Хозяйства» Муниципального Образования Города Пыть-Ях</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Закупка одежды</t>
+          <t>Поставка специальных обуви, одежды, головных уборов, рукавиц и краг</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Коммерческие</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00</t>
+          <t>2026-10-13 06:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>114000</v>
+        <v>3857857.45</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n"/>
+          <t>Ботинки кожаные утепленные: 46 Пара (2 шт.) × ?; Сапоги кожаные утепленные: 185 Пара (2 шт.) × ?; Сапоги утепленные "Надым" ТХ-011р/п с КП и АС: 21 Пара (2 шт.) × ?; Валенки с резиновым низом: 40 Пара (2 шт.) × ?; Костюм сварщика утепленный (4 класс защиты): 8 Штука × ?; Костюм от пониженных температур (4 класс защи: 115 Штука × ?; Костюм сигнальный с водоотталкивающей пропитк: 41 Штука × ?; Костюм зимний петролеум плюс куртка-П/К, Т.Си: 21 Штука × ?; … ещё 18</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n">
-        <v>85500</v>
+        <v>2893393.0875</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>0.25</v>
@@ -3030,10 +3048,10 @@
         <v>0.05</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>16254.24493150685</v>
+        <v>550057.5430099862</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>16254.24493150685</v>
+        <v>550057.5430099862</v>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
@@ -3055,10 +3073,14 @@
           <t>не установлено / не указано</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3070,63 +3092,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0348300075526000435</t>
+          <t>32616431081</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ГБУЗ МО «Королёвская клиническая больница» (ЦКДЛ), лот 7</t>
+          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Контейнеры вакуумные для мочи</t>
+          <t>Поставка спецодежды</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19.10.2026 10:00 МСК</t>
+          <t>2026-10-19 08:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1500000</v>
+        <v>3637476.36</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Контейнер вакуумный для мочи 10 мл, 15–16х100: 21 667 шт × 20.64; Контейнер вакуумный для мочи 6,5–7 мл, 13х100: 21 667 шт × 10.66; Контейнер вакуумный для мочи 9–9,5 мл, 16х100: 21 667 шт × 22.70; Контейнер вакуумный для мочи 9,5 мл, 16х100, : 21 667 шт × 15.23</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>17.30742603959939</v>
+          <t>Жилет сигнальный: 14 Штука × ?; Жилет утепленный: 64 Штука × ?; Костюм летний  мужской противоэнцэфалитный: 1 Комплект × ?; Костюм летний мужской для защиты от механичес: 23 Комплект × ?; Костюм летний женский для защиты от механичес: 1 Комплект × ?; Куртка зимняя мужской для защиты от механичес: 20 Штука × ?; Полукомбинезон зимний мужской для защиты от м: 20 Штука × ?; Костюм летний мужской сигнальный флуоресцентн: 4 Комплект × ?; … ещё 28</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1087916.66</v>
+        <v>2728107.27</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2747222266666667</v>
+        <v>0.25</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>279266.7297835617</v>
+        <v>518635.365684263</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>253970.7297835617</v>
+        <v>518635.365684263</v>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3136,45 +3160,45 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>15 000 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>150 000 ₽ (10.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Сантехника и ЖКХ</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32616451568</t>
+          <t>32616448893</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ПАО «Россети Центр и Приволжье» — филиал «Удмуртэнерго»</t>
+          <t>Государственное автономное учреждение Московской обл. «Мособллес»</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Запорная арматура</t>
+          <t>Поставка обуви специальной для защиты от механических воздействий</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3184,38 +3208,38 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>19.10.2026 09:00 МСК</t>
+          <t>2026-10-16 10:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>113094</v>
+        <v>2511958.68</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Задвижки (28.14.13.120), характеристики в док: 6 шт × ?; Затворы дисковые (28.14.13.132): 10 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+          <t>Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ?; Ботинки с высоким берцем утепленные: 396 Пара (2 шт.) × ? (цена за ед. = НМЦК / кол-во)</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7068.375</v>
+        <v>3171.665</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>84950</v>
+        <v>1883969.01</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2488549348329708</v>
+        <v>0.25</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>21966.38819726027</v>
+        <v>358157.8214258302</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>7662.259077260269</v>
+        <v>358157.8214258302</v>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3230,7 +3254,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>125 598 ₽ (5.0%)</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3240,75 +3264,77 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>РАД (Lot-Online)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Диаметры и типы неизвестны: ТЗ в rar на zakupki.gov.ru, доступа нет. Запрос котировок для МСП на ЭТП РАД (lot-online). Флаг нацрежима стоит → нужен российский производитель. Малый лот, логистика съедает маржу.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0387200029826000340</t>
+          <t>32616427138</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>БУ ХМАО-Югры «Нижневартовская окружная клиническая больница»</t>
+          <t>Федеральное бюджетное учреждение «Государственный Региональный Центр Стандартизации, Метрологии и Испытаний Им. А.М. Муратшина в Республике Башкортостан»</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные (8 видов)</t>
+          <t>Поставка спецодежды для защиты от термических рисков электрической дуги</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>16.10.2026 07:00 МСК</t>
+          <t>2026-10-15 08:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>900000</v>
+        <v>1477969</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная K2ЭДТА 2–? мл 13х75, кол-в: 8 154 шт × 12.86; Пробирка вакуумная цитрат 3,8% 3–? мл 13х75, : 8 154 шт × 12.87; Пробирка вакуумная тромбин 4,5 мл 13х75, кол-: 8 154 шт × 12.10; Пробирка вакуумная K-оксалат/NaF 4,5 мл 13х75: 8 154 шт × 14.72; Пробирка вакуумная активатор 5–? мл 13х(90–10: 8 154 шт × 14.67; Пробирка вакуумная цитрат 3,8% 4–? мл 13х75, : 8 154 шт × 12.88; Пробирка вакуумная K2ЭДТА 4–? мл 13х75, кол-в: 8 154 шт × 12.87; Пробирка вакуумная Li-гепарин 4–? мл 13х75, к: 8 154 шт × 17.40</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>13.79690949227373</v>
+          <t>Костюм летний для защиты от термических риско: 15 Комплект × ?; Костюм зимний для защиты от термических риско: 8 Комплект × ?; Куртка-рубашка для защиты от термических риск: 11 Штука × ?; Куртка-накидка для защиты от термических риск: 10 Штука × ?; Плащ термостойкий для защиты от термических р: 1 Штука × ?; Бельё нательное (фуфайка): 26 Штука × ?; Бельё нательное (кальсоны): 26 Штука × ?; Бельё нательное утепленное (фуфайка): 12 Штука × ?; … ещё 12</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>617434.5</v>
+        <v>1108476.75</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3139616666666666</v>
+        <v>0.25</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>190924.8400684932</v>
+        <v>210730.4397120549</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1204.840068493151</v>
+        <v>210730.4397120549</v>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3323,78 +3349,84 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>90 000 ₽ (10.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Количество не определено — qty условные (НМЦК/Σцен ед. поровну). Доставка в Нижневартовск (дорогая логистика). Контракт до 31.03.2027.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>32616445794</t>
+          <t>10749746</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Саратовский филиал</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Боханский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Приобретение мягкого инвентаря, индивидуальная одежда и обувь для каждого студента. согласно спецификации и списка размеров.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15.10.2026 12:00 МСК</t>
+          <t>2026-10-14 10:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2176178.2</v>
+        <v>498000</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>поз.1 ОКПД2 27.32.13.144 Кабели высоковольтны: 100 Метр × ?; поз.2 ОКПД2 27.32.13.111 Кабели силовые с мед: 300 Метр × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 0.07 Километр; тысяча метров × ?; поз.4 ОКПД2 27.32.13.111 Кабели силовые с мед: 120 Метр × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 50 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.22 Километр; тысяча метров × ?; поз.7 ОКПД2 27.32.13.124 Кабели силовые гибки: 1.30 Километр; тысяча метров × ?; поз.8 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; … ещё 10</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n">
+        <v>373500</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>71005.38575342466</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>71005.38575342466</v>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>есть, размер в документации</t>
+          <t>нет / не указан</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3407,154 +3439,178 @@
           <t>не установлено / не указано</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>РАД (Lot-Online)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>НМЦ 2 176 178,20 в ЕИС — БЕЗ НДС (rostender показывает 2 654 937 с НДС 22%). Клиент на УСН: уточнить в ДоЗ правило сравнения цен (у РусГидро обычно без НДС). Флаги нацрежима по всем 18 позициям = false (ЕИС), но ПП №1875 для 27.32 может быть указан в ДоЗ — проверить. Цены поставщиков не подобраны: н</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>32616445272</t>
+          <t>0173200001426002006</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Воткинский филиал</t>
+          <t>Московская Административная Дорожная Инспекция</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Поставка форменной одежды</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>15.10.2026 12:00 МСК</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1201357.95</v>
+        <v>435666.4</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>поз.1 ОКПД2 27.32.13.159 Кабели, провода и шн: 135 Метр × ?; поз.2 ОКПД2 27.32.13.131 Провода силовые для : 0.10 Километр; тысяча метров × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 100 Метр × ?; поз.4 ОКПД2 27.32.14.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 60 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 115 Метр × ?; поз.7 ОКПД2 27.32.13.111 Кабели силовые с мед: 100 Метр × ?; поз.8 ОКПД2 27.32.13.143 Кабели контрольные (: 0.20 Километр; тысяча метров × ?; … ещё 7</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+          <t>Термобелье спортивное, для взрослого: 2 шт × 6 100; Шорты: 2 шт × 4 266.67; Термобелье спортивное, для взрослого: 4 шт × 5 033.33; Футболка трикотажная: 2 шт × 1 033.33; Футболка трикотажная: 8 шт × 1 033.33; Шорты: 4 шт × 4 266.67; Шорты: 6 шт × 4 266.67; Шорты: 6 шт × 4 266.67; … ещё 29</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>2562.743529411765</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>326749.8</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>62117.79275463011</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>62117.79275463011</v>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>есть, размер в документации</t>
+          <t>нет / не указан</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>4 357 ₽ (1.0%)</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
+          <t>5.00 % (≈21 783 ₽)</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>РАД (Lot-Online)</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>НМЦ 1 201 357,95 без НДС (rostender: 1 465 656 с НДС). Флаги нацрежима false. Цены не подобраны — нет марок/сечений.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32616445510</t>
+          <t>10747873</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>АО «НИОПИК»</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Кабель (27.32)</t>
+          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14.10.2026 10:00 МСК</t>
+          <t>2026-10-14 11:20</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>529280.65</v>
+        <v>402140</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Кабель сигнальный КИМЭлВ-ЗГнг(А) (ОКПД2 27.32: 1 усл. ед. × 529 280.65</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>529280.65</v>
-      </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n">
+        <v>301605</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>есть, размер в документации</t>
+          <t>нет / не указан</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3567,11 +3623,7 @@
           <t>не установлено / не указано</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
@@ -3579,60 +3631,68 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Цена за метр не определена: неизвестны длина и конструкция. Ориентир по аналогам 1х2х0,75 (КПСнг(А)-FRHF, МКЭШВнг(А)-LS) 30–60 ₽/м с НДС — для КИМ неприменимо без спецификации. ЭТП РТС-тендер.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>32616449701</t>
+          <t>10747880</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>НАО «Центр «Омега» (Краснодарский край)</t>
+          <t>Государственное бюджетное Профессиональное Образовательное учреждение Иркутской обл. «Тулунский Аграрный Техникум»</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Приобретение мягкого инвентаря Подбор индивидуальный одежды и обуви для каждого воспитанника .В случае несоответствии размера произвести замену товара, не повторяющиеся модели с учетом выбора воспитанников</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16.10.2026 10:00 МСК</t>
+          <t>2026-10-14 11:20</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>3229618.2</v>
+        <v>402140</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Видеокамера тип 1 (26.40.33.111): 20 шт × ?; Видеокамера тип 2: 30 шт × ?; Видеокамера тип 3: 30 шт × ?; Видеокамера тип 4: 20 шт × ?; Аппаратура коммуникационная передающая (26.30: 1 шт × ?; Панели/комплекты электр. аппаратуры (27.12.31: 2 шт × ?; Приборы для телекоммуникаций (26.51.44, тесте: 1 шт × ?; … ещё 2 (цена за ед. = НМЦК / кол-во)</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>23923.09777777778</v>
-      </c>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n">
+        <v>301605</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>57337.56190136987</v>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3647,14 +3707,10 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>161 481 ₽ (5.0%)</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
@@ -3662,60 +3718,72 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Поставка (АЭФ только СМП), РТС-тендер Id=4056547. Монтаж в предмете не указан, но проверить проект договора. unit_nmck неизвестны → covered_nmck приравнен nmck условно, маржа по гипотезам ненадёжна. Нужна ручная выгрузка Обоснования НМЦД.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>32616433554</t>
+          <t>0358300160926000018</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>МКУ «Управление по Делам Гражданской Обороны, Предупреждения и Ликвидации Чрезвычайных Ситуаций Города Каменск-Шахтинский»</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Поставка специальной одежды</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14.10.2026 08:00 МСК</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>1675767</v>
+        <v>320700.06</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Видеокамера (26.40.33.111): 41 шт × ?; Части/принадлежности видеооборудования (кронш: 41 шт × ?; Части/принадлежности видеооборудования (короб: 41 шт × ?; Видеорегистратор: 2 шт × ?; Базовые системы хранения данных (HDD?): 16 шт × ? (цена за ед. = НМЦК / кол-во)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>11884.87234042553</v>
-      </c>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+          <t>Ботинки с высокими берцами зимние: 18 пар × 5 400; Футболка поло с длинным рукавом: 18 шт × 2 800; Головной убор зимний: 18 шт × 750; Костюм спасателя мужской зимний: 18 шт × 8 866.67</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>240525.045</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>45725.76600692053</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>45725.76600692053</v>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3730,7 +3798,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>83 788 ₽ (5.0%)</t>
+          <t>5.00 % (≈16 035 ₽)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3745,60 +3813,70 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>АЭФ только СМП, РТС-тендер Id=4052238. Поставка, монтаж не указан. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>32616419880</t>
+          <t>0301300019426000247</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ФГБУ «ФЦТОЭ» Минздрава России (г. Чебоксары)</t>
+          <t>ГБУЗ Республиканский Клинический Госпиталь Ветеранов Войн им. М.В. Каменева</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Поставка спецодежды</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15.10.2026 14:00 МСК</t>
+          <t>2026-10-15 07:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>878563.71</v>
+        <v>270651</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Камера видеонаблюдения (26.70.13.000): 16 шт × ?; Коммутатор (26.30.11.110): 3 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+          <t>Костюм мужской рабочий  (96/170): 1 шт × 4 857; Костюм мужской рабочий  (104/165): 1 шт × 4 857; Костюм мужской рабочий  (104/176): 2 шт × 4 857; Костюм мужской рабочий  (108/170): 3 шт × 4 857; Костюм мужской рабочий  (108/176): 3 шт × 4 857; Костюм мужской рабочий  (112/170): 2 шт × 4 857; Костюм мужской рабочий  (112/176): 1 шт × 4 857; Костюм мужской рабочий  (96/158): 1 шт × 5 600; … ещё 29</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>43928.1855</v>
-      </c>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+        <v>5012.055555555556</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>202988.25</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>38589.7161838356</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>38589.7161838356</v>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3808,76 +3886,86 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>1 353 ₽ (0.5%)</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>87 856 ₽ (10.0%)</t>
+          <t>27 065 ₽ (10.0%)</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Документация (.docx) недоступна. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>32616439096</t>
+          <t>0302200020326000023</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>СПб ГБУК «Михайловский театр»</t>
+          <t>Республиканская служба по охране, контролю и регулированию использования объектов животного мира, отнесенных к объектам охоты, контролю и надзору в сфере природопользования</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Телеком-оборудование и расходники (СКС, низкий приоритет)</t>
+          <t>Поставка спецобуви</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>44-ФЗ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13.10.2026 09:00 МСК</t>
+          <t>2026-10-14 04:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>987824.58</v>
+        <v>230181</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>ITK оптический пигтейл: 240 шт/м × ?; Кабель оптический: 900 шт/м × ?; Кросс оптический: 10 шт/м × ?; Шкаф телеком. тип 1: 1 шт/м × ?; Шкаф телеком. тип 2: 2 шт/м × ?; Патч-корды типы 1–5: 160 шт/м × ?; Лоток глухой ЛМГ: 10 шт/м × ?; Кабель-канал типы 1–2: 44 шт/м × ?; … ещё 13 (цена за ед. = НМЦК / кол-во)</t>
+          <t>Ботинки специальные с высокими берцами зимние: 18 пар × 3 639; Ботинки специальные с высокими берцами: 17 пар × 8 299; Обувь демисезонная: 4 пар × 5 899</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>528.2484385026738</v>
-      </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>Нет цен — запросить КП</t>
+        <v>5902.076923076923</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>172635.75</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>32819.45923315067</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>32819.45923315067</v>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3892,7 +3980,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>49 391 ₽ (5.0%)</t>
+          <t>1.00 % (≈2 302 ₽)</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -3907,29 +3995,29 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Пропущено: низкий приоритет, срок истекает, не профиль видеонаблюдения. Себестоимость не оценивалась.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Амуниция</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0356500001426008776</t>
+          <t>0340100009726000070</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>МКУ «Управление по делам ГО и ЧС» Лысьвенского МО</t>
+          <t>Федеральное государственное бюджетное Профессиональное Образовательное учреждение «Орловское Специальное Учебно-Воспитательное Учреждение Закрытого Типа»</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Палатки</t>
+          <t>Поставка зимней одежды для воспитанников (термобелье)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3939,38 +4027,38 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13.10.2026 05:00 МСК</t>
+          <t>2026-10-15 08:30</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>190000</v>
+        <v>213567.9</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Палатка каркасная с утеплителем для спасатель: 1 шт × 190 000</t>
+          <t>Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 4 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 3 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 1 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; Белье нательное трикотажное или вязаное: 2 КОМПЛ × 2 033.98; … ещё 29</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>190000</v>
+        <v>2033.98</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>160000</v>
+        <v>160175.925</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.25</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>21972.38356164384</v>
+        <v>30450.74522901369</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-11846.13698630137</v>
-      </c>
-      <c r="O39" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>30450.74522901369</v>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3980,12 +4068,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>не установлено / не указано</t>
+          <t>2 136 ₽ (1.0%)</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.00 % (≈1 900 ₽)</t>
+          <t>10.00 % (≈21 357 ₽)</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3995,75 +4083,77 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Приём заявок заканчивается завтра (13.10.2026 05:00 МСК) — успеть практически нереально. Запрет ПП 1875: нужна реестровая запись российского производителя. Цена — гипотеза.</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Сантехника и ЖКХ</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0372100004526000032</t>
+          <t>32616452815</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ФКУ ИК-7 ГУФСИН России по г. Санкт-Петербургу и Ленинградской обл.</t>
+          <t>Государственное автономное учреждение Здравоохранения «Городская Больница № 2 г. Магнитогорск»</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Запорная арматура (котельная)</t>
+          <t>Поставка комплектов зимней спецодежды и рукавиц</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20.10.2026 11:45 МСК</t>
+          <t>2026-10-15 07:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>525965.97</v>
+        <v>187355.52</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Задвижка чугунная клиновая фланцевая PN16 DN8: 5 шт × 5 652.36; Затвор межфланцевый, корпус сталь, DN80 PN1,6: 5 шт × 5 203.79; Задвижка чугунная клиновая фланцевая PN16 DN1: 10 шт × 7 949.06; Затвор межфланцевый, корпус сталь, DN100: 5 шт × 6 546.88; Затвор межфланцевый, корпус сталь, DN50: 5 шт × 4 080.65; Задвижка чугунная клиновая фланцевая PN16 DN5: 3 шт × 3 414.66; Задвижка чугунная клиновая фланцевая PN16 DN5: 3 шт × 7 376; Обратный клапан межфланцевый чугун DN100: 3 шт × 7 861.20; … ещё 11</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>4696.124732142857</v>
+          <t>Костюм утепленный Ангара: 16 Комплект × ?; Рукавицы утепленные G14: 16 Пара (2 шт.) × ?</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>445321</v>
+        <v>140516.64</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.1533273530985284</v>
+        <v>0.25</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>57712.31357523285</v>
+        <v>26713.3553627178</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-36454.80894772601</v>
-      </c>
-      <c r="O40" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>26713.3553627178</v>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4078,7 +4168,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>5.00 % (≈26 298 ₽)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4088,75 +4178,73 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>Информационная система "Управление закупками отдельными видами юридических лиц"</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Ограничение ПП 1875 (кроме фланцев — преимущество): нужна арматура российского производства с номером реестровой записи РПП (Челарм, СибЗТА — проверить реестр). ТЗ: задвижки чугунные PN16 металл-по-металлу — 30ч6бр это Ру10; под PN16 нужна 30ч515бр/30ч15бр (цена по запросу, вероятно дороже). Затворы</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Амуниция</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>32616456220</t>
+          <t>295997-26LO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ГАУ Амурской области «Амурская авиабаза»</t>
+          <t>МКУ «Городское Хозяйство» Муниципального Образования Волосовское Городское Поселение Волосовского Муниципального Района Ленинградской Области</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Палатки</t>
+          <t>Поставка товаров согласно Спецификации (Специальная одежда и обувь)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Малые закупки</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20.10.2026 16:00 МСК</t>
+          <t>2026-10-13 10:30</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>630600</v>
+        <v>152190</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Палатка универсальная УП-5 «Берег» или эквива: 6 шт × 66 481.86; Тамбур-баня ПБ-1 «Берег» или эквивалент: 6 шт × 27 863.72; Тамбур-соединитель для палаток УП: 6 шт × 10 754.42</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>35033.33333333334</v>
-      </c>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n">
-        <v>670000</v>
+        <v>114142.5</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-0.0624801776086267</v>
+        <v>0.25</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-55458.49863013699</v>
+        <v>21699.41698356164</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-118014.018630137</v>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>21699.41698356164</v>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4174,84 +4262,76 @@
           <t>не установлено / не указано</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Электронный Магазин Ленинградской области</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>НМЦК за комплект 105 100 ₽ против розницы производителя 107 500 ₽ (УП-5 68 000 + ПБ-1 28 500 + соединитель 11 000) — маржа будет только при дилерской скидке Берега (обычно 15–25% для перепродавцов; нужно запросить). Цены по позициям в извещении не указаны, разбивка unit_nmck — оценка пропорционально</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Амуниция</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>32616447980</t>
+          <t>1022079</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>МАУ Сургутского района «Районный молодёжный центр»</t>
+          <t>Краевое ГКУ Для Детей-Сирот и Детей, Оставшихся без Попечения Родителей «Шушенский Детский Дом»</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Спальные принадлежности</t>
+          <t>Закупка одежды</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Коммерческие</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>15.10.2026 09:00 МСК</t>
+          <t>2026-10-15 20:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1400000</v>
+        <v>114000</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Комплекты постельного белья (13.92.12.114): 280 компл × ?; Матрасы (31.03.12.120): 150 шт × ?; Одеяла (13.92.11.110): 150 шт × ?; Подушки (13.92.24.149): 150 шт × ?; Изделия текстильные прочие (13.92.29.190 — на: 150 шт × ?</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>разные ед. изм.</t>
-        </is>
-      </c>
+          <t>нет данных (коммерческая/малая закупка или позиции не опубликованы)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n">
-        <v>1091850</v>
+        <v>85500</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.2201071428571429</v>
+        <v>0.25</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>237151.5136986302</v>
+        <v>16254.24493150685</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-137638.2191780823</v>
-      </c>
-      <c r="O42" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>16254.24493150685</v>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>Участвовать, если ≤2 заявок</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4269,19 +4349,15 @@
           <t>не установлено / не указано</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Срок подачи 15.10 09:00 МСК — осталось меньше 3 дней. ТЗ и обоснование НМЦД (xls) лежат на zakupki.gov.ru, доступа к ним нет: характеристики (ткань, плотность, наполнитель, размеры) и цены по позициям неизвестны, поэтому вся себестоимость — гипотеза. Вероятна высокая конкуренция ивановских производи</t>
+          <t>себестоимость = 75% НМЦК (данные клиента), снижение ≤5%</t>
         </is>
       </c>
     </row>
@@ -4293,17 +4369,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0855200000526003358</t>
+          <t>0348300075526000435</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ГБУЗ «Каменская ЦРБ им. Г.М. Савельевой»; организатор ГКУ ПО «Управление по осуществлению закупок Пензенской обл.»</t>
+          <t>ГБУЗ МО «Королёвская клиническая больница» (ЦКДЛ), лот 7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные (цитрат/K3/активатор)</t>
+          <t>Контейнеры вакуумные для мочи</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4313,38 +4389,38 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>15.10.2026 08:00 МСК</t>
+          <t>19.10.2026 10:00 МСК</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1432800</v>
+        <v>1500000</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с цитратом натрия 3,8%, 4–: 15 600 шт × 10.80; Пробирка вакуумная K3ЭДТА 3–? мл 13х75 (КТРУ : 50 400 шт × 10.80; Пробирка вакуумная с активатором свертывания : 60 000 шт × 12</t>
+          <t>Контейнер вакуумный для мочи 10 мл, 15–16х100: 21 667 шт × 20.64; Контейнер вакуумный для мочи 6,5–7 мл, 13х100: 21 667 шт × 10.66; Контейнер вакуумный для мочи 9–9,5 мл, 16х100: 21 667 шт × 22.70; Контейнер вакуумный для мочи 9,5 мл, 16х100, : 21 667 шт × 15.23</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11.37142857142857</v>
+        <v>17.30742603959939</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1171120</v>
+        <v>1087916.66</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.1826353992183138</v>
+        <v>0.2747222266666667</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>103594.3298630137</v>
+        <v>279266.7297835617</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-233458.7178082192</v>
-      </c>
-      <c r="O43" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>253970.7297835617</v>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4354,27 +4430,23 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>14 328 ₽ (1.0%)</t>
+          <t>15 000 ₽ (1.0%)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>5.00 % (≈71 640 ₽)</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Для СМП, СОНО</t>
-        </is>
-      </c>
+          <t>150 000 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
+          <t>[ГИПОТЕЗА по себестоимости] Цены поставщика не найдены публично — себестоимость ГИПОТЕЗА (85% от цены победителя-инкумбента). Количество не определено (qty условные: НМЦК/Σцен ед. поровну). Ограничение ПП 1875: импорт (ZMT, Китай) допускается, но отклоняется при ≥2 заявках с российскими изделиями. Сильный инкумбент (выигрывает</t>
         </is>
       </c>
     </row>
@@ -4386,17 +4458,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0809500000326003912</t>
+          <t>0369200001226000192</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ГБУЗ РМ «Республиканская клиническая больница им. С.В. Каткова»; организатор ГКУ РМ «Региональный центр организации закупок»</t>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "ЧЕЛЯБИНСКИЙ ОБЛАСТНОЙ КЛИНИЧЕСКИЙ ТЕРАПЕВТИЧЕСКИЙ ГОСПИТАЛЬ ДЛЯ ВЕТЕРАНОВ ВОЙН"</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА</t>
+          <t>Пробирки вакуумные</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4406,38 +4478,38 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>16.10.2026 09:00 МСК</t>
+          <t>19.10.2026 06:00 МСК</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>950000</v>
+        <v>324727.5</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная K3ЭДТА 2–? мл 13х75, пласт: 95 000 шт × 10</t>
+          <t>Пробирка вакуумная для взятия образцов крови : 17 600 шт × 18.06; Пробирка вакуумная для взятия образцов крови : 450 шт × 15.27</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
+        <v>17.9904432132964</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>852400</v>
+        <v>203313.5</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.1027368421052632</v>
+        <v>0.3738950350678646</v>
       </c>
       <c r="L44" s="4" t="n">
         <v>0.25</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-3413.698630136991</v>
+        <v>82054.96121917808</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-239013.698630137</v>
-      </c>
-      <c r="O44" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>13602.40421917808</v>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4452,7 +4524,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>5.00 % (≈47 500 ₽)</t>
+          <t>5.00 % (≈16 236 ₽)</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4462,77 +4534,75 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>РАД (Lot-Online)</t>
+          <t>ТЭК-Торг</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-10. Пробирки 8 мл 13×100 с гелем — проверить, есть ли у UNIVAC объём 8 мл (обычно до 6 мл; 8 мл бывает в формате 16×100).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>СС</t>
+          <t>Сантехника и ЖКХ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0171100002826000003</t>
+          <t>32616451568</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Управление Минюста России по Ярославской области</t>
+          <t>ПАО «Россети Центр и Приволжье» — филиал «Удмуртэнерго»</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Видеонаблюдение (СС, поставка)</t>
+          <t>Запорная арматура</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>15.10.2026 09:00 МСК</t>
+          <t>19.10.2026 09:00 МСК</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>588408.7</v>
+        <v>113094</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Камера видеонаблюдения КТРУ 26.70.13.000-0000: 21 шт × 6 059.67; Коммутатор: 2 шт × 10 851; Трансивер: 1 шт × 2 185.67; Трансивер: 1 шт × 2 184; Источник бесперебойного питания (1): 1 шт × 15 589; Источник бесперебойного питания (2): 1 шт × 21 507; Блок розеток: 2 шт × 1 356.67; Шкаф телекоммуникационный: 2 шт × 15 799.67; … ещё 9</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>разные позиции — см. колонку слева</t>
-        </is>
+          <t>Задвижки (28.14.13.120), характеристики в док: 6 шт × ?; Затворы дисковые (28.14.13.132): 10 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>7068.375</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>745107.8</v>
+        <v>84950</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-0.2663099644855695</v>
+        <v>0.2488549348329708</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.245</v>
+        <v>0.15</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-193660.3510794521</v>
+        <v>21966.38819726027</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-336667.2015274521</v>
-      </c>
-      <c r="O45" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>7662.259077260269</v>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4542,12 +4612,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>5 884 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>30.00 % (≈176 523 ₽)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -4557,12 +4627,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>РАД (Lot-Online)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>[ГИПОТЕЗА по себестоимости] Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
+          <t>[ГИПОТЕЗА по себестоимости] Диаметры и типы неизвестны: ТЗ в rar на zakupki.gov.ru, доступа нет. Запрос котировок для МСП на ЭТП РАД (lot-online). Флаг нацрежима стоит → нужен российский производитель. Малый лот, логистика съедает маржу.</t>
         </is>
       </c>
     </row>
@@ -4574,17 +4644,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0164200001926003491</t>
+          <t>0387200029826000340</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, Тамбовская КЦРБ, онкодиспансер, Петровская, Мичуринская ЦРБ, ТОДКБ и др.)</t>
+          <t>БУ ХМАО-Югры «Нижневартовская окружная клиническая больница»</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА</t>
+          <t>Пробирки вакуумные (8 видов)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4594,38 +4664,38 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>19.10.2026 07:00 МСК</t>
+          <t>16.10.2026 07:00 МСК</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>1691688</v>
+        <v>900000</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с K3ЭДТА, пластик, 2–2,7 м: 35 000 шт × 9.24; То же, поз.2: 54 500 шт × 9.58; То же, поз.3: 25 000 шт × 9.93; То же, поз.4: 10 000 шт × 10.32; То же, поз.5: 2 400 шт × 10.72; То же, поз.6: 50 000 шт × 9.38</t>
+          <t>Пробирка вакуумная K2ЭДТА 2–? мл 13х75, кол-в: 8 154 шт × 12.86; Пробирка вакуумная цитрат 3,8% 3–? мл 13х75, : 8 154 шт × 12.87; Пробирка вакуумная тромбин 4,5 мл 13х75, кол-: 8 154 шт × 12.10; Пробирка вакуумная K-оксалат/NaF 4,5 мл 13х75: 8 154 шт × 14.72; Пробирка вакуумная активатор 5–? мл 13х(90–10: 8 154 шт × 14.67; Пробирка вакуумная цитрат 3,8% 4–? мл 13х75, : 8 154 шт × 12.88; Пробирка вакуумная K2ЭДТА 4–? мл 13х75, кол-в: 8 154 шт × 12.87; Пробирка вакуумная Li-гепарин 4–? мл 13х75, к: 8 154 шт × 17.40</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9.56296212549463</v>
+        <v>13.79690949227373</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1587948</v>
+        <v>617434.5</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.06132336459205243</v>
+        <v>0.3139616666666666</v>
       </c>
       <c r="L46" s="4" t="n">
         <v>0.25</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>10112.2218739726</v>
+        <v>190924.8400684932</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-407641.8923835617</v>
-      </c>
-      <c r="O46" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+        <v>1204.840068493151</v>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4635,206 +4705,3343 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>16 917 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>84 584 ₽ (5.0%)</t>
+          <t>90 000 ₽ (10.0%)</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
+          <t>Количество не определено — qty условные (НМЦК/Σцен ед. поровну). Доставка в Нижневартовск (дорогая логистика). Контракт до 31.03.2027.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0164200001926003492</t>
+          <t>32616445794</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, ТОДКБ, Тамбовская КЦРБ, онкодиспансер, Петровская, Уметская, Бондарская ЦРБ и др.); организатор — уполномоченный орган Тамбовской обл.</t>
+          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Саратовский филиал</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные с активатором свёртывания</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>19.10.2026 07:00 МСК</t>
+          <t>15.10.2026 12:00 МСК</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2815055</v>
+        <v>2176178.2</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с активатором свертывания,: 60 000 шт × 9.89; То же, поз.2: 115 900 шт × 10.15; То же, поз.3: 20 000 шт × 10.31; То же, поз.4: 36 000 шт × 10.92; То же, поз.5: 45 000 шт × 9.91</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>10.16632358252077</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>2484948</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>0.1172648491770143</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>157285.0023013699</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>-513092.4608219178</v>
-      </c>
-      <c r="O47" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>поз.1 ОКПД2 27.32.13.144 Кабели высоковольтны: 100 Метр × ?; поз.2 ОКПД2 27.32.13.111 Кабели силовые с мед: 300 Метр × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 0.07 Километр; тысяча метров × ?; поз.4 ОКПД2 27.32.13.111 Кабели силовые с мед: 120 Метр × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 50 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.22 Километр; тысяча метров × ?; поз.7 ОКПД2 27.32.13.124 Кабели силовые гибки: 1.30 Километр; тысяча метров × ?; поз.8 ОКПД2 27.32.13.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; … ещё 10</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>нет / не указан</t>
+          <t>есть, размер в документации</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>28 151 ₽ (1.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>140 753 ₽ (5.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>РАД (Lot-Online)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
+          <t>НМЦ 2 176 178,20 в ЕИС — БЕЗ НДС (rostender показывает 2 654 937 с НДС 22%). Клиент на УСН: уточнить в ДоЗ правило сравнения цен (у РусГидро обычно без НДС). Флаги нацрежима по всем 18 позициям = false (ЕИС), но ПП №1875 для 27.32 может быть указан в ДоЗ — проверить. Цены поставщиков не подобраны: н</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Медрасходники</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0335200014926003799</t>
+          <t>32616445272</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Совместная закупка 26 ГБУЗ Калининградской обл.; организатор ГКУ КО «Центр обеспечения организации и проведения торгов»</t>
+          <t>АО «Гидроремонт-ВКК» (группа РусГидро), Воткинский филиал</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные (совместная закупка, гель/NaF)</t>
+          <t>Кабель (27.32)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00 МСК</t>
+          <t>15.10.2026 12:00 МСК</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>5909000</v>
+        <v>1201357.95</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Пробирка вакуумная с активатором свертывания/: 94 122 шт × 12.29; Пробирка вакуумная с K-оксалатом и NaF 4 мл 1: 94 122 шт × 9.90; Пробирка вакуумная с активатором/гелем 5 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 6 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 5,5 мл: 94 122 шт × 13.53</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>12.55604428295191</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>5187766.56</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>0.1220567676425792</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>89623.21567123328</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>-1359992.922739726</v>
-      </c>
-      <c r="O48" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>поз.1 ОКПД2 27.32.13.159 Кабели, провода и шн: 135 Метр × ?; поз.2 ОКПД2 27.32.13.131 Провода силовые для : 0.10 Километр; тысяча метров × ?; поз.3 ОКПД2 27.32.13.130 Провода и шнуры сило: 100 Метр × ?; поз.4 ОКПД2 27.32.14.111 Кабели силовые с мед: 0.06 Километр; тысяча метров × ?; поз.5 ОКПД2 27.32.13.130 Провода и шнуры сило: 60 Метр × ?; поз.6 ОКПД2 27.32.13.111 Кабели силовые с мед: 115 Метр × ?; поз.7 ОКПД2 27.32.13.111 Кабели силовые с мед: 100 Метр × ?; поз.8 ОКПД2 27.32.13.143 Кабели контрольные (: 0.20 Километр; тысяча метров × ?; … ещё 7</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>нет / не указан</t>
+          <t>есть, размер в документации</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>7 500 ₽ (0.1%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>295 450 ₽ (5.0%)</t>
+          <t>не установлено / не указано</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
+          <t>РАД (Lot-Online)</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>НМЦ 1 201 357,95 без НДС (rostender: 1 465 656 с НДС). Флаги нацрежима false. Цены не подобраны — нет марок/сечений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Кабель (ЭОМ)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>32616445510</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>АО «НИОПИК»</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Кабель (27.32)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>14.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>529280.65</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Кабель сигнальный КИМЭлВ-ЗГнг(А) (ОКПД2 27.32: 1 усл. ед. × 529 280.65</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>529280.65</v>
+      </c>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>есть, размер в документации</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Цена за метр не определена: неизвестны длина и конструкция. Ориентир по аналогам 1х2х0,75 (КПСнг(А)-FRHF, МКЭШВнг(А)-LS) 30–60 ₽/м с НДС — для КИМ неприменимо без спецификации. ЭТП РТС-тендер.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>32616449701</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>НАО «Центр «Омега» (Краснодарский край)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение (СС, поставка)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>16.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>3229618.2</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Видеокамера тип 1 (26.40.33.111): 20 шт × ?; Видеокамера тип 2: 30 шт × ?; Видеокамера тип 3: 30 шт × ?; Видеокамера тип 4: 20 шт × ?; Аппаратура коммуникационная передающая (26.30: 1 шт × ?; Панели/комплекты электр. аппаратуры (27.12.31: 2 шт × ?; Приборы для телекоммуникаций (26.51.44, тесте: 1 шт × ?; … ещё 2 (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>23923.09777777778</v>
+      </c>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>161 481 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Поставка (АЭФ только СМП), РТС-тендер Id=4056547. Монтаж в предмете не указан, но проверить проект договора. unit_nmck неизвестны → covered_nmck приравнен nmck условно, маржа по гипотезам ненадёжна. Нужна ручная выгрузка Обоснования НМЦД.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>32616433554</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>СПбГУ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение (СС, поставка)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>14.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>1675767</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Видеокамера (26.40.33.111): 41 шт × ?; Части/принадлежности видеооборудования (кронш: 41 шт × ?; Части/принадлежности видеооборудования (короб: 41 шт × ?; Видеорегистратор: 2 шт × ?; Базовые системы хранения данных (HDD?): 16 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>11884.87234042553</v>
+      </c>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>83 788 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>АЭФ только СМП, РТС-тендер Id=4052238. Поставка, монтаж не указан. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>32616419880</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ФГБУ «ФЦТОЭ» Минздрава России (г. Чебоксары)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение (СС, поставка)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>15.10.2026 14:00 МСК</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>878563.71</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Видеорегистратор (26.40.33.114): 1 шт × ?; Камера видеонаблюдения (26.70.13.000): 16 шт × ?; Коммутатор (26.30.11.110): 3 шт × ? (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>43928.1855</v>
+      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>87 856 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Документация (.docx) недоступна. unit_nmck неизвестны → covered_nmck = nmck условно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>32616439096</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>СПб ГБУК «Михайловский театр»</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Телеком-оборудование и расходники (СКС, низкий приоритет)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>13.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>987824.58</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>ITK оптический пигтейл: 240 шт/м × ?; Кабель оптический: 900 шт/м × ?; Кросс оптический: 10 шт/м × ?; Шкаф телеком. тип 1: 1 шт/м × ?; Шкаф телеком. тип 2: 2 шт/м × ?; Патч-корды типы 1–5: 160 шт/м × ?; Лоток глухой ЛМГ: 10 шт/м × ?; Кабель-канал типы 1–2: 44 шт/м × ?; … ещё 13 (цена за ед. = НМЦК / кол-во)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>528.2484385026738</v>
+      </c>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>Нет цен — запросить КП</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>49 391 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Пропущено: низкий приоритет, срок истекает, не профиль видеонаблюдения. Себестоимость не оценивалась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0334100007126000277</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ФЕДЕРАЛЬНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "ЦЕНТРАЛЬНАЯ МЕДИКО-САНИТАРНАЯ ЧАСТЬ № 28 ФЕДЕРАЛЬНОГО МЕДИКО-БИОЛОГИЧЕСКОГО АГЕНТСТВА"</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Контейнеры для биоматериала</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>16.10.2026 05:00 МСК</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>166670</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Контейнер для сбора проб мочи ИВД (22.22.14.0: 10 000 шт × 15.40; Контейнер для сбора кала ИВД, без добавок (22: 1 000 шт × 12.67</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>15.15181818181818</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>120000</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.2800143997120058</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>27358.06180821918</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>-2534.739331506831</v>
+      </c>
+      <c r="O54" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>10.00 % (≈16 667 ₽)</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-31. Контейнер для мочи 100–150 мл (высота 66–89 мм, Ø 49–66 мм) — проверить габариты Перинт 120 мл. Для кала нужен стерильный контейнер с лопаткой 60–100 мл, взята</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0112200000826004463</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ РЕСПУБЛИКИ ТЫВА "РЕСПУБЛИКАНСКАЯ БОЛЬНИЦА №2"</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>19.10.2026 02:00 МСК</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>100164</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 3 600 шт × 10.73; Пробирка вакуумная для взятия образцов крови : 3 600 шт × 11.03; Пробирка вакуумная для взятия образцов крови : 1 200 шт × 18.19</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>11.92428571428571</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>81148</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>0.1898486482169242</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>12836.83767671233</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>-9738.51002739726</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0891200000626010049</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КРАЕВАЯ КЛИНИЧЕСКАЯ ПСИХИАТРИЧЕСКАЯ БОЛЬНИЦА ИМЕНИ В.Х. КАНДИНСКОГО"</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>16.10.2026 01:00 МСК</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>191364</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 7 400 шт × 12.93; Пробирка вакуумная для взятия образцов крови : 7 400 шт × 12.93</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>147672</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0.2283188060450241</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>31022.41301917809</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>-10961.31550684931</v>
+      </c>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>19 136 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2026-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Амуниция</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0356500001426008776</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>МКУ «Управление по делам ГО и ЧС» Лысьвенского МО</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Палатки</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>13.10.2026 05:00 МСК</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>190000</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Палатка каркасная с утеплителем для спасатель: 1 шт × 190 000</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>190000</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>160000</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>21972.38356164384</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>-11846.13698630137</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1.00 % (≈1 900 ₽)</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>[ГИПОТЕЗА по себестоимости] Приём заявок заканчивается завтра (13.10.2026 05:00 МСК) — успеть практически нереально. Запрет ПП 1875: нужна реестровая запись российского производителя. Цена — гипотеза.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0372200275026000470</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>САНКТ-ПЕТЕРБУРГСКОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ КЛИНИЧЕСКАЯ БОЛЬНИЦА СВЯТИТЕЛЯ ЛУКИ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>15.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>536000</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 8 111 шт × 12.60; Пробирка вакуумная для взятия образцов крови : 8 111 шт × 12.95; Пробирка вакуумная для взятия образцов крови : 8 111 шт × 13.30; Пробирка вакуумная для взятия образцов крови : 8 111 шт × 13.30; Пробирка вакуумная для взятия образцов крови : 8 111 шт × 13.93</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>13.21661940574528</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>375224.97</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0.2999206044880313</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>98040.33135709591</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>-17580.20393753418</v>
+      </c>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>53 600 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК/Σцен ед. поровну по позициям. Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0387200009126004356</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ХАНТЫ-МАНСИЙСКОГО АВТОНОМНОГО ОКРУГА - ЮГРЫ "СУРГУТСКАЯ ГОРОДСКАЯ КЛИНИЧЕСКАЯ ПОЛИКЛИНИКА № 3"</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>16.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>304920</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 13 000 шт × 13.10; Пробирка вакуумная для взятия образцов крови : 10 600 шт × 12.70</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>12.92033898305085</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>228369</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>0.2510527351436442</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>45976.71098630137</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>-21529.91178082192</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>30 492 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-06-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0366300030726000092</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "ДОНСКАЯ ГОРОДСКАЯ БОЛЬНИЦА №1"</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>19.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>206600</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 10 000 шт × 11.30; Пробирка вакуумная для взятия образцов крови : 9 000 шт × 10.40</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>10.87368421052632</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>178609</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0.1354840271055179</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>16897.0782739726</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>-31357.88438356164</v>
+      </c>
+      <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>5.00 % (≈10 330 ₽)</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0365300007826000162</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ОБЛАСТНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КАРГАСОКСКАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>16.10.2026 06:00 МСК</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>399280</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 10 000 шт × 12.88; Пробирка вакуумная для взятия образцов крови : 10 000 шт × 12.88; Пробирка вакуумная для взятия образцов крови : 1 000 шт × 12.88; Пробирка вакуумная для взятия образцов крови : 10 000 шт × 12.88</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>302568</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>0.2422159887798037</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>54687.80953424657</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>-34682.8405479452</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>19 964 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-07-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0816500000626015224</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ РЕСПУБЛИКИ САХА (ЯКУТИЯ) "СУНТАРСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>13.10.2026 03:30 МСК</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>511600</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 40 000 шт × 12.79</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>398948</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0.2201954652071931</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>77038.78542465753</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>-36242.93479452054</v>
+      </c>
+      <c r="O62" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-01-25. Доставка в Якутию (дорогая, сезонная логистика).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Сантехника и ЖКХ</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0372100004526000032</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ФКУ ИК-7 ГУФСИН России по г. Санкт-Петербургу и Ленинградской обл.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Запорная арматура (котельная)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>20.10.2026 11:45 МСК</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>525965.97</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Задвижка чугунная клиновая фланцевая PN16 DN8: 5 шт × 5 652.36; Затвор межфланцевый, корпус сталь, DN80 PN1,6: 5 шт × 5 203.79; Задвижка чугунная клиновая фланцевая PN16 DN1: 10 шт × 7 949.06; Затвор межфланцевый, корпус сталь, DN100: 5 шт × 6 546.88; Затвор межфланцевый, корпус сталь, DN50: 5 шт × 4 080.65; Задвижка чугунная клиновая фланцевая PN16 DN5: 3 шт × 3 414.66; Задвижка чугунная клиновая фланцевая PN16 DN5: 3 шт × 7 376; Обратный клапан межфланцевый чугун DN100: 3 шт × 7 861.20; … ещё 11</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>4696.124732142857</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>445321</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>0.1533273530985284</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>57712.31357523285</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>-36454.80894772601</v>
+      </c>
+      <c r="O63" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>5.00 % (≈26 298 ₽)</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>[ГИПОТЕЗА по себестоимости] Ограничение ПП 1875 (кроме фланцев — преимущество): нужна арматура российского производства с номером реестровой записи РПП (Челарм, СибЗТА — проверить реестр). ТЗ: задвижки чугунные PN16 металл-по-металлу — 30ч6бр это Ру10; под PN16 нужна 30ч515бр/30ч15бр (цена по запросу, вероятно дороже). Затворы</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0330300189626000040</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ВОЛОГОДСКОЙ ОБЛАСТИ "КИРИЛЛОВСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>14.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>497760</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 21 000 шт × 15.02; Пробирка вакуумная для взятия образцов крови : 7 000 шт × 10.72; Пробирка вакуумная для взятия образцов крови : 10 000 шт × 10.73</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>13.09894736842105</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>390736</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>0.2150112504018001</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>68659.02246575343</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-42669.1594520548</v>
+      </c>
+      <c r="O64" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-03-09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0744200000226008021</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ОБЛАСТНОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "КУРСКАЯ ГОРОДСКАЯ ДЕТСКАЯ ПОЛИКЛИНИКА"</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>13.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>134030</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 13 000 шт × 10.31</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>138980</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>-0.03693203014250541</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-11276.82630136986</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>-44516.26630136986</v>
+      </c>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>5.00 % (≈6 702 ₽)</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0375200028126000241</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ РЕСПУБЛИКИ КРЫМ " СИМФЕРОПОЛЬСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ КЛИНИЧЕСКАЯ БОЛЬНИЦА "</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>13.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>1398572</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 80 000 шт × 12.40; Пробирка вакуумная для взятия образцов крови : 30 000 шт × 12.40; Пробирка вакуумная для взятия образцов крови : 1 200 шт × 13.47; Пробирка вакуумная для взятия образцов крови : 1 200 шт × 15.34</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>12.44281138790036</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1045369</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>0.2525454535054327</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>256630.3669753424</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>-44927.77720547946</v>
+      </c>
+      <c r="O66" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>13 986 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>5.00 % (≈69 929 ₽)</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>[ГИПОТЕЗА по себестоимости] Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-31. Позиция 4 — пробирка 1 мл высотой 50 мм (микро-вакуумная) — себестоимость условная (hyp). Доставка в Крым.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0372200000926000359</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>САНКТ-ПЕТЕРБУРГСКОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "ГОРОДСКАЯ КЛИНИЧЕСКАЯ БОЛЬНИЦА № 31"</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>13.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>1499640</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 14 002 шт × 13.50; Пробирка вакуумная для взятия образцов крови : 14 002 шт × 14.10; Пробирка вакуумная для взятия образцов крови : 14 002 шт × 11.10; Пробирка вакуумная для взятия образцов крови : 14 002 шт × 13.20; Пробирка вакуумная для взятия образцов крови : 14 002 шт × 12.90; Пробирка вакуумная для взятия образцов крови : 14 002 шт × 11.40; Пробирка вакуумная для взятия образцов крови : 14 002 шт × 11.40; Пробирка вакуумная для взятия образцов крови : 14 002 шт × 19.50</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>13.38773032423939</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1054161.36</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>0.2970449599637027</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>270241.6847276712</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>-53972.9278027398</v>
+      </c>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>7 498 ₽ (0.5%)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>149 964 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК/Σцен ед. поровну по позициям. Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-12-31. Объёмы и размеры в ТЗ почти не указаны (только цитрат 4–4,05 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0354300008826000066</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ОРЛОВСКОЙ ОБЛАСТИ "БОЛХОВСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>19.10.2026 09:37 МСК</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>125400</v>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 5 000 шт × 8.36; Пробирка вакуумная для взятия образцов крови : 10 000 шт × 8.36</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>143500</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>-0.1443381180223285</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-25865.39178082192</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>-56964.59178082192</v>
+      </c>
+      <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>6 270 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-02-02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0139200000126012135</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "БЕЛОВСКАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>14.10.2026 03:00 МСК</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>179484</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 6 000 шт × 7.44; Пробирка вакуумная для взятия образцов крови : 4 000 шт × 9.45; Пробирка вакуумная для взятия образцов крови : 9 000 шт × 9.74; Пробирка вакуумная для взятия образцов крови : 1 200 шт × 7.82</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>8.885346534653465</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>191598</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>-0.06749348131309754</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-20898.83638356164</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-65410.86838356165</v>
+      </c>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>7.00 % (≈12 564 ₽)</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>ТЭК-Торг</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>[ГИПОТЕЗА по себестоимости] Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0744200000226008031</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ОБЛАСТНОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ  "ЩИГРОВСКО-ЧЕРЕМИСИНОВСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>14.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>152000</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 10 000 шт × 7.55; Пробирка вакуумная для взятия образцов крови : 10 000 шт × 7.65</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>188100</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>-0.2375</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-44530.79452054795</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>-82226.79452054795</v>
+      </c>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>5.00 % (≈7 600 ₽)</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Амуниция</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>32616456220</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ГАУ Амурской области «Амурская авиабаза»</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Палатки</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>20.10.2026 16:00 МСК</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>630600</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Палатка универсальная УП-5 «Берег» или эквива: 6 шт × 66 481.86; Тамбур-баня ПБ-1 «Берег» или эквивалент: 6 шт × 27 863.72; Тамбур-соединитель для палаток УП: 6 шт × 10 754.42</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>35033.33333333334</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>670000</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>-0.0624801776086267</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-55458.49863013699</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>-118014.018630137</v>
+      </c>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>НМЦК за комплект 105 100 ₽ против розницы производителя 107 500 ₽ (УП-5 68 000 + ПБ-1 28 500 + соединитель 11 000) — маржа будет только при дилерской скидке Берега (обычно 15–25% для перепродавцов; нужно запросить). Цены по позициям в извещении не указаны, разбивка unit_nmck — оценка пропорционально</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0341300008826000252</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ОБЛАСТНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "БУЙСКАЯ ЦЕНТРАЛЬНАЯ РАЙОННАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>19.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>249162</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 31 700 шт × 7.86</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>286501</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>-0.1498583251057545</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-58327.70476712329</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>-120119.8807671233</v>
+      </c>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>12 458 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-04-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Амуниция</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>32616447980</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>МАУ Сургутского района «Районный молодёжный центр»</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Спальные принадлежности</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>15.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Комплекты постельного белья (13.92.12.114): 280 компл × ?; Матрасы (31.03.12.120): 150 шт × ?; Одеяла (13.92.11.110): 150 шт × ?; Подушки (13.92.24.149): 150 шт × ?; Изделия текстильные прочие (13.92.29.190 — на: 150 шт × ?</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>разные ед. изм.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1091850</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>0.2201071428571429</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>237151.5136986302</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-137638.2191780823</v>
+      </c>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>[ГИПОТЕЗА по себестоимости] Срок подачи 15.10 09:00 МСК — осталось меньше 3 дней. ТЗ и обоснование НМЦД (xls) лежат на zakupki.gov.ru, доступа к ним нет: характеристики (ткань, плотность, наполнитель, размеры) и цены по позициям неизвестны, поэтому вся себестоимость — гипотеза. Вероятна высокая конкуренция ивановских производи</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0352200029826000793</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ОМСКОЙ ОБЛАСТИ "КЛИНИЧЕСКИЙ МЕДИКО-ХИРУРГИЧЕСКИЙ ЦЕНТР МИНИСТЕРСТВА ЗДРАВООХРАНЕНИЯ ОМСКОЙ ОБЛАСТИ"</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>16.10.2026 06:00 МСК</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>392000</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 40 000 шт × 9.80</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>389480</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>0.006428571428571428</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-43298.73972602739</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>-140514.7397260274</v>
+      </c>
+      <c r="O74" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>39 200 ₽ (10.0%)</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2027-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0348100015026000227</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ФЕДЕРАЛЬНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ "МЕДИКО-САНИТАРНАЯ ЧАСТЬ № 164 ФЕДЕРАЛЬНОГО МЕДИКО-БИОЛОГИЧЕСКОГО АГЕНТСТВА"</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>15.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>291900</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 20 000 шт × 9.30; Пробирка вакуумная для взятия образцов крови : 15 000 шт × 5.83; Пробирка вакуумная для взятия образцов крови : 3 000 шт × 6.15</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>7.681578947368421</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>385538</v>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>-0.3207879410757108</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-109070.9293150685</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>-181462.1293150685</v>
+      </c>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>5.00 % (≈14 595 ₽)</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2026-12-15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0356200000826000232</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ПЕРМСКОГО КРАЯ "ПЕРМСКИЙ КРАЕВОЙ КЛИНИЧЕСКИЙ ГОСПИТАЛЬ ДЛЯ ВЕТЕРАНОВ ВОЙН"</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>14.10.2026 06:00 МСК</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>577000</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 21 000 шт × 9.85; Пробирка вакуумная для взятия образцов крови : 17 000 шт × 9.56; Пробирка вакуумная для взятия образцов крови : 10 000 шт × 10.17; Пробирка вакуумная для взятия образцов крови : 11 000 шт × 9.63</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>9.779661016949152</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>555705</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>0.03690641247833622</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-44220.17808219178</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>-187316.1780821918</v>
+      </c>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>5 770 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>5.00 % (≈28 850 ₽)</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Только СМП. Срок контракта до 2027-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0136500001126005371</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ТВЕРСКОЙ ОБЛАСТИ "ОБЛАСТНАЯ КЛИНИЧЕСКАЯ БОЛЬНИЦА"</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>14.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>558000</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови : 60 000 шт × 9.30</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>583770</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>-0.04618279569892473</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-51345.68219178083</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>-189729.6821917808</v>
+      </c>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>27 900 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Запрет ПП 1875 — только российские изделия (UNIVAC/МиниМед/Гранат подходят при наличии в реестре). Срок контракта до 2026-12-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0855200000526003358</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Каменская ЦРБ им. Г.М. Савельевой»; организатор ГКУ ПО «Управление по осуществлению закупок Пензенской обл.»</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные (цитрат/K3/активатор)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>15.10.2026 08:00 МСК</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>1432800</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с цитратом натрия 3,8%, 4–: 15 600 шт × 10.80; Пробирка вакуумная K3ЭДТА 3–? мл 13х75 (КТРУ : 50 400 шт × 10.80; Пробирка вакуумная с активатором свертывания : 60 000 шт × 12</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>11.37142857142857</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1171120</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>0.1826353992183138</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>103594.3298630137</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-233458.7178082192</v>
+      </c>
+      <c r="O78" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>14 328 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>5.00 % (≈71 640 ₽)</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Запас НМЦК к цене МедРТ 17–20% — при медианной скидке 25% убыток; работает только с заводской ценой. Контракт до 30.12.2027 (поставка партиями — длинный оборот). СМП-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0809500000326003912</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ГБУЗ РМ «Республиканская клиническая больница им. С.В. Каткова»; организатор ГКУ РМ «Региональный центр организации закупок»</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>16.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>950000</v>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная K3ЭДТА 2–? мл 13х75, пласт: 95 000 шт × 10</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>852400</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>0.1027368421052632</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-3413.698630136991</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-239013.698630137</v>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>не установлено / не указано</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>5.00 % (≈47 500 ₽)</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>РАД (Lot-Online)</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>НМЦК 10,00 ₽ vs дистрибьютор 8,92 ₽ (запас 11%) — убыточно при любой скидке &gt;11% без заводской цены. Контракт до 30.12.2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>СС</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0171100002826000003</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Управление Минюста России по Ярославской области</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение (СС, поставка)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>15.10.2026 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>588408.7</v>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Камера видеонаблюдения КТРУ 26.70.13.000-0000: 21 шт × 6 059.67; Коммутатор: 2 шт × 10 851; Трансивер: 1 шт × 2 185.67; Трансивер: 1 шт × 2 184; Источник бесперебойного питания (1): 1 шт × 15 589; Источник бесперебойного питания (2): 1 шт × 21 507; Блок розеток: 2 шт × 1 356.67; Шкаф телекоммуникационный: 2 шт × 15 799.67; … ещё 9</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>разные позиции — см. колонку слева</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>745107.8</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>-0.2663099644855695</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-193660.3510794521</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-336667.2015274521</v>
+      </c>
+      <c r="O80" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>5 884 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>30.00 % (≈176 523 ₽)</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>[ГИПОТЕЗА по себестоимости] Запрос котировок, СМП, обеспечение исполнения 30%. Ограничение (ПП 1875) на все позиции. Камера: КТРУ требует матрицу ≤1/3" при 5 Мп 2560×1920 и НМЦК 6 060 ₽ — типичная спецификация Hikvision/HiWatch; реестровые TRASSIR 5 Мп (1/2.8") стоят от 11,3–13,4 тыс. опт и формально не подходят по размеру мат</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0164200001926003491</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, Тамбовская КЦРБ, онкодиспансер, Петровская, Мичуринская ЦРБ, ТОДКБ и др.)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>1691688</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с K3ЭДТА, пластик, 2–2,7 м: 35 000 шт × 9.24; То же, поз.2: 54 500 шт × 9.58; То же, поз.3: 25 000 шт × 9.93; То же, поз.4: 10 000 шт × 10.32; То же, поз.5: 2 400 шт × 10.72; То же, поз.6: 50 000 шт × 9.38</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>9.56296212549463</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>1587948</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>0.06132336459205243</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>10112.2218739726</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-407641.8923835617</v>
+      </c>
+      <c r="O81" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>16 917 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>84 584 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Совместная закупка (9 контрактов/адресов). Запрет иностранного. Маржа по прайсу дистрибьютора ~6% до снижения; победители по K3 в 09–10.2026 отдавали по 8.75–10.16 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0164200001926003492</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Совместная закупка 9 ТОГБУЗ Тамбовской обл. (ГКП №5, ГКБ №4, ТОДКБ, Тамбовская КЦРБ, онкодиспансер, Петровская, Уметская, Бондарская ЦРБ и др.); организатор — уполномоченный орган Тамбовской обл.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные с активатором свёртывания</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>19.10.2026 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>2815055</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания,: 60 000 шт × 9.89; То же, поз.2: 115 900 шт × 10.15; То же, поз.3: 20 000 шт × 10.31; То же, поз.4: 36 000 шт × 10.92; То же, поз.5: 45 000 шт × 9.91</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>10.16632358252077</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>2484948</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>0.1172648491770143</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>157285.0023013699</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-513092.4608219178</v>
+      </c>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>28 151 ₽ (1.0%)</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>140 753 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Совместная закупка: 9 отдельных контрактов, 9 адресов, приёмка у каждого. Запрет иностранного (нужен РФ-производитель). Крупный лот (2.8 млн) привлечёт производителей/крупных дилеров — высокая вероятность глубокого снижения. Контракты до 25–30.12.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Медрасходники</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0335200014926003799</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Совместная закупка 26 ГБУЗ Калининградской обл.; организатор ГКУ КО «Центр обеспечения организации и проведения торгов»</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные (совместная закупка, гель/NaF)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>26.10.2026 10:00 МСК</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>5909000</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания/: 94 122 шт × 12.29; Пробирка вакуумная с K-оксалатом и NaF 4 мл 1: 94 122 шт × 9.90; Пробирка вакуумная с активатором/гелем 5 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 6 мл 1: 94 122 шт × 13.53; Пробирка вакуумная с активатором/гелем 5,5 мл: 94 122 шт × 13.53</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>12.55604428295191</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>5187766.56</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>0.1220567676425792</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>89623.21567123328</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-1359992.922739726</v>
+      </c>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>нет / не указан</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>7 500 ₽ (0.1%)</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>295 450 ₽ (5.0%)</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
         <is>
           <t>Количество не определено (контракт на сумму, цена за ед.) — qty условные: НМЦК поделена поровну по позициям (НМЦК/Σцен ед.). 26 отдельных контрактов, ~26 точек доставки в эксклаве (транзит через ЛТ/паром), срок до 31.07.2027. NaF-пробирка: дистрибьюторская цена 10,93 &gt; НМЦК 9,90 — убыточна без завод</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U48"/>
+  <autoFilter ref="A1:U83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4897,13 +8104,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>556474.3205479452</v>
+        <v>4078751.933263014</v>
       </c>
     </row>
     <row r="4">

--- a/TENDERS_1210.xlsx
+++ b/TENDERS_1210.xlsx
@@ -647,10 +647,10 @@
         <v>0.8291182501708817</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9262976.735973697</v>
+        <v>9613813.031013699</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>7859631.555813699</v>
@@ -687,7 +687,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ на эквивалент</t>
+          <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ на эквивалент; снижение 15% — консервативно (медиана по соли 3%)</t>
         </is>
       </c>
     </row>
@@ -740,10 +740,10 @@
         <v>0.851279000594884</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4621641.290520548</v>
+        <v>4791731.594520547</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>3941280.074520547</v>
@@ -776,7 +776,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>223-ФЗ; обеспечение исполнения 10%</t>
+          <t>223-ФЗ; обеспечение исполнения 10%; снижение 15% — консервативно (медиана по соли 3%)</t>
         </is>
       </c>
     </row>
@@ -922,10 +922,10 @@
         <v>0.7960848287112561</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1018243.203419178</v>
+        <v>1058559.968219178</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>856976.144219178</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ</t>
+          <t>223-ФЗ; «Концентрат минеральный Галит» — сверить ТЗ; снижение 15% — консервативно (медиана по соли 3%)</t>
         </is>
       </c>
     </row>
